--- a/ukeplan/eksempel/Ukeplan-demo.xlsx
+++ b/ukeplan/eksempel/Ukeplan-demo.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Oppsett" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Lister" sheetId="3" state="hidden" r:id="rId3"/>
     <sheet name="Timeplan" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Rom og lærer" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Lærere" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Uke" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Beskjeder" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
@@ -20,9 +20,10 @@
     <definedName name="Fagliste">OFFSET(Oppsett!$E$10,0,0,MAX(1,COUNTA(Oppsett!$E$10:$E$110)),1)</definedName>
     <definedName name="Dager">Lister!$A$2:$A$6</definedName>
     <definedName name="Typer">Lister!$B$2:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Rom og lærer'!$A$1:$D$120</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Uke'!$A$1:$H$400</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Beskjeder'!$A$1:$D$120</definedName>
+    <definedName name="Uker">Lister!$D$2:$D$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Lærere'!$A$1:$C$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Uke'!$A$1:$H$401</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Beskjeder'!$A$1:$D$121</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -288,7 +289,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -368,16 +369,13 @@
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="15">
     <dxf>
       <font>
         <name val="Aptos Narrow"/>
@@ -544,6 +542,13 @@
     <dxf>
       <border>
         <top style="medium">
+          <color rgb="0016212A"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thick">
           <color rgb="0016212A"/>
         </top>
       </border>
@@ -910,7 +915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B19"/>
+  <dimension ref="B2:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -941,21 +946,21 @@
     <row r="6" ht="26" customHeight="1">
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>3  Rom og lærer – hvilket rom og hvilken lærer faget har i hver klasse. Valgfritt.</t>
+          <t>3  Lærere – hvilken lærer faget har i hver klasse. Valgfritt.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>4  Uke – det som er nytt: tema, lekser, prøver og frister. Én rad per punkt.</t>
+          <t>4  Uke – tema, lekser og frister. Velg uke i nedtrekket i første kolonne.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>5  Beskjeder – korte meldinger hjem.</t>
+          <t>5  Beskjeder – korte meldinger hjem, med samme ukevalg.</t>
         </is>
       </c>
     </row>
@@ -966,57 +971,85 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
+    <row r="11" ht="30" customHeight="1">
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Du får én nettside med alle ukene. Elevene blar mellom dem med piltastene eller pilene.</t>
+          <t>Du får én nettside med alle ukene. Elevene blar mellom dem med pilene eller piltastene.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="B13" s="4" t="inlineStr">
         <is>
+          <t>Når det blir mange uker</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Uke-nedtrekket viser både ukenummer og datoer, så du slipper å telle. Én arbeidsbok tar hele skoleåret.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Klikk på filterpila i Uke-kolonnen og hak av for én uke når du vil jobbe med bare den. Det er en tykk strek mellom ukene.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Skal du gjenta noe fra forrige uke: merk radene, kopier, lim inn nederst og bytt uke i nedtrekket.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="B18" s="4" t="inlineStr">
+        <is>
           <t>Godt å vite</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Uke-kolonnen bestemmer hvilken uke raden hører til. Lar du den stå tom, havner raden i uka som står i Oppsett.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="B15" s="3" t="inlineStr">
+    <row r="19" ht="30" customHeight="1">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Timeplanen gjentas i alle uker. Du fyller den ut én gang, ikke én gang per uke.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="B16" s="3" t="inlineStr">
+    <row r="20" ht="30" customHeight="1">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Klasse, Dag, Fag, Frist og Type har nedtrekkslister. Klikk i cella og velg.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="B17" s="3" t="inlineStr">
+    <row r="21" ht="30" customHeight="1">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Skriv «Alle» i Klasse-feltet når noe gjelder alle klassene.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>I Uke-arket får hver klasse sin egen tone, og det kommer en strek der klassen bytter.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="B19" s="3" t="inlineStr">
+    <row r="22" ht="30" customHeight="1">
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Hver klasse får sin egen tone på ukearket, og det kommer en strek der klassen bytter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Lekser og frister havner i «Å gjøre denne uka» på nettsiden, sortert etter frist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Rader du ikke bruker, lar du stå tomme. Rekkefølgen spiller ingen rolle.</t>
         </is>
@@ -1039,10 +1072,9 @@
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -1082,11 +1114,16 @@
     <row r="6" ht="22" customHeight="1">
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Mandag i uka</t>
+          <t>Mandag i den uka</t>
         </is>
       </c>
       <c r="C6" s="9" t="n">
         <v>46265</v>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>← herfra regnes datoene i alle de andre ukene</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -1666,7 +1703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1680,6 +1717,11 @@
           <t>Typer</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Uker</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1692,6 +1734,11 @@
           <t>Prøve</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>30 · 20.–24. jul 2026</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1704,6 +1751,11 @@
           <t>Innlevering</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>31 · 27.–31. jul 2026</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1716,6 +1768,11 @@
           <t>Frist</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>32 · 3.–7. aug 2026</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1728,6 +1785,11 @@
           <t>Tur</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>33 · 10.–14. aug 2026</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1740,11 +1802,301 @@
           <t>Info</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>34 · 17.–21. aug 2026</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
           <t>Vurdering</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>35 · 24.–28. aug 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>36 · 31. aug – 4. sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>37 · 7.–11. sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>38 · 14.–18. sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>39 · 21.–25. sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>40 · 28. sep – 2. okt 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>41 · 5.–9. okt 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>42 · 12.–16. okt 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>43 · 19.–23. okt 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>44 · 26.–30. okt 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>45 · 2.–6. nov 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>46 · 9.–13. nov 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>47 · 16.–20. nov 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>48 · 23.–27. nov 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>49 · 30. nov – 4. des 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>50 · 7.–11. des 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>51 · 14.–18. des 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>52 · 21.–25. des 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>53 · 28. des – 1. jan 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1 · 4.–8. jan 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2 · 11.–15. jan 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>3 · 18.–22. jan 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>4 · 25.–29. jan 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>5 · 1.–5. feb 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>6 · 8.–12. feb 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>7 · 15.–19. feb 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>8 · 22.–26. feb 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>9 · 1.–5. mar 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>10 · 8.–12. mar 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>11 · 15.–19. mar 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>12 · 22.–26. mar 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>13 · 29. mar – 2. apr 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>14 · 5.–9. apr 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>15 · 12.–16. apr 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>16 · 19.–23. apr 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>17 · 26.–30. apr 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>18 · 3.–7. mai 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>19 · 10.–14. mai 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>20 · 17.–21. mai 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>21 · 24.–28. mai 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>22 · 31. mai – 4. jun 2027</t>
         </is>
       </c>
     </row>
@@ -2807,13 +3159,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D120"/>
+  <dimension ref="A1:C121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -2829,11 +3180,6 @@
       </c>
       <c r="C1" s="30" t="inlineStr">
         <is>
-          <t>Rom</t>
-        </is>
-      </c>
-      <c r="D1" s="30" t="inlineStr">
-        <is>
           <t>Lærer</t>
         </is>
       </c>
@@ -2846,17 +3192,12 @@
       </c>
       <c r="B2" s="31" t="inlineStr">
         <is>
-          <t>Kroppsøving</t>
+          <t>Norsk</t>
         </is>
       </c>
       <c r="C2" s="31" t="inlineStr">
         <is>
-          <t>Gymsal</t>
-        </is>
-      </c>
-      <c r="D2" s="31" t="inlineStr">
-        <is>
-          <t>MR</t>
+          <t>KM</t>
         </is>
       </c>
     </row>
@@ -2868,17 +3209,12 @@
       </c>
       <c r="B3" s="31" t="inlineStr">
         <is>
-          <t>Mat og helse</t>
+          <t>Matematikk</t>
         </is>
       </c>
       <c r="C3" s="31" t="inlineStr">
         <is>
-          <t>Kjøkken</t>
-        </is>
-      </c>
-      <c r="D3" s="31" t="inlineStr">
-        <is>
-          <t>IL</t>
+          <t>AT</t>
         </is>
       </c>
     </row>
@@ -2890,17 +3226,12 @@
       </c>
       <c r="B4" s="31" t="inlineStr">
         <is>
-          <t>Kunst og håndverk</t>
+          <t>Engelsk</t>
         </is>
       </c>
       <c r="C4" s="31" t="inlineStr">
         <is>
-          <t>K&amp;H</t>
-        </is>
-      </c>
-      <c r="D4" s="31" t="inlineStr">
-        <is>
-          <t>EV</t>
+          <t>SB</t>
         </is>
       </c>
     </row>
@@ -2912,17 +3243,12 @@
       </c>
       <c r="B5" s="31" t="inlineStr">
         <is>
-          <t>Naturfag</t>
+          <t>Samfunnsfag</t>
         </is>
       </c>
       <c r="C5" s="31" t="inlineStr">
         <is>
-          <t>Naturfagrom</t>
-        </is>
-      </c>
-      <c r="D5" s="31" t="inlineStr">
-        <is>
-          <t>IL</t>
+          <t>PH</t>
         </is>
       </c>
     </row>
@@ -2934,37 +3260,27 @@
       </c>
       <c r="B6" s="31" t="inlineStr">
         <is>
-          <t>Musikk</t>
+          <t>KRLE</t>
         </is>
       </c>
       <c r="C6" s="31" t="inlineStr">
         <is>
-          <t>Musikkrom</t>
-        </is>
-      </c>
-      <c r="D6" s="31" t="inlineStr">
-        <is>
-          <t>EV</t>
+          <t>PH</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="31" t="inlineStr">
         <is>
-          <t>8A</t>
+          <t>Alle</t>
         </is>
       </c>
       <c r="B7" s="31" t="inlineStr">
         <is>
-          <t>Engelsk</t>
+          <t>Tysk</t>
         </is>
       </c>
       <c r="C7" s="31" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="D7" s="31" t="inlineStr">
         <is>
           <t>SB</t>
         </is>
@@ -2973,1083 +3289,647 @@
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="31" t="inlineStr">
         <is>
-          <t>8A</t>
+          <t>Alle</t>
         </is>
       </c>
       <c r="B8" s="31" t="inlineStr">
         <is>
-          <t>KRLE</t>
+          <t>Valgfag</t>
         </is>
       </c>
       <c r="C8" s="31" t="inlineStr">
         <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="D8" s="31" t="inlineStr">
-        <is>
-          <t>PH</t>
+          <t>MR</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="31" t="inlineStr">
         <is>
-          <t>8A</t>
+          <t>Alle</t>
         </is>
       </c>
       <c r="B9" s="31" t="inlineStr">
         <is>
-          <t>Matematikk</t>
+          <t>Kroppsøving</t>
         </is>
       </c>
       <c r="C9" s="31" t="inlineStr">
         <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="D9" s="31" t="inlineStr">
-        <is>
-          <t>AT</t>
+          <t>MR</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="31" t="inlineStr">
         <is>
-          <t>8A</t>
+          <t>Alle</t>
         </is>
       </c>
       <c r="B10" s="31" t="inlineStr">
         <is>
-          <t>Norsk</t>
+          <t>Mat og helse</t>
         </is>
       </c>
       <c r="C10" s="31" t="inlineStr">
         <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="D10" s="31" t="inlineStr">
-        <is>
-          <t>KM</t>
+          <t>IL</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="31" t="inlineStr">
         <is>
-          <t>8A</t>
+          <t>Alle</t>
         </is>
       </c>
       <c r="B11" s="31" t="inlineStr">
         <is>
-          <t>Samfunnsfag</t>
+          <t>Kunst og håndverk</t>
         </is>
       </c>
       <c r="C11" s="31" t="inlineStr">
         <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="D11" s="31" t="inlineStr">
-        <is>
-          <t>PH</t>
+          <t>EV</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="31" t="inlineStr">
         <is>
-          <t>8A</t>
+          <t>Alle</t>
         </is>
       </c>
       <c r="B12" s="31" t="inlineStr">
         <is>
-          <t>Valgfag</t>
+          <t>Naturfag</t>
         </is>
       </c>
       <c r="C12" s="31" t="inlineStr">
         <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="D12" s="31" t="inlineStr">
-        <is>
-          <t>MR</t>
+          <t>IL</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="31" t="inlineStr">
         <is>
-          <t>8B</t>
+          <t>Alle</t>
         </is>
       </c>
       <c r="B13" s="31" t="inlineStr">
         <is>
-          <t>Engelsk</t>
+          <t>Musikk</t>
         </is>
       </c>
       <c r="C13" s="31" t="inlineStr">
         <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="D13" s="31" t="inlineStr">
-        <is>
-          <t>SB</t>
+          <t>EV</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="31" t="inlineStr">
-        <is>
-          <t>8B</t>
-        </is>
-      </c>
-      <c r="B14" s="31" t="inlineStr">
-        <is>
-          <t>KRLE</t>
-        </is>
-      </c>
-      <c r="C14" s="31" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="D14" s="31" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
+      <c r="A14" s="31" t="n"/>
+      <c r="B14" s="31" t="n"/>
+      <c r="C14" s="31" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="31" t="inlineStr">
-        <is>
-          <t>8B</t>
-        </is>
-      </c>
-      <c r="B15" s="31" t="inlineStr">
-        <is>
-          <t>Matematikk</t>
-        </is>
-      </c>
-      <c r="C15" s="31" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="D15" s="31" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
+      <c r="A15" s="31" t="n"/>
+      <c r="B15" s="31" t="n"/>
+      <c r="C15" s="31" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="31" t="inlineStr">
-        <is>
-          <t>8B</t>
-        </is>
-      </c>
-      <c r="B16" s="31" t="inlineStr">
-        <is>
-          <t>Norsk</t>
-        </is>
-      </c>
-      <c r="C16" s="31" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="D16" s="31" t="inlineStr">
-        <is>
-          <t>KM</t>
-        </is>
-      </c>
+      <c r="A16" s="31" t="n"/>
+      <c r="B16" s="31" t="n"/>
+      <c r="C16" s="31" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="31" t="inlineStr">
-        <is>
-          <t>8B</t>
-        </is>
-      </c>
-      <c r="B17" s="31" t="inlineStr">
-        <is>
-          <t>Samfunnsfag</t>
-        </is>
-      </c>
-      <c r="C17" s="31" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="D17" s="31" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
+      <c r="A17" s="31" t="n"/>
+      <c r="B17" s="31" t="n"/>
+      <c r="C17" s="31" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="31" t="inlineStr">
-        <is>
-          <t>8B</t>
-        </is>
-      </c>
-      <c r="B18" s="31" t="inlineStr">
-        <is>
-          <t>Valgfag</t>
-        </is>
-      </c>
-      <c r="C18" s="31" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="D18" s="31" t="inlineStr">
-        <is>
-          <t>MR</t>
-        </is>
-      </c>
+      <c r="A18" s="31" t="n"/>
+      <c r="B18" s="31" t="n"/>
+      <c r="C18" s="31" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="31" t="inlineStr">
-        <is>
-          <t>9A</t>
-        </is>
-      </c>
-      <c r="B19" s="31" t="inlineStr">
-        <is>
-          <t>Engelsk</t>
-        </is>
-      </c>
-      <c r="C19" s="31" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="D19" s="31" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
+      <c r="A19" s="31" t="n"/>
+      <c r="B19" s="31" t="n"/>
+      <c r="C19" s="31" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="31" t="inlineStr">
-        <is>
-          <t>9A</t>
-        </is>
-      </c>
-      <c r="B20" s="31" t="inlineStr">
-        <is>
-          <t>KRLE</t>
-        </is>
-      </c>
-      <c r="C20" s="31" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="D20" s="31" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
+      <c r="A20" s="31" t="n"/>
+      <c r="B20" s="31" t="n"/>
+      <c r="C20" s="31" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="31" t="inlineStr">
-        <is>
-          <t>9A</t>
-        </is>
-      </c>
-      <c r="B21" s="31" t="inlineStr">
-        <is>
-          <t>Matematikk</t>
-        </is>
-      </c>
-      <c r="C21" s="31" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="D21" s="31" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
+      <c r="A21" s="31" t="n"/>
+      <c r="B21" s="31" t="n"/>
+      <c r="C21" s="31" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="31" t="inlineStr">
-        <is>
-          <t>9A</t>
-        </is>
-      </c>
-      <c r="B22" s="31" t="inlineStr">
-        <is>
-          <t>Norsk</t>
-        </is>
-      </c>
-      <c r="C22" s="31" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="D22" s="31" t="inlineStr">
-        <is>
-          <t>KM</t>
-        </is>
-      </c>
+      <c r="A22" s="31" t="n"/>
+      <c r="B22" s="31" t="n"/>
+      <c r="C22" s="31" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="31" t="inlineStr">
-        <is>
-          <t>9A</t>
-        </is>
-      </c>
-      <c r="B23" s="31" t="inlineStr">
-        <is>
-          <t>Samfunnsfag</t>
-        </is>
-      </c>
-      <c r="C23" s="31" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="D23" s="31" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
+      <c r="A23" s="31" t="n"/>
+      <c r="B23" s="31" t="n"/>
+      <c r="C23" s="31" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="31" t="inlineStr">
-        <is>
-          <t>9A</t>
-        </is>
-      </c>
-      <c r="B24" s="31" t="inlineStr">
-        <is>
-          <t>Tysk</t>
-        </is>
-      </c>
-      <c r="C24" s="31" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="D24" s="31" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
+      <c r="A24" s="31" t="n"/>
+      <c r="B24" s="31" t="n"/>
+      <c r="C24" s="31" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="31" t="inlineStr">
-        <is>
-          <t>9A</t>
-        </is>
-      </c>
-      <c r="B25" s="31" t="inlineStr">
-        <is>
-          <t>Valgfag</t>
-        </is>
-      </c>
-      <c r="C25" s="31" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="D25" s="31" t="inlineStr">
-        <is>
-          <t>MR</t>
-        </is>
-      </c>
+      <c r="A25" s="31" t="n"/>
+      <c r="B25" s="31" t="n"/>
+      <c r="C25" s="31" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="31" t="inlineStr">
-        <is>
-          <t>10B</t>
-        </is>
-      </c>
-      <c r="B26" s="31" t="inlineStr">
-        <is>
-          <t>Engelsk</t>
-        </is>
-      </c>
-      <c r="C26" s="31" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="D26" s="31" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
+      <c r="A26" s="31" t="n"/>
+      <c r="B26" s="31" t="n"/>
+      <c r="C26" s="31" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="31" t="inlineStr">
-        <is>
-          <t>10B</t>
-        </is>
-      </c>
-      <c r="B27" s="31" t="inlineStr">
-        <is>
-          <t>KRLE</t>
-        </is>
-      </c>
-      <c r="C27" s="31" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="D27" s="31" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
+      <c r="A27" s="31" t="n"/>
+      <c r="B27" s="31" t="n"/>
+      <c r="C27" s="31" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="31" t="inlineStr">
-        <is>
-          <t>10B</t>
-        </is>
-      </c>
-      <c r="B28" s="31" t="inlineStr">
-        <is>
-          <t>Matematikk</t>
-        </is>
-      </c>
-      <c r="C28" s="31" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="D28" s="31" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
+      <c r="A28" s="31" t="n"/>
+      <c r="B28" s="31" t="n"/>
+      <c r="C28" s="31" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="31" t="inlineStr">
-        <is>
-          <t>10B</t>
-        </is>
-      </c>
-      <c r="B29" s="31" t="inlineStr">
-        <is>
-          <t>Norsk</t>
-        </is>
-      </c>
-      <c r="C29" s="31" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="D29" s="31" t="inlineStr">
-        <is>
-          <t>KM</t>
-        </is>
-      </c>
+      <c r="A29" s="31" t="n"/>
+      <c r="B29" s="31" t="n"/>
+      <c r="C29" s="31" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="31" t="inlineStr">
-        <is>
-          <t>10B</t>
-        </is>
-      </c>
-      <c r="B30" s="31" t="inlineStr">
-        <is>
-          <t>Samfunnsfag</t>
-        </is>
-      </c>
-      <c r="C30" s="31" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="D30" s="31" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
+      <c r="A30" s="31" t="n"/>
+      <c r="B30" s="31" t="n"/>
+      <c r="C30" s="31" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="31" t="inlineStr">
-        <is>
-          <t>10B</t>
-        </is>
-      </c>
-      <c r="B31" s="31" t="inlineStr">
-        <is>
-          <t>Tysk</t>
-        </is>
-      </c>
-      <c r="C31" s="31" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="D31" s="31" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
+      <c r="A31" s="31" t="n"/>
+      <c r="B31" s="31" t="n"/>
+      <c r="C31" s="31" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="31" t="inlineStr">
-        <is>
-          <t>10B</t>
-        </is>
-      </c>
-      <c r="B32" s="31" t="inlineStr">
-        <is>
-          <t>Valgfag</t>
-        </is>
-      </c>
-      <c r="C32" s="31" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="D32" s="31" t="inlineStr">
-        <is>
-          <t>MR</t>
-        </is>
-      </c>
+      <c r="A32" s="31" t="n"/>
+      <c r="B32" s="31" t="n"/>
+      <c r="C32" s="31" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="31" t="n"/>
       <c r="B33" s="31" t="n"/>
       <c r="C33" s="31" t="n"/>
-      <c r="D33" s="31" t="n"/>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="31" t="n"/>
       <c r="B34" s="31" t="n"/>
       <c r="C34" s="31" t="n"/>
-      <c r="D34" s="31" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="31" t="n"/>
       <c r="B35" s="31" t="n"/>
       <c r="C35" s="31" t="n"/>
-      <c r="D35" s="31" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="31" t="n"/>
       <c r="B36" s="31" t="n"/>
       <c r="C36" s="31" t="n"/>
-      <c r="D36" s="31" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="31" t="n"/>
       <c r="B37" s="31" t="n"/>
       <c r="C37" s="31" t="n"/>
-      <c r="D37" s="31" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="31" t="n"/>
       <c r="B38" s="31" t="n"/>
       <c r="C38" s="31" t="n"/>
-      <c r="D38" s="31" t="n"/>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="31" t="n"/>
       <c r="B39" s="31" t="n"/>
       <c r="C39" s="31" t="n"/>
-      <c r="D39" s="31" t="n"/>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="31" t="n"/>
       <c r="B40" s="31" t="n"/>
       <c r="C40" s="31" t="n"/>
-      <c r="D40" s="31" t="n"/>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="31" t="n"/>
       <c r="B41" s="31" t="n"/>
       <c r="C41" s="31" t="n"/>
-      <c r="D41" s="31" t="n"/>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="31" t="n"/>
       <c r="B42" s="31" t="n"/>
       <c r="C42" s="31" t="n"/>
-      <c r="D42" s="31" t="n"/>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="31" t="n"/>
       <c r="B43" s="31" t="n"/>
       <c r="C43" s="31" t="n"/>
-      <c r="D43" s="31" t="n"/>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="31" t="n"/>
       <c r="B44" s="31" t="n"/>
       <c r="C44" s="31" t="n"/>
-      <c r="D44" s="31" t="n"/>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="31" t="n"/>
       <c r="B45" s="31" t="n"/>
       <c r="C45" s="31" t="n"/>
-      <c r="D45" s="31" t="n"/>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="31" t="n"/>
       <c r="B46" s="31" t="n"/>
       <c r="C46" s="31" t="n"/>
-      <c r="D46" s="31" t="n"/>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="31" t="n"/>
       <c r="B47" s="31" t="n"/>
       <c r="C47" s="31" t="n"/>
-      <c r="D47" s="31" t="n"/>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="31" t="n"/>
       <c r="B48" s="31" t="n"/>
       <c r="C48" s="31" t="n"/>
-      <c r="D48" s="31" t="n"/>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="31" t="n"/>
       <c r="B49" s="31" t="n"/>
       <c r="C49" s="31" t="n"/>
-      <c r="D49" s="31" t="n"/>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="31" t="n"/>
       <c r="B50" s="31" t="n"/>
       <c r="C50" s="31" t="n"/>
-      <c r="D50" s="31" t="n"/>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="31" t="n"/>
       <c r="B51" s="31" t="n"/>
       <c r="C51" s="31" t="n"/>
-      <c r="D51" s="31" t="n"/>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="31" t="n"/>
       <c r="B52" s="31" t="n"/>
       <c r="C52" s="31" t="n"/>
-      <c r="D52" s="31" t="n"/>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="31" t="n"/>
       <c r="B53" s="31" t="n"/>
       <c r="C53" s="31" t="n"/>
-      <c r="D53" s="31" t="n"/>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="31" t="n"/>
       <c r="B54" s="31" t="n"/>
       <c r="C54" s="31" t="n"/>
-      <c r="D54" s="31" t="n"/>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="31" t="n"/>
       <c r="B55" s="31" t="n"/>
       <c r="C55" s="31" t="n"/>
-      <c r="D55" s="31" t="n"/>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="31" t="n"/>
       <c r="B56" s="31" t="n"/>
       <c r="C56" s="31" t="n"/>
-      <c r="D56" s="31" t="n"/>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="31" t="n"/>
       <c r="B57" s="31" t="n"/>
       <c r="C57" s="31" t="n"/>
-      <c r="D57" s="31" t="n"/>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="31" t="n"/>
       <c r="B58" s="31" t="n"/>
       <c r="C58" s="31" t="n"/>
-      <c r="D58" s="31" t="n"/>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="31" t="n"/>
       <c r="B59" s="31" t="n"/>
       <c r="C59" s="31" t="n"/>
-      <c r="D59" s="31" t="n"/>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="31" t="n"/>
       <c r="B60" s="31" t="n"/>
       <c r="C60" s="31" t="n"/>
-      <c r="D60" s="31" t="n"/>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="31" t="n"/>
       <c r="B61" s="31" t="n"/>
       <c r="C61" s="31" t="n"/>
-      <c r="D61" s="31" t="n"/>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="31" t="n"/>
       <c r="B62" s="31" t="n"/>
       <c r="C62" s="31" t="n"/>
-      <c r="D62" s="31" t="n"/>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="31" t="n"/>
       <c r="B63" s="31" t="n"/>
       <c r="C63" s="31" t="n"/>
-      <c r="D63" s="31" t="n"/>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="31" t="n"/>
       <c r="B64" s="31" t="n"/>
       <c r="C64" s="31" t="n"/>
-      <c r="D64" s="31" t="n"/>
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="31" t="n"/>
       <c r="B65" s="31" t="n"/>
       <c r="C65" s="31" t="n"/>
-      <c r="D65" s="31" t="n"/>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="31" t="n"/>
       <c r="B66" s="31" t="n"/>
       <c r="C66" s="31" t="n"/>
-      <c r="D66" s="31" t="n"/>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="31" t="n"/>
       <c r="B67" s="31" t="n"/>
       <c r="C67" s="31" t="n"/>
-      <c r="D67" s="31" t="n"/>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="31" t="n"/>
       <c r="B68" s="31" t="n"/>
       <c r="C68" s="31" t="n"/>
-      <c r="D68" s="31" t="n"/>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="31" t="n"/>
       <c r="B69" s="31" t="n"/>
       <c r="C69" s="31" t="n"/>
-      <c r="D69" s="31" t="n"/>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="31" t="n"/>
       <c r="B70" s="31" t="n"/>
       <c r="C70" s="31" t="n"/>
-      <c r="D70" s="31" t="n"/>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="31" t="n"/>
       <c r="B71" s="31" t="n"/>
       <c r="C71" s="31" t="n"/>
-      <c r="D71" s="31" t="n"/>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="31" t="n"/>
       <c r="B72" s="31" t="n"/>
       <c r="C72" s="31" t="n"/>
-      <c r="D72" s="31" t="n"/>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="31" t="n"/>
       <c r="B73" s="31" t="n"/>
       <c r="C73" s="31" t="n"/>
-      <c r="D73" s="31" t="n"/>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="31" t="n"/>
       <c r="B74" s="31" t="n"/>
       <c r="C74" s="31" t="n"/>
-      <c r="D74" s="31" t="n"/>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="31" t="n"/>
       <c r="B75" s="31" t="n"/>
       <c r="C75" s="31" t="n"/>
-      <c r="D75" s="31" t="n"/>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="31" t="n"/>
       <c r="B76" s="31" t="n"/>
       <c r="C76" s="31" t="n"/>
-      <c r="D76" s="31" t="n"/>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="31" t="n"/>
       <c r="B77" s="31" t="n"/>
       <c r="C77" s="31" t="n"/>
-      <c r="D77" s="31" t="n"/>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="31" t="n"/>
       <c r="B78" s="31" t="n"/>
       <c r="C78" s="31" t="n"/>
-      <c r="D78" s="31" t="n"/>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="31" t="n"/>
       <c r="B79" s="31" t="n"/>
       <c r="C79" s="31" t="n"/>
-      <c r="D79" s="31" t="n"/>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="31" t="n"/>
       <c r="B80" s="31" t="n"/>
       <c r="C80" s="31" t="n"/>
-      <c r="D80" s="31" t="n"/>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="31" t="n"/>
       <c r="B81" s="31" t="n"/>
       <c r="C81" s="31" t="n"/>
-      <c r="D81" s="31" t="n"/>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="31" t="n"/>
       <c r="B82" s="31" t="n"/>
       <c r="C82" s="31" t="n"/>
-      <c r="D82" s="31" t="n"/>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="31" t="n"/>
       <c r="B83" s="31" t="n"/>
       <c r="C83" s="31" t="n"/>
-      <c r="D83" s="31" t="n"/>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="31" t="n"/>
       <c r="B84" s="31" t="n"/>
       <c r="C84" s="31" t="n"/>
-      <c r="D84" s="31" t="n"/>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="31" t="n"/>
       <c r="B85" s="31" t="n"/>
       <c r="C85" s="31" t="n"/>
-      <c r="D85" s="31" t="n"/>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="31" t="n"/>
       <c r="B86" s="31" t="n"/>
       <c r="C86" s="31" t="n"/>
-      <c r="D86" s="31" t="n"/>
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="31" t="n"/>
       <c r="B87" s="31" t="n"/>
       <c r="C87" s="31" t="n"/>
-      <c r="D87" s="31" t="n"/>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="31" t="n"/>
       <c r="B88" s="31" t="n"/>
       <c r="C88" s="31" t="n"/>
-      <c r="D88" s="31" t="n"/>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="31" t="n"/>
       <c r="B89" s="31" t="n"/>
       <c r="C89" s="31" t="n"/>
-      <c r="D89" s="31" t="n"/>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="31" t="n"/>
       <c r="B90" s="31" t="n"/>
       <c r="C90" s="31" t="n"/>
-      <c r="D90" s="31" t="n"/>
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="A91" s="31" t="n"/>
       <c r="B91" s="31" t="n"/>
       <c r="C91" s="31" t="n"/>
-      <c r="D91" s="31" t="n"/>
     </row>
     <row r="92" ht="20" customHeight="1">
       <c r="A92" s="31" t="n"/>
       <c r="B92" s="31" t="n"/>
       <c r="C92" s="31" t="n"/>
-      <c r="D92" s="31" t="n"/>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="31" t="n"/>
       <c r="B93" s="31" t="n"/>
       <c r="C93" s="31" t="n"/>
-      <c r="D93" s="31" t="n"/>
     </row>
     <row r="94" ht="20" customHeight="1">
       <c r="A94" s="31" t="n"/>
       <c r="B94" s="31" t="n"/>
       <c r="C94" s="31" t="n"/>
-      <c r="D94" s="31" t="n"/>
     </row>
     <row r="95" ht="20" customHeight="1">
       <c r="A95" s="31" t="n"/>
       <c r="B95" s="31" t="n"/>
       <c r="C95" s="31" t="n"/>
-      <c r="D95" s="31" t="n"/>
     </row>
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="31" t="n"/>
       <c r="B96" s="31" t="n"/>
       <c r="C96" s="31" t="n"/>
-      <c r="D96" s="31" t="n"/>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="31" t="n"/>
       <c r="B97" s="31" t="n"/>
       <c r="C97" s="31" t="n"/>
-      <c r="D97" s="31" t="n"/>
     </row>
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="31" t="n"/>
       <c r="B98" s="31" t="n"/>
       <c r="C98" s="31" t="n"/>
-      <c r="D98" s="31" t="n"/>
     </row>
     <row r="99" ht="20" customHeight="1">
       <c r="A99" s="31" t="n"/>
       <c r="B99" s="31" t="n"/>
       <c r="C99" s="31" t="n"/>
-      <c r="D99" s="31" t="n"/>
     </row>
     <row r="100" ht="20" customHeight="1">
       <c r="A100" s="31" t="n"/>
       <c r="B100" s="31" t="n"/>
       <c r="C100" s="31" t="n"/>
-      <c r="D100" s="31" t="n"/>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="A101" s="31" t="n"/>
       <c r="B101" s="31" t="n"/>
       <c r="C101" s="31" t="n"/>
-      <c r="D101" s="31" t="n"/>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="31" t="n"/>
       <c r="B102" s="31" t="n"/>
       <c r="C102" s="31" t="n"/>
-      <c r="D102" s="31" t="n"/>
     </row>
     <row r="103" ht="20" customHeight="1">
       <c r="A103" s="31" t="n"/>
       <c r="B103" s="31" t="n"/>
       <c r="C103" s="31" t="n"/>
-      <c r="D103" s="31" t="n"/>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="31" t="n"/>
       <c r="B104" s="31" t="n"/>
       <c r="C104" s="31" t="n"/>
-      <c r="D104" s="31" t="n"/>
     </row>
     <row r="105" ht="20" customHeight="1">
       <c r="A105" s="31" t="n"/>
       <c r="B105" s="31" t="n"/>
       <c r="C105" s="31" t="n"/>
-      <c r="D105" s="31" t="n"/>
     </row>
     <row r="106" ht="20" customHeight="1">
       <c r="A106" s="31" t="n"/>
       <c r="B106" s="31" t="n"/>
       <c r="C106" s="31" t="n"/>
-      <c r="D106" s="31" t="n"/>
     </row>
     <row r="107" ht="20" customHeight="1">
       <c r="A107" s="31" t="n"/>
       <c r="B107" s="31" t="n"/>
       <c r="C107" s="31" t="n"/>
-      <c r="D107" s="31" t="n"/>
     </row>
     <row r="108" ht="20" customHeight="1">
       <c r="A108" s="31" t="n"/>
       <c r="B108" s="31" t="n"/>
       <c r="C108" s="31" t="n"/>
-      <c r="D108" s="31" t="n"/>
     </row>
     <row r="109" ht="20" customHeight="1">
       <c r="A109" s="31" t="n"/>
       <c r="B109" s="31" t="n"/>
       <c r="C109" s="31" t="n"/>
-      <c r="D109" s="31" t="n"/>
     </row>
     <row r="110" ht="20" customHeight="1">
       <c r="A110" s="31" t="n"/>
       <c r="B110" s="31" t="n"/>
       <c r="C110" s="31" t="n"/>
-      <c r="D110" s="31" t="n"/>
     </row>
     <row r="111" ht="20" customHeight="1">
       <c r="A111" s="31" t="n"/>
       <c r="B111" s="31" t="n"/>
       <c r="C111" s="31" t="n"/>
-      <c r="D111" s="31" t="n"/>
     </row>
     <row r="112" ht="20" customHeight="1">
       <c r="A112" s="31" t="n"/>
       <c r="B112" s="31" t="n"/>
       <c r="C112" s="31" t="n"/>
-      <c r="D112" s="31" t="n"/>
     </row>
     <row r="113" ht="20" customHeight="1">
       <c r="A113" s="31" t="n"/>
       <c r="B113" s="31" t="n"/>
       <c r="C113" s="31" t="n"/>
-      <c r="D113" s="31" t="n"/>
     </row>
     <row r="114" ht="20" customHeight="1">
       <c r="A114" s="31" t="n"/>
       <c r="B114" s="31" t="n"/>
       <c r="C114" s="31" t="n"/>
-      <c r="D114" s="31" t="n"/>
     </row>
     <row r="115" ht="20" customHeight="1">
       <c r="A115" s="31" t="n"/>
       <c r="B115" s="31" t="n"/>
       <c r="C115" s="31" t="n"/>
-      <c r="D115" s="31" t="n"/>
     </row>
     <row r="116" ht="20" customHeight="1">
       <c r="A116" s="31" t="n"/>
       <c r="B116" s="31" t="n"/>
       <c r="C116" s="31" t="n"/>
-      <c r="D116" s="31" t="n"/>
     </row>
     <row r="117" ht="20" customHeight="1">
       <c r="A117" s="31" t="n"/>
       <c r="B117" s="31" t="n"/>
       <c r="C117" s="31" t="n"/>
-      <c r="D117" s="31" t="n"/>
     </row>
     <row r="118" ht="20" customHeight="1">
       <c r="A118" s="31" t="n"/>
       <c r="B118" s="31" t="n"/>
       <c r="C118" s="31" t="n"/>
-      <c r="D118" s="31" t="n"/>
     </row>
     <row r="119" ht="20" customHeight="1">
       <c r="A119" s="31" t="n"/>
       <c r="B119" s="31" t="n"/>
       <c r="C119" s="31" t="n"/>
-      <c r="D119" s="31" t="n"/>
     </row>
     <row r="120" ht="20" customHeight="1">
       <c r="A120" s="31" t="n"/>
       <c r="B120" s="31" t="n"/>
       <c r="C120" s="31" t="n"/>
-      <c r="D120" s="31" t="n"/>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="31" t="n"/>
+      <c r="B121" s="31" t="n"/>
+      <c r="C121" s="31" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D120"/>
+  <autoFilter ref="A1:C120"/>
   <conditionalFormatting sqref="B2:B120">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>EXACT($B2,"Norsk")</formula>
@@ -4088,7 +3968,7 @@
       <formula>EXACT($B2,"Valgfag")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:D120">
+  <conditionalFormatting sqref="A2:C120">
     <cfRule type="expression" priority="13" dxfId="12">
       <formula>AND($A2&lt;&gt;"",ISODD(MATCH($A2,Klasser,0)))</formula>
     </cfRule>
@@ -4114,15 +3994,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H400"/>
+  <dimension ref="A1:H401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
@@ -4170,8 +4050,10 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="32" t="n">
-        <v>35</v>
+      <c r="A2" s="31" t="inlineStr">
+        <is>
+          <t>35 · 24.–28. aug 2026</t>
+        </is>
       </c>
       <c r="B2" s="31" t="inlineStr">
         <is>
@@ -4188,12 +4070,12 @@
           <t>Norsk</t>
         </is>
       </c>
-      <c r="E2" s="33" t="inlineStr">
+      <c r="E2" s="32" t="inlineStr">
         <is>
           <t>Oppstart: vi blir kjent med Kontekst</t>
         </is>
       </c>
-      <c r="F2" s="33" t="inlineStr">
+      <c r="F2" s="32" t="inlineStr">
         <is>
           <t>Bla gjennom kapittel 1</t>
         </is>
@@ -4206,8 +4088,10 @@
       <c r="H2" s="31" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="32" t="n">
-        <v>35</v>
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t>35 · 24.–28. aug 2026</t>
+        </is>
       </c>
       <c r="B3" s="31" t="inlineStr">
         <is>
@@ -4224,12 +4108,12 @@
           <t>Naturfag</t>
         </is>
       </c>
-      <c r="E3" s="33" t="inlineStr">
+      <c r="E3" s="32" t="inlineStr">
         <is>
           <t>Sikkerhet på naturfagrommet</t>
         </is>
       </c>
-      <c r="F3" s="33" t="n"/>
+      <c r="F3" s="32" t="n"/>
       <c r="G3" s="31" t="n"/>
       <c r="H3" s="31" t="inlineStr">
         <is>
@@ -4238,8 +4122,10 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="32" t="n">
-        <v>35</v>
+      <c r="A4" s="31" t="inlineStr">
+        <is>
+          <t>35 · 24.–28. aug 2026</t>
+        </is>
       </c>
       <c r="B4" s="31" t="inlineStr">
         <is>
@@ -4256,12 +4142,12 @@
           <t>Matematikk</t>
         </is>
       </c>
-      <c r="E4" s="33" t="inlineStr">
+      <c r="E4" s="32" t="inlineStr">
         <is>
           <t>Repetisjon: de fire regneartene</t>
         </is>
       </c>
-      <c r="F4" s="33" t="inlineStr">
+      <c r="F4" s="32" t="inlineStr">
         <is>
           <t>Oppgave 1.1–1.12</t>
         </is>
@@ -4274,8 +4160,10 @@
       <c r="H4" s="31" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="32" t="n">
-        <v>35</v>
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>35 · 24.–28. aug 2026</t>
+        </is>
       </c>
       <c r="B5" s="31" t="inlineStr">
         <is>
@@ -4292,12 +4180,12 @@
           <t>Matematikk</t>
         </is>
       </c>
-      <c r="E5" s="33" t="inlineStr">
+      <c r="E5" s="32" t="inlineStr">
         <is>
           <t>Repetisjon: de fire regneartene</t>
         </is>
       </c>
-      <c r="F5" s="33" t="inlineStr">
+      <c r="F5" s="32" t="inlineStr">
         <is>
           <t>Oppgave 1.1–1.12</t>
         </is>
@@ -4310,8 +4198,10 @@
       <c r="H5" s="31" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="32" t="n">
-        <v>35</v>
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>35 · 24.–28. aug 2026</t>
+        </is>
       </c>
       <c r="B6" s="31" t="inlineStr">
         <is>
@@ -4328,12 +4218,12 @@
           <t>Naturfag</t>
         </is>
       </c>
-      <c r="E6" s="33" t="inlineStr">
+      <c r="E6" s="32" t="inlineStr">
         <is>
           <t>Vi starter med elektrisitet</t>
         </is>
       </c>
-      <c r="F6" s="33" t="inlineStr">
+      <c r="F6" s="32" t="inlineStr">
         <is>
           <t>Les s. 60–66</t>
         </is>
@@ -4346,8 +4236,10 @@
       <c r="H6" s="31" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="32" t="n">
-        <v>35</v>
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>35 · 24.–28. aug 2026</t>
+        </is>
       </c>
       <c r="B7" s="31" t="inlineStr">
         <is>
@@ -4364,12 +4256,12 @@
           <t>Norsk</t>
         </is>
       </c>
-      <c r="E7" s="33" t="inlineStr">
+      <c r="E7" s="32" t="inlineStr">
         <is>
           <t>Skriveramme: argumenterende tekst</t>
         </is>
       </c>
-      <c r="F7" s="33" t="inlineStr">
+      <c r="F7" s="32" t="inlineStr">
         <is>
           <t>Velg tema til teksten</t>
         </is>
@@ -4382,8 +4274,10 @@
       <c r="H7" s="31" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="32" t="n">
-        <v>36</v>
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>36 · 31. aug – 4. sep 2026</t>
+        </is>
       </c>
       <c r="B8" s="31" t="inlineStr">
         <is>
@@ -4400,12 +4294,12 @@
           <t>Norsk</t>
         </is>
       </c>
-      <c r="E8" s="33" t="inlineStr">
+      <c r="E8" s="32" t="inlineStr">
         <is>
           <t>Nynorsk: samansette ord og orddeling</t>
         </is>
       </c>
-      <c r="F8" s="33" t="inlineStr">
+      <c r="F8" s="32" t="inlineStr">
         <is>
           <t>Les s. 40–44 i Kontekst. Skriv fem setningar med samansette ord.</t>
         </is>
@@ -4418,8 +4312,10 @@
       <c r="H8" s="31" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="32" t="n">
-        <v>36</v>
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>36 · 31. aug – 4. sep 2026</t>
+        </is>
       </c>
       <c r="B9" s="31" t="inlineStr">
         <is>
@@ -4436,12 +4332,12 @@
           <t>Matematikk</t>
         </is>
       </c>
-      <c r="E9" s="33" t="inlineStr">
+      <c r="E9" s="32" t="inlineStr">
         <is>
           <t>Brøk: utviding og forkorting</t>
         </is>
       </c>
-      <c r="F9" s="33" t="inlineStr">
+      <c r="F9" s="32" t="inlineStr">
         <is>
           <t>Oppgave 2.14–2.22</t>
         </is>
@@ -4454,8 +4350,10 @@
       <c r="H9" s="31" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="32" t="n">
-        <v>36</v>
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>36 · 31. aug – 4. sep 2026</t>
+        </is>
       </c>
       <c r="B10" s="31" t="inlineStr">
         <is>
@@ -4472,12 +4370,12 @@
           <t>Engelsk</t>
         </is>
       </c>
-      <c r="E10" s="33" t="inlineStr">
+      <c r="E10" s="32" t="inlineStr">
         <is>
           <t>Australia: reading and vocabulary</t>
         </is>
       </c>
-      <c r="F10" s="33" t="inlineStr">
+      <c r="F10" s="32" t="inlineStr">
         <is>
           <t>Glosetest torsdag – 20 ord fra kapittel 3</t>
         </is>
@@ -4494,8 +4392,10 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="32" t="n">
-        <v>36</v>
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>36 · 31. aug – 4. sep 2026</t>
+        </is>
       </c>
       <c r="B11" s="31" t="inlineStr">
         <is>
@@ -4512,12 +4412,12 @@
           <t>Naturfag</t>
         </is>
       </c>
-      <c r="E11" s="33" t="inlineStr">
+      <c r="E11" s="32" t="inlineStr">
         <is>
           <t>Cellen: bygning og deler</t>
         </is>
       </c>
-      <c r="F11" s="33" t="inlineStr">
+      <c r="F11" s="32" t="inlineStr">
         <is>
           <t>Tegn en dyrecelle med navn på delene</t>
         </is>
@@ -4530,8 +4430,10 @@
       <c r="H11" s="31" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="32" t="n">
-        <v>36</v>
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>36 · 31. aug – 4. sep 2026</t>
+        </is>
       </c>
       <c r="B12" s="31" t="inlineStr">
         <is>
@@ -4548,12 +4450,12 @@
           <t>Mat og helse</t>
         </is>
       </c>
-      <c r="E12" s="33" t="inlineStr">
+      <c r="E12" s="32" t="inlineStr">
         <is>
           <t>Vi baker grovbrød – husk forkle</t>
         </is>
       </c>
-      <c r="F12" s="33" t="n"/>
+      <c r="F12" s="32" t="n"/>
       <c r="G12" s="31" t="n"/>
       <c r="H12" s="31" t="inlineStr">
         <is>
@@ -4562,8 +4464,10 @@
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="32" t="n">
-        <v>36</v>
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>36 · 31. aug – 4. sep 2026</t>
+        </is>
       </c>
       <c r="B13" s="31" t="inlineStr">
         <is>
@@ -4580,18 +4484,20 @@
           <t>KRLE</t>
         </is>
       </c>
-      <c r="E13" s="33" t="inlineStr">
+      <c r="E13" s="32" t="inlineStr">
         <is>
           <t>Buddhismen: de fire edle sannheter</t>
         </is>
       </c>
-      <c r="F13" s="33" t="n"/>
+      <c r="F13" s="32" t="n"/>
       <c r="G13" s="31" t="n"/>
       <c r="H13" s="31" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="32" t="n">
-        <v>36</v>
+      <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t>36 · 31. aug – 4. sep 2026</t>
+        </is>
       </c>
       <c r="B14" s="31" t="inlineStr">
         <is>
@@ -4608,12 +4514,12 @@
           <t>Matematikk</t>
         </is>
       </c>
-      <c r="E14" s="33" t="inlineStr">
+      <c r="E14" s="32" t="inlineStr">
         <is>
           <t>Prøve i brøk og prosent</t>
         </is>
       </c>
-      <c r="F14" s="33" t="inlineStr">
+      <c r="F14" s="32" t="inlineStr">
         <is>
           <t>Øv på oppgavene fra kapittel 2</t>
         </is>
@@ -4630,8 +4536,10 @@
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="32" t="n">
-        <v>36</v>
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>36 · 31. aug – 4. sep 2026</t>
+        </is>
       </c>
       <c r="B15" s="31" t="inlineStr">
         <is>
@@ -4648,18 +4556,20 @@
           <t>Kunst og håndverk</t>
         </is>
       </c>
-      <c r="E15" s="33" t="inlineStr">
+      <c r="E15" s="32" t="inlineStr">
         <is>
           <t>Vi fortsetter med trearbeid</t>
         </is>
       </c>
-      <c r="F15" s="33" t="n"/>
+      <c r="F15" s="32" t="n"/>
       <c r="G15" s="31" t="n"/>
       <c r="H15" s="31" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="32" t="n">
-        <v>36</v>
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>36 · 31. aug – 4. sep 2026</t>
+        </is>
       </c>
       <c r="B16" s="31" t="inlineStr">
         <is>
@@ -4676,12 +4586,12 @@
           <t>Matematikk</t>
         </is>
       </c>
-      <c r="E16" s="33" t="inlineStr">
+      <c r="E16" s="32" t="inlineStr">
         <is>
           <t>Brøk: utviding og forkorting</t>
         </is>
       </c>
-      <c r="F16" s="33" t="inlineStr">
+      <c r="F16" s="32" t="inlineStr">
         <is>
           <t>Oppgave 2.14–2.22</t>
         </is>
@@ -4694,8 +4604,10 @@
       <c r="H16" s="31" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="32" t="n">
-        <v>36</v>
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>36 · 31. aug – 4. sep 2026</t>
+        </is>
       </c>
       <c r="B17" s="31" t="inlineStr">
         <is>
@@ -4712,12 +4624,12 @@
           <t>Kroppsøving</t>
         </is>
       </c>
-      <c r="E17" s="33" t="inlineStr">
+      <c r="E17" s="32" t="inlineStr">
         <is>
           <t>Friidrett ute – kle deg etter været</t>
         </is>
       </c>
-      <c r="F17" s="33" t="n"/>
+      <c r="F17" s="32" t="n"/>
       <c r="G17" s="31" t="n"/>
       <c r="H17" s="31" t="inlineStr">
         <is>
@@ -4726,8 +4638,10 @@
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="32" t="n">
-        <v>36</v>
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>36 · 31. aug – 4. sep 2026</t>
+        </is>
       </c>
       <c r="B18" s="31" t="inlineStr">
         <is>
@@ -4744,12 +4658,12 @@
           <t>Norsk</t>
         </is>
       </c>
-      <c r="E18" s="33" t="inlineStr">
+      <c r="E18" s="32" t="inlineStr">
         <is>
           <t>Nynorsk: samansette ord</t>
         </is>
       </c>
-      <c r="F18" s="33" t="inlineStr">
+      <c r="F18" s="32" t="inlineStr">
         <is>
           <t>Les s. 40–44 i Kontekst</t>
         </is>
@@ -4762,8 +4676,10 @@
       <c r="H18" s="31" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="32" t="n">
-        <v>36</v>
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>36 · 31. aug – 4. sep 2026</t>
+        </is>
       </c>
       <c r="B19" s="31" t="inlineStr">
         <is>
@@ -4780,12 +4696,12 @@
           <t>Samfunnsfag</t>
         </is>
       </c>
-      <c r="E19" s="33" t="inlineStr">
+      <c r="E19" s="32" t="inlineStr">
         <is>
           <t>Innleveringsfrist: kildekritikk</t>
         </is>
       </c>
-      <c r="F19" s="33" t="inlineStr">
+      <c r="F19" s="32" t="inlineStr">
         <is>
           <t>Lever oppgaven i Teams før kl. 15</t>
         </is>
@@ -4802,8 +4718,10 @@
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="32" t="n">
-        <v>36</v>
+      <c r="A20" s="31" t="inlineStr">
+        <is>
+          <t>36 · 31. aug – 4. sep 2026</t>
+        </is>
       </c>
       <c r="B20" s="31" t="inlineStr">
         <is>
@@ -4820,12 +4738,12 @@
           <t>Samfunnsfag</t>
         </is>
       </c>
-      <c r="E20" s="33" t="inlineStr">
+      <c r="E20" s="32" t="inlineStr">
         <is>
           <t>Den industrielle revolusjonen</t>
         </is>
       </c>
-      <c r="F20" s="33" t="inlineStr">
+      <c r="F20" s="32" t="inlineStr">
         <is>
           <t>Les s. 88–95 og svar på tre spørsmål</t>
         </is>
@@ -4838,8 +4756,10 @@
       <c r="H20" s="31" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="32" t="n">
-        <v>36</v>
+      <c r="A21" s="31" t="inlineStr">
+        <is>
+          <t>36 · 31. aug – 4. sep 2026</t>
+        </is>
       </c>
       <c r="B21" s="31" t="inlineStr">
         <is>
@@ -4856,12 +4776,12 @@
           <t>Naturfag</t>
         </is>
       </c>
-      <c r="E21" s="33" t="inlineStr">
+      <c r="E21" s="32" t="inlineStr">
         <is>
           <t>Forsøk: elektrisitet og kretser</t>
         </is>
       </c>
-      <c r="F21" s="33" t="inlineStr">
+      <c r="F21" s="32" t="inlineStr">
         <is>
           <t>Skriv rapport fra forsøket</t>
         </is>
@@ -4874,8 +4794,10 @@
       <c r="H21" s="31" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="32" t="n">
-        <v>36</v>
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>36 · 31. aug – 4. sep 2026</t>
+        </is>
       </c>
       <c r="B22" s="31" t="inlineStr">
         <is>
@@ -4892,12 +4814,12 @@
           <t>Kunst og håndverk</t>
         </is>
       </c>
-      <c r="E22" s="33" t="inlineStr">
+      <c r="E22" s="32" t="inlineStr">
         <is>
           <t>Ekskursjon til kunstmuseet – vi går kl. 12.00</t>
         </is>
       </c>
-      <c r="F22" s="33" t="inlineStr">
+      <c r="F22" s="32" t="inlineStr">
         <is>
           <t>Ta med matpakke</t>
         </is>
@@ -4914,8 +4836,10 @@
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="32" t="n">
-        <v>36</v>
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>36 · 31. aug – 4. sep 2026</t>
+        </is>
       </c>
       <c r="B23" s="31" t="inlineStr">
         <is>
@@ -4932,12 +4856,12 @@
           <t>Norsk</t>
         </is>
       </c>
-      <c r="E23" s="33" t="inlineStr">
+      <c r="E23" s="32" t="inlineStr">
         <is>
           <t>Novelleanalyse: virkemidler</t>
         </is>
       </c>
-      <c r="F23" s="33" t="inlineStr">
+      <c r="F23" s="32" t="inlineStr">
         <is>
           <t>Les novellen «Karen» og noter virkemidler</t>
         </is>
@@ -4950,8 +4874,10 @@
       <c r="H23" s="31" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="32" t="n">
-        <v>36</v>
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>36 · 31. aug – 4. sep 2026</t>
+        </is>
       </c>
       <c r="B24" s="31" t="inlineStr">
         <is>
@@ -4968,12 +4894,12 @@
           <t>Matematikk</t>
         </is>
       </c>
-      <c r="E24" s="33" t="inlineStr">
+      <c r="E24" s="32" t="inlineStr">
         <is>
           <t>Funksjoner: lineære sammenhenger</t>
         </is>
       </c>
-      <c r="F24" s="33" t="inlineStr">
+      <c r="F24" s="32" t="inlineStr">
         <is>
           <t>Oppgave 5.30–5.40</t>
         </is>
@@ -4986,8 +4912,10 @@
       <c r="H24" s="31" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="32" t="n">
-        <v>36</v>
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>36 · 31. aug – 4. sep 2026</t>
+        </is>
       </c>
       <c r="B25" s="31" t="inlineStr">
         <is>
@@ -5004,12 +4932,12 @@
           <t>Norsk</t>
         </is>
       </c>
-      <c r="E25" s="33" t="inlineStr">
+      <c r="E25" s="32" t="inlineStr">
         <is>
           <t>Skriveøkt: argumenterende tekst</t>
         </is>
       </c>
-      <c r="F25" s="33" t="inlineStr">
+      <c r="F25" s="32" t="inlineStr">
         <is>
           <t>Førsteutkast leveres i Teams</t>
         </is>
@@ -5026,8 +4954,10 @@
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="32" t="n">
-        <v>36</v>
+      <c r="A26" s="31" t="inlineStr">
+        <is>
+          <t>36 · 31. aug – 4. sep 2026</t>
+        </is>
       </c>
       <c r="B26" s="31" t="inlineStr">
         <is>
@@ -5044,12 +4974,12 @@
           <t>Engelsk</t>
         </is>
       </c>
-      <c r="E26" s="33" t="inlineStr">
+      <c r="E26" s="32" t="inlineStr">
         <is>
           <t>Oral presentations: prepare in pairs</t>
         </is>
       </c>
-      <c r="F26" s="33" t="inlineStr">
+      <c r="F26" s="32" t="inlineStr">
         <is>
           <t>Øv på framføringen hjemme</t>
         </is>
@@ -5062,8 +4992,10 @@
       <c r="H26" s="31" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="32" t="n">
-        <v>36</v>
+      <c r="A27" s="31" t="inlineStr">
+        <is>
+          <t>36 · 31. aug – 4. sep 2026</t>
+        </is>
       </c>
       <c r="B27" s="31" t="inlineStr">
         <is>
@@ -5080,18 +5012,20 @@
           <t>Naturfag</t>
         </is>
       </c>
-      <c r="E27" s="33" t="inlineStr">
+      <c r="E27" s="32" t="inlineStr">
         <is>
           <t>Repetisjon før tentamen</t>
         </is>
       </c>
-      <c r="F27" s="33" t="n"/>
+      <c r="F27" s="32" t="n"/>
       <c r="G27" s="31" t="n"/>
       <c r="H27" s="31" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="32" t="n">
-        <v>36</v>
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>36 · 31. aug – 4. sep 2026</t>
+        </is>
       </c>
       <c r="B28" s="31" t="inlineStr">
         <is>
@@ -5108,8 +5042,8 @@
           <t>Valgfag</t>
         </is>
       </c>
-      <c r="E28" s="33" t="n"/>
-      <c r="F28" s="33" t="inlineStr">
+      <c r="E28" s="32" t="n"/>
+      <c r="F28" s="32" t="inlineStr">
         <is>
           <t>Frist for å melde seg på turneringen</t>
         </is>
@@ -5126,8 +5060,10 @@
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="32" t="n">
-        <v>37</v>
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>37 · 7.–11. sep 2026</t>
+        </is>
       </c>
       <c r="B29" s="31" t="inlineStr">
         <is>
@@ -5144,12 +5080,12 @@
           <t>Norsk</t>
         </is>
       </c>
-      <c r="E29" s="33" t="inlineStr">
+      <c r="E29" s="32" t="inlineStr">
         <is>
           <t>Vi skriver forteljing</t>
         </is>
       </c>
-      <c r="F29" s="33" t="inlineStr">
+      <c r="F29" s="32" t="inlineStr">
         <is>
           <t>Skriv ferdig utkastet</t>
         </is>
@@ -5162,8 +5098,10 @@
       <c r="H29" s="31" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="32" t="n">
-        <v>37</v>
+      <c r="A30" s="31" t="inlineStr">
+        <is>
+          <t>37 · 7.–11. sep 2026</t>
+        </is>
       </c>
       <c r="B30" s="31" t="inlineStr">
         <is>
@@ -5180,12 +5118,12 @@
           <t>Samfunnsfag</t>
         </is>
       </c>
-      <c r="E30" s="33" t="inlineStr">
+      <c r="E30" s="32" t="inlineStr">
         <is>
           <t>Demokrati: hvem bestemmer i Norge?</t>
         </is>
       </c>
-      <c r="F30" s="33" t="inlineStr">
+      <c r="F30" s="32" t="inlineStr">
         <is>
           <t>Les s. 22–29</t>
         </is>
@@ -5198,8 +5136,10 @@
       <c r="H30" s="31" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="32" t="n">
-        <v>37</v>
+      <c r="A31" s="31" t="inlineStr">
+        <is>
+          <t>37 · 7.–11. sep 2026</t>
+        </is>
       </c>
       <c r="B31" s="31" t="inlineStr">
         <is>
@@ -5216,12 +5156,12 @@
           <t>Musikk</t>
         </is>
       </c>
-      <c r="E31" s="33" t="inlineStr">
+      <c r="E31" s="32" t="inlineStr">
         <is>
           <t>Vi øver til høstkonserten</t>
         </is>
       </c>
-      <c r="F31" s="33" t="n"/>
+      <c r="F31" s="32" t="n"/>
       <c r="G31" s="31" t="n"/>
       <c r="H31" s="31" t="inlineStr">
         <is>
@@ -5230,8 +5170,10 @@
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="32" t="n">
-        <v>37</v>
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>37 · 7.–11. sep 2026</t>
+        </is>
       </c>
       <c r="B32" s="31" t="inlineStr">
         <is>
@@ -5248,12 +5190,12 @@
           <t>Engelsk</t>
         </is>
       </c>
-      <c r="E32" s="33" t="inlineStr">
+      <c r="E32" s="32" t="inlineStr">
         <is>
           <t>Presentations: my hometown</t>
         </is>
       </c>
-      <c r="F32" s="33" t="inlineStr">
+      <c r="F32" s="32" t="inlineStr">
         <is>
           <t>Framføring torsdag</t>
         </is>
@@ -5270,8 +5212,10 @@
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="32" t="n">
-        <v>37</v>
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>37 · 7.–11. sep 2026</t>
+        </is>
       </c>
       <c r="B33" s="31" t="inlineStr">
         <is>
@@ -5288,12 +5232,12 @@
           <t>Matematikk</t>
         </is>
       </c>
-      <c r="E33" s="33" t="inlineStr">
+      <c r="E33" s="32" t="inlineStr">
         <is>
           <t>Prøve i likninger</t>
         </is>
       </c>
-      <c r="F33" s="33" t="inlineStr">
+      <c r="F33" s="32" t="inlineStr">
         <is>
           <t>Øv på kapittel 3</t>
         </is>
@@ -5310,8 +5254,10 @@
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="32" t="n">
-        <v>37</v>
+      <c r="A34" s="31" t="inlineStr">
+        <is>
+          <t>37 · 7.–11. sep 2026</t>
+        </is>
       </c>
       <c r="B34" s="31" t="inlineStr">
         <is>
@@ -5328,12 +5274,12 @@
           <t>Matematikk</t>
         </is>
       </c>
-      <c r="E34" s="33" t="inlineStr">
+      <c r="E34" s="32" t="inlineStr">
         <is>
           <t>Tentamen – hele dagen</t>
         </is>
       </c>
-      <c r="F34" s="33" t="inlineStr">
+      <c r="F34" s="32" t="inlineStr">
         <is>
           <t>Ta med kalkulator og linjal</t>
         </is>
@@ -5350,8 +5296,10 @@
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="32" t="n">
-        <v>37</v>
+      <c r="A35" s="31" t="inlineStr">
+        <is>
+          <t>37 · 7.–11. sep 2026</t>
+        </is>
       </c>
       <c r="B35" s="31" t="inlineStr">
         <is>
@@ -5364,8 +5312,8 @@
         </is>
       </c>
       <c r="D35" s="31" t="n"/>
-      <c r="E35" s="33" t="n"/>
-      <c r="F35" s="33" t="inlineStr">
+      <c r="E35" s="32" t="n"/>
+      <c r="F35" s="32" t="inlineStr">
         <is>
           <t>Skolen slutter kl. 12.00 – planleggingsdag</t>
         </is>
@@ -5382,3658 +5330,3668 @@
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="32" t="n"/>
+      <c r="A36" s="31" t="n"/>
       <c r="B36" s="31" t="n"/>
       <c r="C36" s="31" t="n"/>
       <c r="D36" s="31" t="n"/>
-      <c r="E36" s="33" t="n"/>
-      <c r="F36" s="33" t="n"/>
+      <c r="E36" s="32" t="n"/>
+      <c r="F36" s="32" t="n"/>
       <c r="G36" s="31" t="n"/>
       <c r="H36" s="31" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="32" t="n"/>
+      <c r="A37" s="31" t="n"/>
       <c r="B37" s="31" t="n"/>
       <c r="C37" s="31" t="n"/>
       <c r="D37" s="31" t="n"/>
-      <c r="E37" s="33" t="n"/>
-      <c r="F37" s="33" t="n"/>
+      <c r="E37" s="32" t="n"/>
+      <c r="F37" s="32" t="n"/>
       <c r="G37" s="31" t="n"/>
       <c r="H37" s="31" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="32" t="n"/>
+      <c r="A38" s="31" t="n"/>
       <c r="B38" s="31" t="n"/>
       <c r="C38" s="31" t="n"/>
       <c r="D38" s="31" t="n"/>
-      <c r="E38" s="33" t="n"/>
-      <c r="F38" s="33" t="n"/>
+      <c r="E38" s="32" t="n"/>
+      <c r="F38" s="32" t="n"/>
       <c r="G38" s="31" t="n"/>
       <c r="H38" s="31" t="n"/>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="32" t="n"/>
+      <c r="A39" s="31" t="n"/>
       <c r="B39" s="31" t="n"/>
       <c r="C39" s="31" t="n"/>
       <c r="D39" s="31" t="n"/>
-      <c r="E39" s="33" t="n"/>
-      <c r="F39" s="33" t="n"/>
+      <c r="E39" s="32" t="n"/>
+      <c r="F39" s="32" t="n"/>
       <c r="G39" s="31" t="n"/>
       <c r="H39" s="31" t="n"/>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="32" t="n"/>
+      <c r="A40" s="31" t="n"/>
       <c r="B40" s="31" t="n"/>
       <c r="C40" s="31" t="n"/>
       <c r="D40" s="31" t="n"/>
-      <c r="E40" s="33" t="n"/>
-      <c r="F40" s="33" t="n"/>
+      <c r="E40" s="32" t="n"/>
+      <c r="F40" s="32" t="n"/>
       <c r="G40" s="31" t="n"/>
       <c r="H40" s="31" t="n"/>
     </row>
     <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="32" t="n"/>
+      <c r="A41" s="31" t="n"/>
       <c r="B41" s="31" t="n"/>
       <c r="C41" s="31" t="n"/>
       <c r="D41" s="31" t="n"/>
-      <c r="E41" s="33" t="n"/>
-      <c r="F41" s="33" t="n"/>
+      <c r="E41" s="32" t="n"/>
+      <c r="F41" s="32" t="n"/>
       <c r="G41" s="31" t="n"/>
       <c r="H41" s="31" t="n"/>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="32" t="n"/>
+      <c r="A42" s="31" t="n"/>
       <c r="B42" s="31" t="n"/>
       <c r="C42" s="31" t="n"/>
       <c r="D42" s="31" t="n"/>
-      <c r="E42" s="33" t="n"/>
-      <c r="F42" s="33" t="n"/>
+      <c r="E42" s="32" t="n"/>
+      <c r="F42" s="32" t="n"/>
       <c r="G42" s="31" t="n"/>
       <c r="H42" s="31" t="n"/>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="32" t="n"/>
+      <c r="A43" s="31" t="n"/>
       <c r="B43" s="31" t="n"/>
       <c r="C43" s="31" t="n"/>
       <c r="D43" s="31" t="n"/>
-      <c r="E43" s="33" t="n"/>
-      <c r="F43" s="33" t="n"/>
+      <c r="E43" s="32" t="n"/>
+      <c r="F43" s="32" t="n"/>
       <c r="G43" s="31" t="n"/>
       <c r="H43" s="31" t="n"/>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="32" t="n"/>
+      <c r="A44" s="31" t="n"/>
       <c r="B44" s="31" t="n"/>
       <c r="C44" s="31" t="n"/>
       <c r="D44" s="31" t="n"/>
-      <c r="E44" s="33" t="n"/>
-      <c r="F44" s="33" t="n"/>
+      <c r="E44" s="32" t="n"/>
+      <c r="F44" s="32" t="n"/>
       <c r="G44" s="31" t="n"/>
       <c r="H44" s="31" t="n"/>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="32" t="n"/>
+      <c r="A45" s="31" t="n"/>
       <c r="B45" s="31" t="n"/>
       <c r="C45" s="31" t="n"/>
       <c r="D45" s="31" t="n"/>
-      <c r="E45" s="33" t="n"/>
-      <c r="F45" s="33" t="n"/>
+      <c r="E45" s="32" t="n"/>
+      <c r="F45" s="32" t="n"/>
       <c r="G45" s="31" t="n"/>
       <c r="H45" s="31" t="n"/>
     </row>
     <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="32" t="n"/>
+      <c r="A46" s="31" t="n"/>
       <c r="B46" s="31" t="n"/>
       <c r="C46" s="31" t="n"/>
       <c r="D46" s="31" t="n"/>
-      <c r="E46" s="33" t="n"/>
-      <c r="F46" s="33" t="n"/>
+      <c r="E46" s="32" t="n"/>
+      <c r="F46" s="32" t="n"/>
       <c r="G46" s="31" t="n"/>
       <c r="H46" s="31" t="n"/>
     </row>
     <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="32" t="n"/>
+      <c r="A47" s="31" t="n"/>
       <c r="B47" s="31" t="n"/>
       <c r="C47" s="31" t="n"/>
       <c r="D47" s="31" t="n"/>
-      <c r="E47" s="33" t="n"/>
-      <c r="F47" s="33" t="n"/>
+      <c r="E47" s="32" t="n"/>
+      <c r="F47" s="32" t="n"/>
       <c r="G47" s="31" t="n"/>
       <c r="H47" s="31" t="n"/>
     </row>
     <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="32" t="n"/>
+      <c r="A48" s="31" t="n"/>
       <c r="B48" s="31" t="n"/>
       <c r="C48" s="31" t="n"/>
       <c r="D48" s="31" t="n"/>
-      <c r="E48" s="33" t="n"/>
-      <c r="F48" s="33" t="n"/>
+      <c r="E48" s="32" t="n"/>
+      <c r="F48" s="32" t="n"/>
       <c r="G48" s="31" t="n"/>
       <c r="H48" s="31" t="n"/>
     </row>
     <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="32" t="n"/>
+      <c r="A49" s="31" t="n"/>
       <c r="B49" s="31" t="n"/>
       <c r="C49" s="31" t="n"/>
       <c r="D49" s="31" t="n"/>
-      <c r="E49" s="33" t="n"/>
-      <c r="F49" s="33" t="n"/>
+      <c r="E49" s="32" t="n"/>
+      <c r="F49" s="32" t="n"/>
       <c r="G49" s="31" t="n"/>
       <c r="H49" s="31" t="n"/>
     </row>
     <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="32" t="n"/>
+      <c r="A50" s="31" t="n"/>
       <c r="B50" s="31" t="n"/>
       <c r="C50" s="31" t="n"/>
       <c r="D50" s="31" t="n"/>
-      <c r="E50" s="33" t="n"/>
-      <c r="F50" s="33" t="n"/>
+      <c r="E50" s="32" t="n"/>
+      <c r="F50" s="32" t="n"/>
       <c r="G50" s="31" t="n"/>
       <c r="H50" s="31" t="n"/>
     </row>
     <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="32" t="n"/>
+      <c r="A51" s="31" t="n"/>
       <c r="B51" s="31" t="n"/>
       <c r="C51" s="31" t="n"/>
       <c r="D51" s="31" t="n"/>
-      <c r="E51" s="33" t="n"/>
-      <c r="F51" s="33" t="n"/>
+      <c r="E51" s="32" t="n"/>
+      <c r="F51" s="32" t="n"/>
       <c r="G51" s="31" t="n"/>
       <c r="H51" s="31" t="n"/>
     </row>
     <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="32" t="n"/>
+      <c r="A52" s="31" t="n"/>
       <c r="B52" s="31" t="n"/>
       <c r="C52" s="31" t="n"/>
       <c r="D52" s="31" t="n"/>
-      <c r="E52" s="33" t="n"/>
-      <c r="F52" s="33" t="n"/>
+      <c r="E52" s="32" t="n"/>
+      <c r="F52" s="32" t="n"/>
       <c r="G52" s="31" t="n"/>
       <c r="H52" s="31" t="n"/>
     </row>
     <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="32" t="n"/>
+      <c r="A53" s="31" t="n"/>
       <c r="B53" s="31" t="n"/>
       <c r="C53" s="31" t="n"/>
       <c r="D53" s="31" t="n"/>
-      <c r="E53" s="33" t="n"/>
-      <c r="F53" s="33" t="n"/>
+      <c r="E53" s="32" t="n"/>
+      <c r="F53" s="32" t="n"/>
       <c r="G53" s="31" t="n"/>
       <c r="H53" s="31" t="n"/>
     </row>
     <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="32" t="n"/>
+      <c r="A54" s="31" t="n"/>
       <c r="B54" s="31" t="n"/>
       <c r="C54" s="31" t="n"/>
       <c r="D54" s="31" t="n"/>
-      <c r="E54" s="33" t="n"/>
-      <c r="F54" s="33" t="n"/>
+      <c r="E54" s="32" t="n"/>
+      <c r="F54" s="32" t="n"/>
       <c r="G54" s="31" t="n"/>
       <c r="H54" s="31" t="n"/>
     </row>
     <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="32" t="n"/>
+      <c r="A55" s="31" t="n"/>
       <c r="B55" s="31" t="n"/>
       <c r="C55" s="31" t="n"/>
       <c r="D55" s="31" t="n"/>
-      <c r="E55" s="33" t="n"/>
-      <c r="F55" s="33" t="n"/>
+      <c r="E55" s="32" t="n"/>
+      <c r="F55" s="32" t="n"/>
       <c r="G55" s="31" t="n"/>
       <c r="H55" s="31" t="n"/>
     </row>
     <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="32" t="n"/>
+      <c r="A56" s="31" t="n"/>
       <c r="B56" s="31" t="n"/>
       <c r="C56" s="31" t="n"/>
       <c r="D56" s="31" t="n"/>
-      <c r="E56" s="33" t="n"/>
-      <c r="F56" s="33" t="n"/>
+      <c r="E56" s="32" t="n"/>
+      <c r="F56" s="32" t="n"/>
       <c r="G56" s="31" t="n"/>
       <c r="H56" s="31" t="n"/>
     </row>
     <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="32" t="n"/>
+      <c r="A57" s="31" t="n"/>
       <c r="B57" s="31" t="n"/>
       <c r="C57" s="31" t="n"/>
       <c r="D57" s="31" t="n"/>
-      <c r="E57" s="33" t="n"/>
-      <c r="F57" s="33" t="n"/>
+      <c r="E57" s="32" t="n"/>
+      <c r="F57" s="32" t="n"/>
       <c r="G57" s="31" t="n"/>
       <c r="H57" s="31" t="n"/>
     </row>
     <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="32" t="n"/>
+      <c r="A58" s="31" t="n"/>
       <c r="B58" s="31" t="n"/>
       <c r="C58" s="31" t="n"/>
       <c r="D58" s="31" t="n"/>
-      <c r="E58" s="33" t="n"/>
-      <c r="F58" s="33" t="n"/>
+      <c r="E58" s="32" t="n"/>
+      <c r="F58" s="32" t="n"/>
       <c r="G58" s="31" t="n"/>
       <c r="H58" s="31" t="n"/>
     </row>
     <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="32" t="n"/>
+      <c r="A59" s="31" t="n"/>
       <c r="B59" s="31" t="n"/>
       <c r="C59" s="31" t="n"/>
       <c r="D59" s="31" t="n"/>
-      <c r="E59" s="33" t="n"/>
-      <c r="F59" s="33" t="n"/>
+      <c r="E59" s="32" t="n"/>
+      <c r="F59" s="32" t="n"/>
       <c r="G59" s="31" t="n"/>
       <c r="H59" s="31" t="n"/>
     </row>
     <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="32" t="n"/>
+      <c r="A60" s="31" t="n"/>
       <c r="B60" s="31" t="n"/>
       <c r="C60" s="31" t="n"/>
       <c r="D60" s="31" t="n"/>
-      <c r="E60" s="33" t="n"/>
-      <c r="F60" s="33" t="n"/>
+      <c r="E60" s="32" t="n"/>
+      <c r="F60" s="32" t="n"/>
       <c r="G60" s="31" t="n"/>
       <c r="H60" s="31" t="n"/>
     </row>
     <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="32" t="n"/>
+      <c r="A61" s="31" t="n"/>
       <c r="B61" s="31" t="n"/>
       <c r="C61" s="31" t="n"/>
       <c r="D61" s="31" t="n"/>
-      <c r="E61" s="33" t="n"/>
-      <c r="F61" s="33" t="n"/>
+      <c r="E61" s="32" t="n"/>
+      <c r="F61" s="32" t="n"/>
       <c r="G61" s="31" t="n"/>
       <c r="H61" s="31" t="n"/>
     </row>
     <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="32" t="n"/>
+      <c r="A62" s="31" t="n"/>
       <c r="B62" s="31" t="n"/>
       <c r="C62" s="31" t="n"/>
       <c r="D62" s="31" t="n"/>
-      <c r="E62" s="33" t="n"/>
-      <c r="F62" s="33" t="n"/>
+      <c r="E62" s="32" t="n"/>
+      <c r="F62" s="32" t="n"/>
       <c r="G62" s="31" t="n"/>
       <c r="H62" s="31" t="n"/>
     </row>
     <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="32" t="n"/>
+      <c r="A63" s="31" t="n"/>
       <c r="B63" s="31" t="n"/>
       <c r="C63" s="31" t="n"/>
       <c r="D63" s="31" t="n"/>
-      <c r="E63" s="33" t="n"/>
-      <c r="F63" s="33" t="n"/>
+      <c r="E63" s="32" t="n"/>
+      <c r="F63" s="32" t="n"/>
       <c r="G63" s="31" t="n"/>
       <c r="H63" s="31" t="n"/>
     </row>
     <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="32" t="n"/>
+      <c r="A64" s="31" t="n"/>
       <c r="B64" s="31" t="n"/>
       <c r="C64" s="31" t="n"/>
       <c r="D64" s="31" t="n"/>
-      <c r="E64" s="33" t="n"/>
-      <c r="F64" s="33" t="n"/>
+      <c r="E64" s="32" t="n"/>
+      <c r="F64" s="32" t="n"/>
       <c r="G64" s="31" t="n"/>
       <c r="H64" s="31" t="n"/>
     </row>
     <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="32" t="n"/>
+      <c r="A65" s="31" t="n"/>
       <c r="B65" s="31" t="n"/>
       <c r="C65" s="31" t="n"/>
       <c r="D65" s="31" t="n"/>
-      <c r="E65" s="33" t="n"/>
-      <c r="F65" s="33" t="n"/>
+      <c r="E65" s="32" t="n"/>
+      <c r="F65" s="32" t="n"/>
       <c r="G65" s="31" t="n"/>
       <c r="H65" s="31" t="n"/>
     </row>
     <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="32" t="n"/>
+      <c r="A66" s="31" t="n"/>
       <c r="B66" s="31" t="n"/>
       <c r="C66" s="31" t="n"/>
       <c r="D66" s="31" t="n"/>
-      <c r="E66" s="33" t="n"/>
-      <c r="F66" s="33" t="n"/>
+      <c r="E66" s="32" t="n"/>
+      <c r="F66" s="32" t="n"/>
       <c r="G66" s="31" t="n"/>
       <c r="H66" s="31" t="n"/>
     </row>
     <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="32" t="n"/>
+      <c r="A67" s="31" t="n"/>
       <c r="B67" s="31" t="n"/>
       <c r="C67" s="31" t="n"/>
       <c r="D67" s="31" t="n"/>
-      <c r="E67" s="33" t="n"/>
-      <c r="F67" s="33" t="n"/>
+      <c r="E67" s="32" t="n"/>
+      <c r="F67" s="32" t="n"/>
       <c r="G67" s="31" t="n"/>
       <c r="H67" s="31" t="n"/>
     </row>
     <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="32" t="n"/>
+      <c r="A68" s="31" t="n"/>
       <c r="B68" s="31" t="n"/>
       <c r="C68" s="31" t="n"/>
       <c r="D68" s="31" t="n"/>
-      <c r="E68" s="33" t="n"/>
-      <c r="F68" s="33" t="n"/>
+      <c r="E68" s="32" t="n"/>
+      <c r="F68" s="32" t="n"/>
       <c r="G68" s="31" t="n"/>
       <c r="H68" s="31" t="n"/>
     </row>
     <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="32" t="n"/>
+      <c r="A69" s="31" t="n"/>
       <c r="B69" s="31" t="n"/>
       <c r="C69" s="31" t="n"/>
       <c r="D69" s="31" t="n"/>
-      <c r="E69" s="33" t="n"/>
-      <c r="F69" s="33" t="n"/>
+      <c r="E69" s="32" t="n"/>
+      <c r="F69" s="32" t="n"/>
       <c r="G69" s="31" t="n"/>
       <c r="H69" s="31" t="n"/>
     </row>
     <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="32" t="n"/>
+      <c r="A70" s="31" t="n"/>
       <c r="B70" s="31" t="n"/>
       <c r="C70" s="31" t="n"/>
       <c r="D70" s="31" t="n"/>
-      <c r="E70" s="33" t="n"/>
-      <c r="F70" s="33" t="n"/>
+      <c r="E70" s="32" t="n"/>
+      <c r="F70" s="32" t="n"/>
       <c r="G70" s="31" t="n"/>
       <c r="H70" s="31" t="n"/>
     </row>
     <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="32" t="n"/>
+      <c r="A71" s="31" t="n"/>
       <c r="B71" s="31" t="n"/>
       <c r="C71" s="31" t="n"/>
       <c r="D71" s="31" t="n"/>
-      <c r="E71" s="33" t="n"/>
-      <c r="F71" s="33" t="n"/>
+      <c r="E71" s="32" t="n"/>
+      <c r="F71" s="32" t="n"/>
       <c r="G71" s="31" t="n"/>
       <c r="H71" s="31" t="n"/>
     </row>
     <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="32" t="n"/>
+      <c r="A72" s="31" t="n"/>
       <c r="B72" s="31" t="n"/>
       <c r="C72" s="31" t="n"/>
       <c r="D72" s="31" t="n"/>
-      <c r="E72" s="33" t="n"/>
-      <c r="F72" s="33" t="n"/>
+      <c r="E72" s="32" t="n"/>
+      <c r="F72" s="32" t="n"/>
       <c r="G72" s="31" t="n"/>
       <c r="H72" s="31" t="n"/>
     </row>
     <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="32" t="n"/>
+      <c r="A73" s="31" t="n"/>
       <c r="B73" s="31" t="n"/>
       <c r="C73" s="31" t="n"/>
       <c r="D73" s="31" t="n"/>
-      <c r="E73" s="33" t="n"/>
-      <c r="F73" s="33" t="n"/>
+      <c r="E73" s="32" t="n"/>
+      <c r="F73" s="32" t="n"/>
       <c r="G73" s="31" t="n"/>
       <c r="H73" s="31" t="n"/>
     </row>
     <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="32" t="n"/>
+      <c r="A74" s="31" t="n"/>
       <c r="B74" s="31" t="n"/>
       <c r="C74" s="31" t="n"/>
       <c r="D74" s="31" t="n"/>
-      <c r="E74" s="33" t="n"/>
-      <c r="F74" s="33" t="n"/>
+      <c r="E74" s="32" t="n"/>
+      <c r="F74" s="32" t="n"/>
       <c r="G74" s="31" t="n"/>
       <c r="H74" s="31" t="n"/>
     </row>
     <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="32" t="n"/>
+      <c r="A75" s="31" t="n"/>
       <c r="B75" s="31" t="n"/>
       <c r="C75" s="31" t="n"/>
       <c r="D75" s="31" t="n"/>
-      <c r="E75" s="33" t="n"/>
-      <c r="F75" s="33" t="n"/>
+      <c r="E75" s="32" t="n"/>
+      <c r="F75" s="32" t="n"/>
       <c r="G75" s="31" t="n"/>
       <c r="H75" s="31" t="n"/>
     </row>
     <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="32" t="n"/>
+      <c r="A76" s="31" t="n"/>
       <c r="B76" s="31" t="n"/>
       <c r="C76" s="31" t="n"/>
       <c r="D76" s="31" t="n"/>
-      <c r="E76" s="33" t="n"/>
-      <c r="F76" s="33" t="n"/>
+      <c r="E76" s="32" t="n"/>
+      <c r="F76" s="32" t="n"/>
       <c r="G76" s="31" t="n"/>
       <c r="H76" s="31" t="n"/>
     </row>
     <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="32" t="n"/>
+      <c r="A77" s="31" t="n"/>
       <c r="B77" s="31" t="n"/>
       <c r="C77" s="31" t="n"/>
       <c r="D77" s="31" t="n"/>
-      <c r="E77" s="33" t="n"/>
-      <c r="F77" s="33" t="n"/>
+      <c r="E77" s="32" t="n"/>
+      <c r="F77" s="32" t="n"/>
       <c r="G77" s="31" t="n"/>
       <c r="H77" s="31" t="n"/>
     </row>
     <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="32" t="n"/>
+      <c r="A78" s="31" t="n"/>
       <c r="B78" s="31" t="n"/>
       <c r="C78" s="31" t="n"/>
       <c r="D78" s="31" t="n"/>
-      <c r="E78" s="33" t="n"/>
-      <c r="F78" s="33" t="n"/>
+      <c r="E78" s="32" t="n"/>
+      <c r="F78" s="32" t="n"/>
       <c r="G78" s="31" t="n"/>
       <c r="H78" s="31" t="n"/>
     </row>
     <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="32" t="n"/>
+      <c r="A79" s="31" t="n"/>
       <c r="B79" s="31" t="n"/>
       <c r="C79" s="31" t="n"/>
       <c r="D79" s="31" t="n"/>
-      <c r="E79" s="33" t="n"/>
-      <c r="F79" s="33" t="n"/>
+      <c r="E79" s="32" t="n"/>
+      <c r="F79" s="32" t="n"/>
       <c r="G79" s="31" t="n"/>
       <c r="H79" s="31" t="n"/>
     </row>
     <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="32" t="n"/>
+      <c r="A80" s="31" t="n"/>
       <c r="B80" s="31" t="n"/>
       <c r="C80" s="31" t="n"/>
       <c r="D80" s="31" t="n"/>
-      <c r="E80" s="33" t="n"/>
-      <c r="F80" s="33" t="n"/>
+      <c r="E80" s="32" t="n"/>
+      <c r="F80" s="32" t="n"/>
       <c r="G80" s="31" t="n"/>
       <c r="H80" s="31" t="n"/>
     </row>
     <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="32" t="n"/>
+      <c r="A81" s="31" t="n"/>
       <c r="B81" s="31" t="n"/>
       <c r="C81" s="31" t="n"/>
       <c r="D81" s="31" t="n"/>
-      <c r="E81" s="33" t="n"/>
-      <c r="F81" s="33" t="n"/>
+      <c r="E81" s="32" t="n"/>
+      <c r="F81" s="32" t="n"/>
       <c r="G81" s="31" t="n"/>
       <c r="H81" s="31" t="n"/>
     </row>
     <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="32" t="n"/>
+      <c r="A82" s="31" t="n"/>
       <c r="B82" s="31" t="n"/>
       <c r="C82" s="31" t="n"/>
       <c r="D82" s="31" t="n"/>
-      <c r="E82" s="33" t="n"/>
-      <c r="F82" s="33" t="n"/>
+      <c r="E82" s="32" t="n"/>
+      <c r="F82" s="32" t="n"/>
       <c r="G82" s="31" t="n"/>
       <c r="H82" s="31" t="n"/>
     </row>
     <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="32" t="n"/>
+      <c r="A83" s="31" t="n"/>
       <c r="B83" s="31" t="n"/>
       <c r="C83" s="31" t="n"/>
       <c r="D83" s="31" t="n"/>
-      <c r="E83" s="33" t="n"/>
-      <c r="F83" s="33" t="n"/>
+      <c r="E83" s="32" t="n"/>
+      <c r="F83" s="32" t="n"/>
       <c r="G83" s="31" t="n"/>
       <c r="H83" s="31" t="n"/>
     </row>
     <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="32" t="n"/>
+      <c r="A84" s="31" t="n"/>
       <c r="B84" s="31" t="n"/>
       <c r="C84" s="31" t="n"/>
       <c r="D84" s="31" t="n"/>
-      <c r="E84" s="33" t="n"/>
-      <c r="F84" s="33" t="n"/>
+      <c r="E84" s="32" t="n"/>
+      <c r="F84" s="32" t="n"/>
       <c r="G84" s="31" t="n"/>
       <c r="H84" s="31" t="n"/>
     </row>
     <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="32" t="n"/>
+      <c r="A85" s="31" t="n"/>
       <c r="B85" s="31" t="n"/>
       <c r="C85" s="31" t="n"/>
       <c r="D85" s="31" t="n"/>
-      <c r="E85" s="33" t="n"/>
-      <c r="F85" s="33" t="n"/>
+      <c r="E85" s="32" t="n"/>
+      <c r="F85" s="32" t="n"/>
       <c r="G85" s="31" t="n"/>
       <c r="H85" s="31" t="n"/>
     </row>
     <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="32" t="n"/>
+      <c r="A86" s="31" t="n"/>
       <c r="B86" s="31" t="n"/>
       <c r="C86" s="31" t="n"/>
       <c r="D86" s="31" t="n"/>
-      <c r="E86" s="33" t="n"/>
-      <c r="F86" s="33" t="n"/>
+      <c r="E86" s="32" t="n"/>
+      <c r="F86" s="32" t="n"/>
       <c r="G86" s="31" t="n"/>
       <c r="H86" s="31" t="n"/>
     </row>
     <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="32" t="n"/>
+      <c r="A87" s="31" t="n"/>
       <c r="B87" s="31" t="n"/>
       <c r="C87" s="31" t="n"/>
       <c r="D87" s="31" t="n"/>
-      <c r="E87" s="33" t="n"/>
-      <c r="F87" s="33" t="n"/>
+      <c r="E87" s="32" t="n"/>
+      <c r="F87" s="32" t="n"/>
       <c r="G87" s="31" t="n"/>
       <c r="H87" s="31" t="n"/>
     </row>
     <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="32" t="n"/>
+      <c r="A88" s="31" t="n"/>
       <c r="B88" s="31" t="n"/>
       <c r="C88" s="31" t="n"/>
       <c r="D88" s="31" t="n"/>
-      <c r="E88" s="33" t="n"/>
-      <c r="F88" s="33" t="n"/>
+      <c r="E88" s="32" t="n"/>
+      <c r="F88" s="32" t="n"/>
       <c r="G88" s="31" t="n"/>
       <c r="H88" s="31" t="n"/>
     </row>
     <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="32" t="n"/>
+      <c r="A89" s="31" t="n"/>
       <c r="B89" s="31" t="n"/>
       <c r="C89" s="31" t="n"/>
       <c r="D89" s="31" t="n"/>
-      <c r="E89" s="33" t="n"/>
-      <c r="F89" s="33" t="n"/>
+      <c r="E89" s="32" t="n"/>
+      <c r="F89" s="32" t="n"/>
       <c r="G89" s="31" t="n"/>
       <c r="H89" s="31" t="n"/>
     </row>
     <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="32" t="n"/>
+      <c r="A90" s="31" t="n"/>
       <c r="B90" s="31" t="n"/>
       <c r="C90" s="31" t="n"/>
       <c r="D90" s="31" t="n"/>
-      <c r="E90" s="33" t="n"/>
-      <c r="F90" s="33" t="n"/>
+      <c r="E90" s="32" t="n"/>
+      <c r="F90" s="32" t="n"/>
       <c r="G90" s="31" t="n"/>
       <c r="H90" s="31" t="n"/>
     </row>
     <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="32" t="n"/>
+      <c r="A91" s="31" t="n"/>
       <c r="B91" s="31" t="n"/>
       <c r="C91" s="31" t="n"/>
       <c r="D91" s="31" t="n"/>
-      <c r="E91" s="33" t="n"/>
-      <c r="F91" s="33" t="n"/>
+      <c r="E91" s="32" t="n"/>
+      <c r="F91" s="32" t="n"/>
       <c r="G91" s="31" t="n"/>
       <c r="H91" s="31" t="n"/>
     </row>
     <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="32" t="n"/>
+      <c r="A92" s="31" t="n"/>
       <c r="B92" s="31" t="n"/>
       <c r="C92" s="31" t="n"/>
       <c r="D92" s="31" t="n"/>
-      <c r="E92" s="33" t="n"/>
-      <c r="F92" s="33" t="n"/>
+      <c r="E92" s="32" t="n"/>
+      <c r="F92" s="32" t="n"/>
       <c r="G92" s="31" t="n"/>
       <c r="H92" s="31" t="n"/>
     </row>
     <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="32" t="n"/>
+      <c r="A93" s="31" t="n"/>
       <c r="B93" s="31" t="n"/>
       <c r="C93" s="31" t="n"/>
       <c r="D93" s="31" t="n"/>
-      <c r="E93" s="33" t="n"/>
-      <c r="F93" s="33" t="n"/>
+      <c r="E93" s="32" t="n"/>
+      <c r="F93" s="32" t="n"/>
       <c r="G93" s="31" t="n"/>
       <c r="H93" s="31" t="n"/>
     </row>
     <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="32" t="n"/>
+      <c r="A94" s="31" t="n"/>
       <c r="B94" s="31" t="n"/>
       <c r="C94" s="31" t="n"/>
       <c r="D94" s="31" t="n"/>
-      <c r="E94" s="33" t="n"/>
-      <c r="F94" s="33" t="n"/>
+      <c r="E94" s="32" t="n"/>
+      <c r="F94" s="32" t="n"/>
       <c r="G94" s="31" t="n"/>
       <c r="H94" s="31" t="n"/>
     </row>
     <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="32" t="n"/>
+      <c r="A95" s="31" t="n"/>
       <c r="B95" s="31" t="n"/>
       <c r="C95" s="31" t="n"/>
       <c r="D95" s="31" t="n"/>
-      <c r="E95" s="33" t="n"/>
-      <c r="F95" s="33" t="n"/>
+      <c r="E95" s="32" t="n"/>
+      <c r="F95" s="32" t="n"/>
       <c r="G95" s="31" t="n"/>
       <c r="H95" s="31" t="n"/>
     </row>
     <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="32" t="n"/>
+      <c r="A96" s="31" t="n"/>
       <c r="B96" s="31" t="n"/>
       <c r="C96" s="31" t="n"/>
       <c r="D96" s="31" t="n"/>
-      <c r="E96" s="33" t="n"/>
-      <c r="F96" s="33" t="n"/>
+      <c r="E96" s="32" t="n"/>
+      <c r="F96" s="32" t="n"/>
       <c r="G96" s="31" t="n"/>
       <c r="H96" s="31" t="n"/>
     </row>
     <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="32" t="n"/>
+      <c r="A97" s="31" t="n"/>
       <c r="B97" s="31" t="n"/>
       <c r="C97" s="31" t="n"/>
       <c r="D97" s="31" t="n"/>
-      <c r="E97" s="33" t="n"/>
-      <c r="F97" s="33" t="n"/>
+      <c r="E97" s="32" t="n"/>
+      <c r="F97" s="32" t="n"/>
       <c r="G97" s="31" t="n"/>
       <c r="H97" s="31" t="n"/>
     </row>
     <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="32" t="n"/>
+      <c r="A98" s="31" t="n"/>
       <c r="B98" s="31" t="n"/>
       <c r="C98" s="31" t="n"/>
       <c r="D98" s="31" t="n"/>
-      <c r="E98" s="33" t="n"/>
-      <c r="F98" s="33" t="n"/>
+      <c r="E98" s="32" t="n"/>
+      <c r="F98" s="32" t="n"/>
       <c r="G98" s="31" t="n"/>
       <c r="H98" s="31" t="n"/>
     </row>
     <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="32" t="n"/>
+      <c r="A99" s="31" t="n"/>
       <c r="B99" s="31" t="n"/>
       <c r="C99" s="31" t="n"/>
       <c r="D99" s="31" t="n"/>
-      <c r="E99" s="33" t="n"/>
-      <c r="F99" s="33" t="n"/>
+      <c r="E99" s="32" t="n"/>
+      <c r="F99" s="32" t="n"/>
       <c r="G99" s="31" t="n"/>
       <c r="H99" s="31" t="n"/>
     </row>
     <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="32" t="n"/>
+      <c r="A100" s="31" t="n"/>
       <c r="B100" s="31" t="n"/>
       <c r="C100" s="31" t="n"/>
       <c r="D100" s="31" t="n"/>
-      <c r="E100" s="33" t="n"/>
-      <c r="F100" s="33" t="n"/>
+      <c r="E100" s="32" t="n"/>
+      <c r="F100" s="32" t="n"/>
       <c r="G100" s="31" t="n"/>
       <c r="H100" s="31" t="n"/>
     </row>
     <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="32" t="n"/>
+      <c r="A101" s="31" t="n"/>
       <c r="B101" s="31" t="n"/>
       <c r="C101" s="31" t="n"/>
       <c r="D101" s="31" t="n"/>
-      <c r="E101" s="33" t="n"/>
-      <c r="F101" s="33" t="n"/>
+      <c r="E101" s="32" t="n"/>
+      <c r="F101" s="32" t="n"/>
       <c r="G101" s="31" t="n"/>
       <c r="H101" s="31" t="n"/>
     </row>
     <row r="102" ht="20" customHeight="1">
-      <c r="A102" s="32" t="n"/>
+      <c r="A102" s="31" t="n"/>
       <c r="B102" s="31" t="n"/>
       <c r="C102" s="31" t="n"/>
       <c r="D102" s="31" t="n"/>
-      <c r="E102" s="33" t="n"/>
-      <c r="F102" s="33" t="n"/>
+      <c r="E102" s="32" t="n"/>
+      <c r="F102" s="32" t="n"/>
       <c r="G102" s="31" t="n"/>
       <c r="H102" s="31" t="n"/>
     </row>
     <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="32" t="n"/>
+      <c r="A103" s="31" t="n"/>
       <c r="B103" s="31" t="n"/>
       <c r="C103" s="31" t="n"/>
       <c r="D103" s="31" t="n"/>
-      <c r="E103" s="33" t="n"/>
-      <c r="F103" s="33" t="n"/>
+      <c r="E103" s="32" t="n"/>
+      <c r="F103" s="32" t="n"/>
       <c r="G103" s="31" t="n"/>
       <c r="H103" s="31" t="n"/>
     </row>
     <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="32" t="n"/>
+      <c r="A104" s="31" t="n"/>
       <c r="B104" s="31" t="n"/>
       <c r="C104" s="31" t="n"/>
       <c r="D104" s="31" t="n"/>
-      <c r="E104" s="33" t="n"/>
-      <c r="F104" s="33" t="n"/>
+      <c r="E104" s="32" t="n"/>
+      <c r="F104" s="32" t="n"/>
       <c r="G104" s="31" t="n"/>
       <c r="H104" s="31" t="n"/>
     </row>
     <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="32" t="n"/>
+      <c r="A105" s="31" t="n"/>
       <c r="B105" s="31" t="n"/>
       <c r="C105" s="31" t="n"/>
       <c r="D105" s="31" t="n"/>
-      <c r="E105" s="33" t="n"/>
-      <c r="F105" s="33" t="n"/>
+      <c r="E105" s="32" t="n"/>
+      <c r="F105" s="32" t="n"/>
       <c r="G105" s="31" t="n"/>
       <c r="H105" s="31" t="n"/>
     </row>
     <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="32" t="n"/>
+      <c r="A106" s="31" t="n"/>
       <c r="B106" s="31" t="n"/>
       <c r="C106" s="31" t="n"/>
       <c r="D106" s="31" t="n"/>
-      <c r="E106" s="33" t="n"/>
-      <c r="F106" s="33" t="n"/>
+      <c r="E106" s="32" t="n"/>
+      <c r="F106" s="32" t="n"/>
       <c r="G106" s="31" t="n"/>
       <c r="H106" s="31" t="n"/>
     </row>
     <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="32" t="n"/>
+      <c r="A107" s="31" t="n"/>
       <c r="B107" s="31" t="n"/>
       <c r="C107" s="31" t="n"/>
       <c r="D107" s="31" t="n"/>
-      <c r="E107" s="33" t="n"/>
-      <c r="F107" s="33" t="n"/>
+      <c r="E107" s="32" t="n"/>
+      <c r="F107" s="32" t="n"/>
       <c r="G107" s="31" t="n"/>
       <c r="H107" s="31" t="n"/>
     </row>
     <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="32" t="n"/>
+      <c r="A108" s="31" t="n"/>
       <c r="B108" s="31" t="n"/>
       <c r="C108" s="31" t="n"/>
       <c r="D108" s="31" t="n"/>
-      <c r="E108" s="33" t="n"/>
-      <c r="F108" s="33" t="n"/>
+      <c r="E108" s="32" t="n"/>
+      <c r="F108" s="32" t="n"/>
       <c r="G108" s="31" t="n"/>
       <c r="H108" s="31" t="n"/>
     </row>
     <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="32" t="n"/>
+      <c r="A109" s="31" t="n"/>
       <c r="B109" s="31" t="n"/>
       <c r="C109" s="31" t="n"/>
       <c r="D109" s="31" t="n"/>
-      <c r="E109" s="33" t="n"/>
-      <c r="F109" s="33" t="n"/>
+      <c r="E109" s="32" t="n"/>
+      <c r="F109" s="32" t="n"/>
       <c r="G109" s="31" t="n"/>
       <c r="H109" s="31" t="n"/>
     </row>
     <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="32" t="n"/>
+      <c r="A110" s="31" t="n"/>
       <c r="B110" s="31" t="n"/>
       <c r="C110" s="31" t="n"/>
       <c r="D110" s="31" t="n"/>
-      <c r="E110" s="33" t="n"/>
-      <c r="F110" s="33" t="n"/>
+      <c r="E110" s="32" t="n"/>
+      <c r="F110" s="32" t="n"/>
       <c r="G110" s="31" t="n"/>
       <c r="H110" s="31" t="n"/>
     </row>
     <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="32" t="n"/>
+      <c r="A111" s="31" t="n"/>
       <c r="B111" s="31" t="n"/>
       <c r="C111" s="31" t="n"/>
       <c r="D111" s="31" t="n"/>
-      <c r="E111" s="33" t="n"/>
-      <c r="F111" s="33" t="n"/>
+      <c r="E111" s="32" t="n"/>
+      <c r="F111" s="32" t="n"/>
       <c r="G111" s="31" t="n"/>
       <c r="H111" s="31" t="n"/>
     </row>
     <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="32" t="n"/>
+      <c r="A112" s="31" t="n"/>
       <c r="B112" s="31" t="n"/>
       <c r="C112" s="31" t="n"/>
       <c r="D112" s="31" t="n"/>
-      <c r="E112" s="33" t="n"/>
-      <c r="F112" s="33" t="n"/>
+      <c r="E112" s="32" t="n"/>
+      <c r="F112" s="32" t="n"/>
       <c r="G112" s="31" t="n"/>
       <c r="H112" s="31" t="n"/>
     </row>
     <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="32" t="n"/>
+      <c r="A113" s="31" t="n"/>
       <c r="B113" s="31" t="n"/>
       <c r="C113" s="31" t="n"/>
       <c r="D113" s="31" t="n"/>
-      <c r="E113" s="33" t="n"/>
-      <c r="F113" s="33" t="n"/>
+      <c r="E113" s="32" t="n"/>
+      <c r="F113" s="32" t="n"/>
       <c r="G113" s="31" t="n"/>
       <c r="H113" s="31" t="n"/>
     </row>
     <row r="114" ht="20" customHeight="1">
-      <c r="A114" s="32" t="n"/>
+      <c r="A114" s="31" t="n"/>
       <c r="B114" s="31" t="n"/>
       <c r="C114" s="31" t="n"/>
       <c r="D114" s="31" t="n"/>
-      <c r="E114" s="33" t="n"/>
-      <c r="F114" s="33" t="n"/>
+      <c r="E114" s="32" t="n"/>
+      <c r="F114" s="32" t="n"/>
       <c r="G114" s="31" t="n"/>
       <c r="H114" s="31" t="n"/>
     </row>
     <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="32" t="n"/>
+      <c r="A115" s="31" t="n"/>
       <c r="B115" s="31" t="n"/>
       <c r="C115" s="31" t="n"/>
       <c r="D115" s="31" t="n"/>
-      <c r="E115" s="33" t="n"/>
-      <c r="F115" s="33" t="n"/>
+      <c r="E115" s="32" t="n"/>
+      <c r="F115" s="32" t="n"/>
       <c r="G115" s="31" t="n"/>
       <c r="H115" s="31" t="n"/>
     </row>
     <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="32" t="n"/>
+      <c r="A116" s="31" t="n"/>
       <c r="B116" s="31" t="n"/>
       <c r="C116" s="31" t="n"/>
       <c r="D116" s="31" t="n"/>
-      <c r="E116" s="33" t="n"/>
-      <c r="F116" s="33" t="n"/>
+      <c r="E116" s="32" t="n"/>
+      <c r="F116" s="32" t="n"/>
       <c r="G116" s="31" t="n"/>
       <c r="H116" s="31" t="n"/>
     </row>
     <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="32" t="n"/>
+      <c r="A117" s="31" t="n"/>
       <c r="B117" s="31" t="n"/>
       <c r="C117" s="31" t="n"/>
       <c r="D117" s="31" t="n"/>
-      <c r="E117" s="33" t="n"/>
-      <c r="F117" s="33" t="n"/>
+      <c r="E117" s="32" t="n"/>
+      <c r="F117" s="32" t="n"/>
       <c r="G117" s="31" t="n"/>
       <c r="H117" s="31" t="n"/>
     </row>
     <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="32" t="n"/>
+      <c r="A118" s="31" t="n"/>
       <c r="B118" s="31" t="n"/>
       <c r="C118" s="31" t="n"/>
       <c r="D118" s="31" t="n"/>
-      <c r="E118" s="33" t="n"/>
-      <c r="F118" s="33" t="n"/>
+      <c r="E118" s="32" t="n"/>
+      <c r="F118" s="32" t="n"/>
       <c r="G118" s="31" t="n"/>
       <c r="H118" s="31" t="n"/>
     </row>
     <row r="119" ht="20" customHeight="1">
-      <c r="A119" s="32" t="n"/>
+      <c r="A119" s="31" t="n"/>
       <c r="B119" s="31" t="n"/>
       <c r="C119" s="31" t="n"/>
       <c r="D119" s="31" t="n"/>
-      <c r="E119" s="33" t="n"/>
-      <c r="F119" s="33" t="n"/>
+      <c r="E119" s="32" t="n"/>
+      <c r="F119" s="32" t="n"/>
       <c r="G119" s="31" t="n"/>
       <c r="H119" s="31" t="n"/>
     </row>
     <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="32" t="n"/>
+      <c r="A120" s="31" t="n"/>
       <c r="B120" s="31" t="n"/>
       <c r="C120" s="31" t="n"/>
       <c r="D120" s="31" t="n"/>
-      <c r="E120" s="33" t="n"/>
-      <c r="F120" s="33" t="n"/>
+      <c r="E120" s="32" t="n"/>
+      <c r="F120" s="32" t="n"/>
       <c r="G120" s="31" t="n"/>
       <c r="H120" s="31" t="n"/>
     </row>
     <row r="121" ht="20" customHeight="1">
-      <c r="A121" s="32" t="n"/>
+      <c r="A121" s="31" t="n"/>
       <c r="B121" s="31" t="n"/>
       <c r="C121" s="31" t="n"/>
       <c r="D121" s="31" t="n"/>
-      <c r="E121" s="33" t="n"/>
-      <c r="F121" s="33" t="n"/>
+      <c r="E121" s="32" t="n"/>
+      <c r="F121" s="32" t="n"/>
       <c r="G121" s="31" t="n"/>
       <c r="H121" s="31" t="n"/>
     </row>
     <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="32" t="n"/>
+      <c r="A122" s="31" t="n"/>
       <c r="B122" s="31" t="n"/>
       <c r="C122" s="31" t="n"/>
       <c r="D122" s="31" t="n"/>
-      <c r="E122" s="33" t="n"/>
-      <c r="F122" s="33" t="n"/>
+      <c r="E122" s="32" t="n"/>
+      <c r="F122" s="32" t="n"/>
       <c r="G122" s="31" t="n"/>
       <c r="H122" s="31" t="n"/>
     </row>
     <row r="123" ht="20" customHeight="1">
-      <c r="A123" s="32" t="n"/>
+      <c r="A123" s="31" t="n"/>
       <c r="B123" s="31" t="n"/>
       <c r="C123" s="31" t="n"/>
       <c r="D123" s="31" t="n"/>
-      <c r="E123" s="33" t="n"/>
-      <c r="F123" s="33" t="n"/>
+      <c r="E123" s="32" t="n"/>
+      <c r="F123" s="32" t="n"/>
       <c r="G123" s="31" t="n"/>
       <c r="H123" s="31" t="n"/>
     </row>
     <row r="124" ht="20" customHeight="1">
-      <c r="A124" s="32" t="n"/>
+      <c r="A124" s="31" t="n"/>
       <c r="B124" s="31" t="n"/>
       <c r="C124" s="31" t="n"/>
       <c r="D124" s="31" t="n"/>
-      <c r="E124" s="33" t="n"/>
-      <c r="F124" s="33" t="n"/>
+      <c r="E124" s="32" t="n"/>
+      <c r="F124" s="32" t="n"/>
       <c r="G124" s="31" t="n"/>
       <c r="H124" s="31" t="n"/>
     </row>
     <row r="125" ht="20" customHeight="1">
-      <c r="A125" s="32" t="n"/>
+      <c r="A125" s="31" t="n"/>
       <c r="B125" s="31" t="n"/>
       <c r="C125" s="31" t="n"/>
       <c r="D125" s="31" t="n"/>
-      <c r="E125" s="33" t="n"/>
-      <c r="F125" s="33" t="n"/>
+      <c r="E125" s="32" t="n"/>
+      <c r="F125" s="32" t="n"/>
       <c r="G125" s="31" t="n"/>
       <c r="H125" s="31" t="n"/>
     </row>
     <row r="126" ht="20" customHeight="1">
-      <c r="A126" s="32" t="n"/>
+      <c r="A126" s="31" t="n"/>
       <c r="B126" s="31" t="n"/>
       <c r="C126" s="31" t="n"/>
       <c r="D126" s="31" t="n"/>
-      <c r="E126" s="33" t="n"/>
-      <c r="F126" s="33" t="n"/>
+      <c r="E126" s="32" t="n"/>
+      <c r="F126" s="32" t="n"/>
       <c r="G126" s="31" t="n"/>
       <c r="H126" s="31" t="n"/>
     </row>
     <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="32" t="n"/>
+      <c r="A127" s="31" t="n"/>
       <c r="B127" s="31" t="n"/>
       <c r="C127" s="31" t="n"/>
       <c r="D127" s="31" t="n"/>
-      <c r="E127" s="33" t="n"/>
-      <c r="F127" s="33" t="n"/>
+      <c r="E127" s="32" t="n"/>
+      <c r="F127" s="32" t="n"/>
       <c r="G127" s="31" t="n"/>
       <c r="H127" s="31" t="n"/>
     </row>
     <row r="128" ht="20" customHeight="1">
-      <c r="A128" s="32" t="n"/>
+      <c r="A128" s="31" t="n"/>
       <c r="B128" s="31" t="n"/>
       <c r="C128" s="31" t="n"/>
       <c r="D128" s="31" t="n"/>
-      <c r="E128" s="33" t="n"/>
-      <c r="F128" s="33" t="n"/>
+      <c r="E128" s="32" t="n"/>
+      <c r="F128" s="32" t="n"/>
       <c r="G128" s="31" t="n"/>
       <c r="H128" s="31" t="n"/>
     </row>
     <row r="129" ht="20" customHeight="1">
-      <c r="A129" s="32" t="n"/>
+      <c r="A129" s="31" t="n"/>
       <c r="B129" s="31" t="n"/>
       <c r="C129" s="31" t="n"/>
       <c r="D129" s="31" t="n"/>
-      <c r="E129" s="33" t="n"/>
-      <c r="F129" s="33" t="n"/>
+      <c r="E129" s="32" t="n"/>
+      <c r="F129" s="32" t="n"/>
       <c r="G129" s="31" t="n"/>
       <c r="H129" s="31" t="n"/>
     </row>
     <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="32" t="n"/>
+      <c r="A130" s="31" t="n"/>
       <c r="B130" s="31" t="n"/>
       <c r="C130" s="31" t="n"/>
       <c r="D130" s="31" t="n"/>
-      <c r="E130" s="33" t="n"/>
-      <c r="F130" s="33" t="n"/>
+      <c r="E130" s="32" t="n"/>
+      <c r="F130" s="32" t="n"/>
       <c r="G130" s="31" t="n"/>
       <c r="H130" s="31" t="n"/>
     </row>
     <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="32" t="n"/>
+      <c r="A131" s="31" t="n"/>
       <c r="B131" s="31" t="n"/>
       <c r="C131" s="31" t="n"/>
       <c r="D131" s="31" t="n"/>
-      <c r="E131" s="33" t="n"/>
-      <c r="F131" s="33" t="n"/>
+      <c r="E131" s="32" t="n"/>
+      <c r="F131" s="32" t="n"/>
       <c r="G131" s="31" t="n"/>
       <c r="H131" s="31" t="n"/>
     </row>
     <row r="132" ht="20" customHeight="1">
-      <c r="A132" s="32" t="n"/>
+      <c r="A132" s="31" t="n"/>
       <c r="B132" s="31" t="n"/>
       <c r="C132" s="31" t="n"/>
       <c r="D132" s="31" t="n"/>
-      <c r="E132" s="33" t="n"/>
-      <c r="F132" s="33" t="n"/>
+      <c r="E132" s="32" t="n"/>
+      <c r="F132" s="32" t="n"/>
       <c r="G132" s="31" t="n"/>
       <c r="H132" s="31" t="n"/>
     </row>
     <row r="133" ht="20" customHeight="1">
-      <c r="A133" s="32" t="n"/>
+      <c r="A133" s="31" t="n"/>
       <c r="B133" s="31" t="n"/>
       <c r="C133" s="31" t="n"/>
       <c r="D133" s="31" t="n"/>
-      <c r="E133" s="33" t="n"/>
-      <c r="F133" s="33" t="n"/>
+      <c r="E133" s="32" t="n"/>
+      <c r="F133" s="32" t="n"/>
       <c r="G133" s="31" t="n"/>
       <c r="H133" s="31" t="n"/>
     </row>
     <row r="134" ht="20" customHeight="1">
-      <c r="A134" s="32" t="n"/>
+      <c r="A134" s="31" t="n"/>
       <c r="B134" s="31" t="n"/>
       <c r="C134" s="31" t="n"/>
       <c r="D134" s="31" t="n"/>
-      <c r="E134" s="33" t="n"/>
-      <c r="F134" s="33" t="n"/>
+      <c r="E134" s="32" t="n"/>
+      <c r="F134" s="32" t="n"/>
       <c r="G134" s="31" t="n"/>
       <c r="H134" s="31" t="n"/>
     </row>
     <row r="135" ht="20" customHeight="1">
-      <c r="A135" s="32" t="n"/>
+      <c r="A135" s="31" t="n"/>
       <c r="B135" s="31" t="n"/>
       <c r="C135" s="31" t="n"/>
       <c r="D135" s="31" t="n"/>
-      <c r="E135" s="33" t="n"/>
-      <c r="F135" s="33" t="n"/>
+      <c r="E135" s="32" t="n"/>
+      <c r="F135" s="32" t="n"/>
       <c r="G135" s="31" t="n"/>
       <c r="H135" s="31" t="n"/>
     </row>
     <row r="136" ht="20" customHeight="1">
-      <c r="A136" s="32" t="n"/>
+      <c r="A136" s="31" t="n"/>
       <c r="B136" s="31" t="n"/>
       <c r="C136" s="31" t="n"/>
       <c r="D136" s="31" t="n"/>
-      <c r="E136" s="33" t="n"/>
-      <c r="F136" s="33" t="n"/>
+      <c r="E136" s="32" t="n"/>
+      <c r="F136" s="32" t="n"/>
       <c r="G136" s="31" t="n"/>
       <c r="H136" s="31" t="n"/>
     </row>
     <row r="137" ht="20" customHeight="1">
-      <c r="A137" s="32" t="n"/>
+      <c r="A137" s="31" t="n"/>
       <c r="B137" s="31" t="n"/>
       <c r="C137" s="31" t="n"/>
       <c r="D137" s="31" t="n"/>
-      <c r="E137" s="33" t="n"/>
-      <c r="F137" s="33" t="n"/>
+      <c r="E137" s="32" t="n"/>
+      <c r="F137" s="32" t="n"/>
       <c r="G137" s="31" t="n"/>
       <c r="H137" s="31" t="n"/>
     </row>
     <row r="138" ht="20" customHeight="1">
-      <c r="A138" s="32" t="n"/>
+      <c r="A138" s="31" t="n"/>
       <c r="B138" s="31" t="n"/>
       <c r="C138" s="31" t="n"/>
       <c r="D138" s="31" t="n"/>
-      <c r="E138" s="33" t="n"/>
-      <c r="F138" s="33" t="n"/>
+      <c r="E138" s="32" t="n"/>
+      <c r="F138" s="32" t="n"/>
       <c r="G138" s="31" t="n"/>
       <c r="H138" s="31" t="n"/>
     </row>
     <row r="139" ht="20" customHeight="1">
-      <c r="A139" s="32" t="n"/>
+      <c r="A139" s="31" t="n"/>
       <c r="B139" s="31" t="n"/>
       <c r="C139" s="31" t="n"/>
       <c r="D139" s="31" t="n"/>
-      <c r="E139" s="33" t="n"/>
-      <c r="F139" s="33" t="n"/>
+      <c r="E139" s="32" t="n"/>
+      <c r="F139" s="32" t="n"/>
       <c r="G139" s="31" t="n"/>
       <c r="H139" s="31" t="n"/>
     </row>
     <row r="140" ht="20" customHeight="1">
-      <c r="A140" s="32" t="n"/>
+      <c r="A140" s="31" t="n"/>
       <c r="B140" s="31" t="n"/>
       <c r="C140" s="31" t="n"/>
       <c r="D140" s="31" t="n"/>
-      <c r="E140" s="33" t="n"/>
-      <c r="F140" s="33" t="n"/>
+      <c r="E140" s="32" t="n"/>
+      <c r="F140" s="32" t="n"/>
       <c r="G140" s="31" t="n"/>
       <c r="H140" s="31" t="n"/>
     </row>
     <row r="141" ht="20" customHeight="1">
-      <c r="A141" s="32" t="n"/>
+      <c r="A141" s="31" t="n"/>
       <c r="B141" s="31" t="n"/>
       <c r="C141" s="31" t="n"/>
       <c r="D141" s="31" t="n"/>
-      <c r="E141" s="33" t="n"/>
-      <c r="F141" s="33" t="n"/>
+      <c r="E141" s="32" t="n"/>
+      <c r="F141" s="32" t="n"/>
       <c r="G141" s="31" t="n"/>
       <c r="H141" s="31" t="n"/>
     </row>
     <row r="142" ht="20" customHeight="1">
-      <c r="A142" s="32" t="n"/>
+      <c r="A142" s="31" t="n"/>
       <c r="B142" s="31" t="n"/>
       <c r="C142" s="31" t="n"/>
       <c r="D142" s="31" t="n"/>
-      <c r="E142" s="33" t="n"/>
-      <c r="F142" s="33" t="n"/>
+      <c r="E142" s="32" t="n"/>
+      <c r="F142" s="32" t="n"/>
       <c r="G142" s="31" t="n"/>
       <c r="H142" s="31" t="n"/>
     </row>
     <row r="143" ht="20" customHeight="1">
-      <c r="A143" s="32" t="n"/>
+      <c r="A143" s="31" t="n"/>
       <c r="B143" s="31" t="n"/>
       <c r="C143" s="31" t="n"/>
       <c r="D143" s="31" t="n"/>
-      <c r="E143" s="33" t="n"/>
-      <c r="F143" s="33" t="n"/>
+      <c r="E143" s="32" t="n"/>
+      <c r="F143" s="32" t="n"/>
       <c r="G143" s="31" t="n"/>
       <c r="H143" s="31" t="n"/>
     </row>
     <row r="144" ht="20" customHeight="1">
-      <c r="A144" s="32" t="n"/>
+      <c r="A144" s="31" t="n"/>
       <c r="B144" s="31" t="n"/>
       <c r="C144" s="31" t="n"/>
       <c r="D144" s="31" t="n"/>
-      <c r="E144" s="33" t="n"/>
-      <c r="F144" s="33" t="n"/>
+      <c r="E144" s="32" t="n"/>
+      <c r="F144" s="32" t="n"/>
       <c r="G144" s="31" t="n"/>
       <c r="H144" s="31" t="n"/>
     </row>
     <row r="145" ht="20" customHeight="1">
-      <c r="A145" s="32" t="n"/>
+      <c r="A145" s="31" t="n"/>
       <c r="B145" s="31" t="n"/>
       <c r="C145" s="31" t="n"/>
       <c r="D145" s="31" t="n"/>
-      <c r="E145" s="33" t="n"/>
-      <c r="F145" s="33" t="n"/>
+      <c r="E145" s="32" t="n"/>
+      <c r="F145" s="32" t="n"/>
       <c r="G145" s="31" t="n"/>
       <c r="H145" s="31" t="n"/>
     </row>
     <row r="146" ht="20" customHeight="1">
-      <c r="A146" s="32" t="n"/>
+      <c r="A146" s="31" t="n"/>
       <c r="B146" s="31" t="n"/>
       <c r="C146" s="31" t="n"/>
       <c r="D146" s="31" t="n"/>
-      <c r="E146" s="33" t="n"/>
-      <c r="F146" s="33" t="n"/>
+      <c r="E146" s="32" t="n"/>
+      <c r="F146" s="32" t="n"/>
       <c r="G146" s="31" t="n"/>
       <c r="H146" s="31" t="n"/>
     </row>
     <row r="147" ht="20" customHeight="1">
-      <c r="A147" s="32" t="n"/>
+      <c r="A147" s="31" t="n"/>
       <c r="B147" s="31" t="n"/>
       <c r="C147" s="31" t="n"/>
       <c r="D147" s="31" t="n"/>
-      <c r="E147" s="33" t="n"/>
-      <c r="F147" s="33" t="n"/>
+      <c r="E147" s="32" t="n"/>
+      <c r="F147" s="32" t="n"/>
       <c r="G147" s="31" t="n"/>
       <c r="H147" s="31" t="n"/>
     </row>
     <row r="148" ht="20" customHeight="1">
-      <c r="A148" s="32" t="n"/>
+      <c r="A148" s="31" t="n"/>
       <c r="B148" s="31" t="n"/>
       <c r="C148" s="31" t="n"/>
       <c r="D148" s="31" t="n"/>
-      <c r="E148" s="33" t="n"/>
-      <c r="F148" s="33" t="n"/>
+      <c r="E148" s="32" t="n"/>
+      <c r="F148" s="32" t="n"/>
       <c r="G148" s="31" t="n"/>
       <c r="H148" s="31" t="n"/>
     </row>
     <row r="149" ht="20" customHeight="1">
-      <c r="A149" s="32" t="n"/>
+      <c r="A149" s="31" t="n"/>
       <c r="B149" s="31" t="n"/>
       <c r="C149" s="31" t="n"/>
       <c r="D149" s="31" t="n"/>
-      <c r="E149" s="33" t="n"/>
-      <c r="F149" s="33" t="n"/>
+      <c r="E149" s="32" t="n"/>
+      <c r="F149" s="32" t="n"/>
       <c r="G149" s="31" t="n"/>
       <c r="H149" s="31" t="n"/>
     </row>
     <row r="150" ht="20" customHeight="1">
-      <c r="A150" s="32" t="n"/>
+      <c r="A150" s="31" t="n"/>
       <c r="B150" s="31" t="n"/>
       <c r="C150" s="31" t="n"/>
       <c r="D150" s="31" t="n"/>
-      <c r="E150" s="33" t="n"/>
-      <c r="F150" s="33" t="n"/>
+      <c r="E150" s="32" t="n"/>
+      <c r="F150" s="32" t="n"/>
       <c r="G150" s="31" t="n"/>
       <c r="H150" s="31" t="n"/>
     </row>
     <row r="151" ht="20" customHeight="1">
-      <c r="A151" s="32" t="n"/>
+      <c r="A151" s="31" t="n"/>
       <c r="B151" s="31" t="n"/>
       <c r="C151" s="31" t="n"/>
       <c r="D151" s="31" t="n"/>
-      <c r="E151" s="33" t="n"/>
-      <c r="F151" s="33" t="n"/>
+      <c r="E151" s="32" t="n"/>
+      <c r="F151" s="32" t="n"/>
       <c r="G151" s="31" t="n"/>
       <c r="H151" s="31" t="n"/>
     </row>
     <row r="152" ht="20" customHeight="1">
-      <c r="A152" s="32" t="n"/>
+      <c r="A152" s="31" t="n"/>
       <c r="B152" s="31" t="n"/>
       <c r="C152" s="31" t="n"/>
       <c r="D152" s="31" t="n"/>
-      <c r="E152" s="33" t="n"/>
-      <c r="F152" s="33" t="n"/>
+      <c r="E152" s="32" t="n"/>
+      <c r="F152" s="32" t="n"/>
       <c r="G152" s="31" t="n"/>
       <c r="H152" s="31" t="n"/>
     </row>
     <row r="153" ht="20" customHeight="1">
-      <c r="A153" s="32" t="n"/>
+      <c r="A153" s="31" t="n"/>
       <c r="B153" s="31" t="n"/>
       <c r="C153" s="31" t="n"/>
       <c r="D153" s="31" t="n"/>
-      <c r="E153" s="33" t="n"/>
-      <c r="F153" s="33" t="n"/>
+      <c r="E153" s="32" t="n"/>
+      <c r="F153" s="32" t="n"/>
       <c r="G153" s="31" t="n"/>
       <c r="H153" s="31" t="n"/>
     </row>
     <row r="154" ht="20" customHeight="1">
-      <c r="A154" s="32" t="n"/>
+      <c r="A154" s="31" t="n"/>
       <c r="B154" s="31" t="n"/>
       <c r="C154" s="31" t="n"/>
       <c r="D154" s="31" t="n"/>
-      <c r="E154" s="33" t="n"/>
-      <c r="F154" s="33" t="n"/>
+      <c r="E154" s="32" t="n"/>
+      <c r="F154" s="32" t="n"/>
       <c r="G154" s="31" t="n"/>
       <c r="H154" s="31" t="n"/>
     </row>
     <row r="155" ht="20" customHeight="1">
-      <c r="A155" s="32" t="n"/>
+      <c r="A155" s="31" t="n"/>
       <c r="B155" s="31" t="n"/>
       <c r="C155" s="31" t="n"/>
       <c r="D155" s="31" t="n"/>
-      <c r="E155" s="33" t="n"/>
-      <c r="F155" s="33" t="n"/>
+      <c r="E155" s="32" t="n"/>
+      <c r="F155" s="32" t="n"/>
       <c r="G155" s="31" t="n"/>
       <c r="H155" s="31" t="n"/>
     </row>
     <row r="156" ht="20" customHeight="1">
-      <c r="A156" s="32" t="n"/>
+      <c r="A156" s="31" t="n"/>
       <c r="B156" s="31" t="n"/>
       <c r="C156" s="31" t="n"/>
       <c r="D156" s="31" t="n"/>
-      <c r="E156" s="33" t="n"/>
-      <c r="F156" s="33" t="n"/>
+      <c r="E156" s="32" t="n"/>
+      <c r="F156" s="32" t="n"/>
       <c r="G156" s="31" t="n"/>
       <c r="H156" s="31" t="n"/>
     </row>
     <row r="157" ht="20" customHeight="1">
-      <c r="A157" s="32" t="n"/>
+      <c r="A157" s="31" t="n"/>
       <c r="B157" s="31" t="n"/>
       <c r="C157" s="31" t="n"/>
       <c r="D157" s="31" t="n"/>
-      <c r="E157" s="33" t="n"/>
-      <c r="F157" s="33" t="n"/>
+      <c r="E157" s="32" t="n"/>
+      <c r="F157" s="32" t="n"/>
       <c r="G157" s="31" t="n"/>
       <c r="H157" s="31" t="n"/>
     </row>
     <row r="158" ht="20" customHeight="1">
-      <c r="A158" s="32" t="n"/>
+      <c r="A158" s="31" t="n"/>
       <c r="B158" s="31" t="n"/>
       <c r="C158" s="31" t="n"/>
       <c r="D158" s="31" t="n"/>
-      <c r="E158" s="33" t="n"/>
-      <c r="F158" s="33" t="n"/>
+      <c r="E158" s="32" t="n"/>
+      <c r="F158" s="32" t="n"/>
       <c r="G158" s="31" t="n"/>
       <c r="H158" s="31" t="n"/>
     </row>
     <row r="159" ht="20" customHeight="1">
-      <c r="A159" s="32" t="n"/>
+      <c r="A159" s="31" t="n"/>
       <c r="B159" s="31" t="n"/>
       <c r="C159" s="31" t="n"/>
       <c r="D159" s="31" t="n"/>
-      <c r="E159" s="33" t="n"/>
-      <c r="F159" s="33" t="n"/>
+      <c r="E159" s="32" t="n"/>
+      <c r="F159" s="32" t="n"/>
       <c r="G159" s="31" t="n"/>
       <c r="H159" s="31" t="n"/>
     </row>
     <row r="160" ht="20" customHeight="1">
-      <c r="A160" s="32" t="n"/>
+      <c r="A160" s="31" t="n"/>
       <c r="B160" s="31" t="n"/>
       <c r="C160" s="31" t="n"/>
       <c r="D160" s="31" t="n"/>
-      <c r="E160" s="33" t="n"/>
-      <c r="F160" s="33" t="n"/>
+      <c r="E160" s="32" t="n"/>
+      <c r="F160" s="32" t="n"/>
       <c r="G160" s="31" t="n"/>
       <c r="H160" s="31" t="n"/>
     </row>
     <row r="161" ht="20" customHeight="1">
-      <c r="A161" s="32" t="n"/>
+      <c r="A161" s="31" t="n"/>
       <c r="B161" s="31" t="n"/>
       <c r="C161" s="31" t="n"/>
       <c r="D161" s="31" t="n"/>
-      <c r="E161" s="33" t="n"/>
-      <c r="F161" s="33" t="n"/>
+      <c r="E161" s="32" t="n"/>
+      <c r="F161" s="32" t="n"/>
       <c r="G161" s="31" t="n"/>
       <c r="H161" s="31" t="n"/>
     </row>
     <row r="162" ht="20" customHeight="1">
-      <c r="A162" s="32" t="n"/>
+      <c r="A162" s="31" t="n"/>
       <c r="B162" s="31" t="n"/>
       <c r="C162" s="31" t="n"/>
       <c r="D162" s="31" t="n"/>
-      <c r="E162" s="33" t="n"/>
-      <c r="F162" s="33" t="n"/>
+      <c r="E162" s="32" t="n"/>
+      <c r="F162" s="32" t="n"/>
       <c r="G162" s="31" t="n"/>
       <c r="H162" s="31" t="n"/>
     </row>
     <row r="163" ht="20" customHeight="1">
-      <c r="A163" s="32" t="n"/>
+      <c r="A163" s="31" t="n"/>
       <c r="B163" s="31" t="n"/>
       <c r="C163" s="31" t="n"/>
       <c r="D163" s="31" t="n"/>
-      <c r="E163" s="33" t="n"/>
-      <c r="F163" s="33" t="n"/>
+      <c r="E163" s="32" t="n"/>
+      <c r="F163" s="32" t="n"/>
       <c r="G163" s="31" t="n"/>
       <c r="H163" s="31" t="n"/>
     </row>
     <row r="164" ht="20" customHeight="1">
-      <c r="A164" s="32" t="n"/>
+      <c r="A164" s="31" t="n"/>
       <c r="B164" s="31" t="n"/>
       <c r="C164" s="31" t="n"/>
       <c r="D164" s="31" t="n"/>
-      <c r="E164" s="33" t="n"/>
-      <c r="F164" s="33" t="n"/>
+      <c r="E164" s="32" t="n"/>
+      <c r="F164" s="32" t="n"/>
       <c r="G164" s="31" t="n"/>
       <c r="H164" s="31" t="n"/>
     </row>
     <row r="165" ht="20" customHeight="1">
-      <c r="A165" s="32" t="n"/>
+      <c r="A165" s="31" t="n"/>
       <c r="B165" s="31" t="n"/>
       <c r="C165" s="31" t="n"/>
       <c r="D165" s="31" t="n"/>
-      <c r="E165" s="33" t="n"/>
-      <c r="F165" s="33" t="n"/>
+      <c r="E165" s="32" t="n"/>
+      <c r="F165" s="32" t="n"/>
       <c r="G165" s="31" t="n"/>
       <c r="H165" s="31" t="n"/>
     </row>
     <row r="166" ht="20" customHeight="1">
-      <c r="A166" s="32" t="n"/>
+      <c r="A166" s="31" t="n"/>
       <c r="B166" s="31" t="n"/>
       <c r="C166" s="31" t="n"/>
       <c r="D166" s="31" t="n"/>
-      <c r="E166" s="33" t="n"/>
-      <c r="F166" s="33" t="n"/>
+      <c r="E166" s="32" t="n"/>
+      <c r="F166" s="32" t="n"/>
       <c r="G166" s="31" t="n"/>
       <c r="H166" s="31" t="n"/>
     </row>
     <row r="167" ht="20" customHeight="1">
-      <c r="A167" s="32" t="n"/>
+      <c r="A167" s="31" t="n"/>
       <c r="B167" s="31" t="n"/>
       <c r="C167" s="31" t="n"/>
       <c r="D167" s="31" t="n"/>
-      <c r="E167" s="33" t="n"/>
-      <c r="F167" s="33" t="n"/>
+      <c r="E167" s="32" t="n"/>
+      <c r="F167" s="32" t="n"/>
       <c r="G167" s="31" t="n"/>
       <c r="H167" s="31" t="n"/>
     </row>
     <row r="168" ht="20" customHeight="1">
-      <c r="A168" s="32" t="n"/>
+      <c r="A168" s="31" t="n"/>
       <c r="B168" s="31" t="n"/>
       <c r="C168" s="31" t="n"/>
       <c r="D168" s="31" t="n"/>
-      <c r="E168" s="33" t="n"/>
-      <c r="F168" s="33" t="n"/>
+      <c r="E168" s="32" t="n"/>
+      <c r="F168" s="32" t="n"/>
       <c r="G168" s="31" t="n"/>
       <c r="H168" s="31" t="n"/>
     </row>
     <row r="169" ht="20" customHeight="1">
-      <c r="A169" s="32" t="n"/>
+      <c r="A169" s="31" t="n"/>
       <c r="B169" s="31" t="n"/>
       <c r="C169" s="31" t="n"/>
       <c r="D169" s="31" t="n"/>
-      <c r="E169" s="33" t="n"/>
-      <c r="F169" s="33" t="n"/>
+      <c r="E169" s="32" t="n"/>
+      <c r="F169" s="32" t="n"/>
       <c r="G169" s="31" t="n"/>
       <c r="H169" s="31" t="n"/>
     </row>
     <row r="170" ht="20" customHeight="1">
-      <c r="A170" s="32" t="n"/>
+      <c r="A170" s="31" t="n"/>
       <c r="B170" s="31" t="n"/>
       <c r="C170" s="31" t="n"/>
       <c r="D170" s="31" t="n"/>
-      <c r="E170" s="33" t="n"/>
-      <c r="F170" s="33" t="n"/>
+      <c r="E170" s="32" t="n"/>
+      <c r="F170" s="32" t="n"/>
       <c r="G170" s="31" t="n"/>
       <c r="H170" s="31" t="n"/>
     </row>
     <row r="171" ht="20" customHeight="1">
-      <c r="A171" s="32" t="n"/>
+      <c r="A171" s="31" t="n"/>
       <c r="B171" s="31" t="n"/>
       <c r="C171" s="31" t="n"/>
       <c r="D171" s="31" t="n"/>
-      <c r="E171" s="33" t="n"/>
-      <c r="F171" s="33" t="n"/>
+      <c r="E171" s="32" t="n"/>
+      <c r="F171" s="32" t="n"/>
       <c r="G171" s="31" t="n"/>
       <c r="H171" s="31" t="n"/>
     </row>
     <row r="172" ht="20" customHeight="1">
-      <c r="A172" s="32" t="n"/>
+      <c r="A172" s="31" t="n"/>
       <c r="B172" s="31" t="n"/>
       <c r="C172" s="31" t="n"/>
       <c r="D172" s="31" t="n"/>
-      <c r="E172" s="33" t="n"/>
-      <c r="F172" s="33" t="n"/>
+      <c r="E172" s="32" t="n"/>
+      <c r="F172" s="32" t="n"/>
       <c r="G172" s="31" t="n"/>
       <c r="H172" s="31" t="n"/>
     </row>
     <row r="173" ht="20" customHeight="1">
-      <c r="A173" s="32" t="n"/>
+      <c r="A173" s="31" t="n"/>
       <c r="B173" s="31" t="n"/>
       <c r="C173" s="31" t="n"/>
       <c r="D173" s="31" t="n"/>
-      <c r="E173" s="33" t="n"/>
-      <c r="F173" s="33" t="n"/>
+      <c r="E173" s="32" t="n"/>
+      <c r="F173" s="32" t="n"/>
       <c r="G173" s="31" t="n"/>
       <c r="H173" s="31" t="n"/>
     </row>
     <row r="174" ht="20" customHeight="1">
-      <c r="A174" s="32" t="n"/>
+      <c r="A174" s="31" t="n"/>
       <c r="B174" s="31" t="n"/>
       <c r="C174" s="31" t="n"/>
       <c r="D174" s="31" t="n"/>
-      <c r="E174" s="33" t="n"/>
-      <c r="F174" s="33" t="n"/>
+      <c r="E174" s="32" t="n"/>
+      <c r="F174" s="32" t="n"/>
       <c r="G174" s="31" t="n"/>
       <c r="H174" s="31" t="n"/>
     </row>
     <row r="175" ht="20" customHeight="1">
-      <c r="A175" s="32" t="n"/>
+      <c r="A175" s="31" t="n"/>
       <c r="B175" s="31" t="n"/>
       <c r="C175" s="31" t="n"/>
       <c r="D175" s="31" t="n"/>
-      <c r="E175" s="33" t="n"/>
-      <c r="F175" s="33" t="n"/>
+      <c r="E175" s="32" t="n"/>
+      <c r="F175" s="32" t="n"/>
       <c r="G175" s="31" t="n"/>
       <c r="H175" s="31" t="n"/>
     </row>
     <row r="176" ht="20" customHeight="1">
-      <c r="A176" s="32" t="n"/>
+      <c r="A176" s="31" t="n"/>
       <c r="B176" s="31" t="n"/>
       <c r="C176" s="31" t="n"/>
       <c r="D176" s="31" t="n"/>
-      <c r="E176" s="33" t="n"/>
-      <c r="F176" s="33" t="n"/>
+      <c r="E176" s="32" t="n"/>
+      <c r="F176" s="32" t="n"/>
       <c r="G176" s="31" t="n"/>
       <c r="H176" s="31" t="n"/>
     </row>
     <row r="177" ht="20" customHeight="1">
-      <c r="A177" s="32" t="n"/>
+      <c r="A177" s="31" t="n"/>
       <c r="B177" s="31" t="n"/>
       <c r="C177" s="31" t="n"/>
       <c r="D177" s="31" t="n"/>
-      <c r="E177" s="33" t="n"/>
-      <c r="F177" s="33" t="n"/>
+      <c r="E177" s="32" t="n"/>
+      <c r="F177" s="32" t="n"/>
       <c r="G177" s="31" t="n"/>
       <c r="H177" s="31" t="n"/>
     </row>
     <row r="178" ht="20" customHeight="1">
-      <c r="A178" s="32" t="n"/>
+      <c r="A178" s="31" t="n"/>
       <c r="B178" s="31" t="n"/>
       <c r="C178" s="31" t="n"/>
       <c r="D178" s="31" t="n"/>
-      <c r="E178" s="33" t="n"/>
-      <c r="F178" s="33" t="n"/>
+      <c r="E178" s="32" t="n"/>
+      <c r="F178" s="32" t="n"/>
       <c r="G178" s="31" t="n"/>
       <c r="H178" s="31" t="n"/>
     </row>
     <row r="179" ht="20" customHeight="1">
-      <c r="A179" s="32" t="n"/>
+      <c r="A179" s="31" t="n"/>
       <c r="B179" s="31" t="n"/>
       <c r="C179" s="31" t="n"/>
       <c r="D179" s="31" t="n"/>
-      <c r="E179" s="33" t="n"/>
-      <c r="F179" s="33" t="n"/>
+      <c r="E179" s="32" t="n"/>
+      <c r="F179" s="32" t="n"/>
       <c r="G179" s="31" t="n"/>
       <c r="H179" s="31" t="n"/>
     </row>
     <row r="180" ht="20" customHeight="1">
-      <c r="A180" s="32" t="n"/>
+      <c r="A180" s="31" t="n"/>
       <c r="B180" s="31" t="n"/>
       <c r="C180" s="31" t="n"/>
       <c r="D180" s="31" t="n"/>
-      <c r="E180" s="33" t="n"/>
-      <c r="F180" s="33" t="n"/>
+      <c r="E180" s="32" t="n"/>
+      <c r="F180" s="32" t="n"/>
       <c r="G180" s="31" t="n"/>
       <c r="H180" s="31" t="n"/>
     </row>
     <row r="181" ht="20" customHeight="1">
-      <c r="A181" s="32" t="n"/>
+      <c r="A181" s="31" t="n"/>
       <c r="B181" s="31" t="n"/>
       <c r="C181" s="31" t="n"/>
       <c r="D181" s="31" t="n"/>
-      <c r="E181" s="33" t="n"/>
-      <c r="F181" s="33" t="n"/>
+      <c r="E181" s="32" t="n"/>
+      <c r="F181" s="32" t="n"/>
       <c r="G181" s="31" t="n"/>
       <c r="H181" s="31" t="n"/>
     </row>
     <row r="182" ht="20" customHeight="1">
-      <c r="A182" s="32" t="n"/>
+      <c r="A182" s="31" t="n"/>
       <c r="B182" s="31" t="n"/>
       <c r="C182" s="31" t="n"/>
       <c r="D182" s="31" t="n"/>
-      <c r="E182" s="33" t="n"/>
-      <c r="F182" s="33" t="n"/>
+      <c r="E182" s="32" t="n"/>
+      <c r="F182" s="32" t="n"/>
       <c r="G182" s="31" t="n"/>
       <c r="H182" s="31" t="n"/>
     </row>
     <row r="183" ht="20" customHeight="1">
-      <c r="A183" s="32" t="n"/>
+      <c r="A183" s="31" t="n"/>
       <c r="B183" s="31" t="n"/>
       <c r="C183" s="31" t="n"/>
       <c r="D183" s="31" t="n"/>
-      <c r="E183" s="33" t="n"/>
-      <c r="F183" s="33" t="n"/>
+      <c r="E183" s="32" t="n"/>
+      <c r="F183" s="32" t="n"/>
       <c r="G183" s="31" t="n"/>
       <c r="H183" s="31" t="n"/>
     </row>
     <row r="184" ht="20" customHeight="1">
-      <c r="A184" s="32" t="n"/>
+      <c r="A184" s="31" t="n"/>
       <c r="B184" s="31" t="n"/>
       <c r="C184" s="31" t="n"/>
       <c r="D184" s="31" t="n"/>
-      <c r="E184" s="33" t="n"/>
-      <c r="F184" s="33" t="n"/>
+      <c r="E184" s="32" t="n"/>
+      <c r="F184" s="32" t="n"/>
       <c r="G184" s="31" t="n"/>
       <c r="H184" s="31" t="n"/>
     </row>
     <row r="185" ht="20" customHeight="1">
-      <c r="A185" s="32" t="n"/>
+      <c r="A185" s="31" t="n"/>
       <c r="B185" s="31" t="n"/>
       <c r="C185" s="31" t="n"/>
       <c r="D185" s="31" t="n"/>
-      <c r="E185" s="33" t="n"/>
-      <c r="F185" s="33" t="n"/>
+      <c r="E185" s="32" t="n"/>
+      <c r="F185" s="32" t="n"/>
       <c r="G185" s="31" t="n"/>
       <c r="H185" s="31" t="n"/>
     </row>
     <row r="186" ht="20" customHeight="1">
-      <c r="A186" s="32" t="n"/>
+      <c r="A186" s="31" t="n"/>
       <c r="B186" s="31" t="n"/>
       <c r="C186" s="31" t="n"/>
       <c r="D186" s="31" t="n"/>
-      <c r="E186" s="33" t="n"/>
-      <c r="F186" s="33" t="n"/>
+      <c r="E186" s="32" t="n"/>
+      <c r="F186" s="32" t="n"/>
       <c r="G186" s="31" t="n"/>
       <c r="H186" s="31" t="n"/>
     </row>
     <row r="187" ht="20" customHeight="1">
-      <c r="A187" s="32" t="n"/>
+      <c r="A187" s="31" t="n"/>
       <c r="B187" s="31" t="n"/>
       <c r="C187" s="31" t="n"/>
       <c r="D187" s="31" t="n"/>
-      <c r="E187" s="33" t="n"/>
-      <c r="F187" s="33" t="n"/>
+      <c r="E187" s="32" t="n"/>
+      <c r="F187" s="32" t="n"/>
       <c r="G187" s="31" t="n"/>
       <c r="H187" s="31" t="n"/>
     </row>
     <row r="188" ht="20" customHeight="1">
-      <c r="A188" s="32" t="n"/>
+      <c r="A188" s="31" t="n"/>
       <c r="B188" s="31" t="n"/>
       <c r="C188" s="31" t="n"/>
       <c r="D188" s="31" t="n"/>
-      <c r="E188" s="33" t="n"/>
-      <c r="F188" s="33" t="n"/>
+      <c r="E188" s="32" t="n"/>
+      <c r="F188" s="32" t="n"/>
       <c r="G188" s="31" t="n"/>
       <c r="H188" s="31" t="n"/>
     </row>
     <row r="189" ht="20" customHeight="1">
-      <c r="A189" s="32" t="n"/>
+      <c r="A189" s="31" t="n"/>
       <c r="B189" s="31" t="n"/>
       <c r="C189" s="31" t="n"/>
       <c r="D189" s="31" t="n"/>
-      <c r="E189" s="33" t="n"/>
-      <c r="F189" s="33" t="n"/>
+      <c r="E189" s="32" t="n"/>
+      <c r="F189" s="32" t="n"/>
       <c r="G189" s="31" t="n"/>
       <c r="H189" s="31" t="n"/>
     </row>
     <row r="190" ht="20" customHeight="1">
-      <c r="A190" s="32" t="n"/>
+      <c r="A190" s="31" t="n"/>
       <c r="B190" s="31" t="n"/>
       <c r="C190" s="31" t="n"/>
       <c r="D190" s="31" t="n"/>
-      <c r="E190" s="33" t="n"/>
-      <c r="F190" s="33" t="n"/>
+      <c r="E190" s="32" t="n"/>
+      <c r="F190" s="32" t="n"/>
       <c r="G190" s="31" t="n"/>
       <c r="H190" s="31" t="n"/>
     </row>
     <row r="191" ht="20" customHeight="1">
-      <c r="A191" s="32" t="n"/>
+      <c r="A191" s="31" t="n"/>
       <c r="B191" s="31" t="n"/>
       <c r="C191" s="31" t="n"/>
       <c r="D191" s="31" t="n"/>
-      <c r="E191" s="33" t="n"/>
-      <c r="F191" s="33" t="n"/>
+      <c r="E191" s="32" t="n"/>
+      <c r="F191" s="32" t="n"/>
       <c r="G191" s="31" t="n"/>
       <c r="H191" s="31" t="n"/>
     </row>
     <row r="192" ht="20" customHeight="1">
-      <c r="A192" s="32" t="n"/>
+      <c r="A192" s="31" t="n"/>
       <c r="B192" s="31" t="n"/>
       <c r="C192" s="31" t="n"/>
       <c r="D192" s="31" t="n"/>
-      <c r="E192" s="33" t="n"/>
-      <c r="F192" s="33" t="n"/>
+      <c r="E192" s="32" t="n"/>
+      <c r="F192" s="32" t="n"/>
       <c r="G192" s="31" t="n"/>
       <c r="H192" s="31" t="n"/>
     </row>
     <row r="193" ht="20" customHeight="1">
-      <c r="A193" s="32" t="n"/>
+      <c r="A193" s="31" t="n"/>
       <c r="B193" s="31" t="n"/>
       <c r="C193" s="31" t="n"/>
       <c r="D193" s="31" t="n"/>
-      <c r="E193" s="33" t="n"/>
-      <c r="F193" s="33" t="n"/>
+      <c r="E193" s="32" t="n"/>
+      <c r="F193" s="32" t="n"/>
       <c r="G193" s="31" t="n"/>
       <c r="H193" s="31" t="n"/>
     </row>
     <row r="194" ht="20" customHeight="1">
-      <c r="A194" s="32" t="n"/>
+      <c r="A194" s="31" t="n"/>
       <c r="B194" s="31" t="n"/>
       <c r="C194" s="31" t="n"/>
       <c r="D194" s="31" t="n"/>
-      <c r="E194" s="33" t="n"/>
-      <c r="F194" s="33" t="n"/>
+      <c r="E194" s="32" t="n"/>
+      <c r="F194" s="32" t="n"/>
       <c r="G194" s="31" t="n"/>
       <c r="H194" s="31" t="n"/>
     </row>
     <row r="195" ht="20" customHeight="1">
-      <c r="A195" s="32" t="n"/>
+      <c r="A195" s="31" t="n"/>
       <c r="B195" s="31" t="n"/>
       <c r="C195" s="31" t="n"/>
       <c r="D195" s="31" t="n"/>
-      <c r="E195" s="33" t="n"/>
-      <c r="F195" s="33" t="n"/>
+      <c r="E195" s="32" t="n"/>
+      <c r="F195" s="32" t="n"/>
       <c r="G195" s="31" t="n"/>
       <c r="H195" s="31" t="n"/>
     </row>
     <row r="196" ht="20" customHeight="1">
-      <c r="A196" s="32" t="n"/>
+      <c r="A196" s="31" t="n"/>
       <c r="B196" s="31" t="n"/>
       <c r="C196" s="31" t="n"/>
       <c r="D196" s="31" t="n"/>
-      <c r="E196" s="33" t="n"/>
-      <c r="F196" s="33" t="n"/>
+      <c r="E196" s="32" t="n"/>
+      <c r="F196" s="32" t="n"/>
       <c r="G196" s="31" t="n"/>
       <c r="H196" s="31" t="n"/>
     </row>
     <row r="197" ht="20" customHeight="1">
-      <c r="A197" s="32" t="n"/>
+      <c r="A197" s="31" t="n"/>
       <c r="B197" s="31" t="n"/>
       <c r="C197" s="31" t="n"/>
       <c r="D197" s="31" t="n"/>
-      <c r="E197" s="33" t="n"/>
-      <c r="F197" s="33" t="n"/>
+      <c r="E197" s="32" t="n"/>
+      <c r="F197" s="32" t="n"/>
       <c r="G197" s="31" t="n"/>
       <c r="H197" s="31" t="n"/>
     </row>
     <row r="198" ht="20" customHeight="1">
-      <c r="A198" s="32" t="n"/>
+      <c r="A198" s="31" t="n"/>
       <c r="B198" s="31" t="n"/>
       <c r="C198" s="31" t="n"/>
       <c r="D198" s="31" t="n"/>
-      <c r="E198" s="33" t="n"/>
-      <c r="F198" s="33" t="n"/>
+      <c r="E198" s="32" t="n"/>
+      <c r="F198" s="32" t="n"/>
       <c r="G198" s="31" t="n"/>
       <c r="H198" s="31" t="n"/>
     </row>
     <row r="199" ht="20" customHeight="1">
-      <c r="A199" s="32" t="n"/>
+      <c r="A199" s="31" t="n"/>
       <c r="B199" s="31" t="n"/>
       <c r="C199" s="31" t="n"/>
       <c r="D199" s="31" t="n"/>
-      <c r="E199" s="33" t="n"/>
-      <c r="F199" s="33" t="n"/>
+      <c r="E199" s="32" t="n"/>
+      <c r="F199" s="32" t="n"/>
       <c r="G199" s="31" t="n"/>
       <c r="H199" s="31" t="n"/>
     </row>
     <row r="200" ht="20" customHeight="1">
-      <c r="A200" s="32" t="n"/>
+      <c r="A200" s="31" t="n"/>
       <c r="B200" s="31" t="n"/>
       <c r="C200" s="31" t="n"/>
       <c r="D200" s="31" t="n"/>
-      <c r="E200" s="33" t="n"/>
-      <c r="F200" s="33" t="n"/>
+      <c r="E200" s="32" t="n"/>
+      <c r="F200" s="32" t="n"/>
       <c r="G200" s="31" t="n"/>
       <c r="H200" s="31" t="n"/>
     </row>
     <row r="201" ht="20" customHeight="1">
-      <c r="A201" s="32" t="n"/>
+      <c r="A201" s="31" t="n"/>
       <c r="B201" s="31" t="n"/>
       <c r="C201" s="31" t="n"/>
       <c r="D201" s="31" t="n"/>
-      <c r="E201" s="33" t="n"/>
-      <c r="F201" s="33" t="n"/>
+      <c r="E201" s="32" t="n"/>
+      <c r="F201" s="32" t="n"/>
       <c r="G201" s="31" t="n"/>
       <c r="H201" s="31" t="n"/>
     </row>
     <row r="202" ht="20" customHeight="1">
-      <c r="A202" s="32" t="n"/>
+      <c r="A202" s="31" t="n"/>
       <c r="B202" s="31" t="n"/>
       <c r="C202" s="31" t="n"/>
       <c r="D202" s="31" t="n"/>
-      <c r="E202" s="33" t="n"/>
-      <c r="F202" s="33" t="n"/>
+      <c r="E202" s="32" t="n"/>
+      <c r="F202" s="32" t="n"/>
       <c r="G202" s="31" t="n"/>
       <c r="H202" s="31" t="n"/>
     </row>
     <row r="203" ht="20" customHeight="1">
-      <c r="A203" s="32" t="n"/>
+      <c r="A203" s="31" t="n"/>
       <c r="B203" s="31" t="n"/>
       <c r="C203" s="31" t="n"/>
       <c r="D203" s="31" t="n"/>
-      <c r="E203" s="33" t="n"/>
-      <c r="F203" s="33" t="n"/>
+      <c r="E203" s="32" t="n"/>
+      <c r="F203" s="32" t="n"/>
       <c r="G203" s="31" t="n"/>
       <c r="H203" s="31" t="n"/>
     </row>
     <row r="204" ht="20" customHeight="1">
-      <c r="A204" s="32" t="n"/>
+      <c r="A204" s="31" t="n"/>
       <c r="B204" s="31" t="n"/>
       <c r="C204" s="31" t="n"/>
       <c r="D204" s="31" t="n"/>
-      <c r="E204" s="33" t="n"/>
-      <c r="F204" s="33" t="n"/>
+      <c r="E204" s="32" t="n"/>
+      <c r="F204" s="32" t="n"/>
       <c r="G204" s="31" t="n"/>
       <c r="H204" s="31" t="n"/>
     </row>
     <row r="205" ht="20" customHeight="1">
-      <c r="A205" s="32" t="n"/>
+      <c r="A205" s="31" t="n"/>
       <c r="B205" s="31" t="n"/>
       <c r="C205" s="31" t="n"/>
       <c r="D205" s="31" t="n"/>
-      <c r="E205" s="33" t="n"/>
-      <c r="F205" s="33" t="n"/>
+      <c r="E205" s="32" t="n"/>
+      <c r="F205" s="32" t="n"/>
       <c r="G205" s="31" t="n"/>
       <c r="H205" s="31" t="n"/>
     </row>
     <row r="206" ht="20" customHeight="1">
-      <c r="A206" s="32" t="n"/>
+      <c r="A206" s="31" t="n"/>
       <c r="B206" s="31" t="n"/>
       <c r="C206" s="31" t="n"/>
       <c r="D206" s="31" t="n"/>
-      <c r="E206" s="33" t="n"/>
-      <c r="F206" s="33" t="n"/>
+      <c r="E206" s="32" t="n"/>
+      <c r="F206" s="32" t="n"/>
       <c r="G206" s="31" t="n"/>
       <c r="H206" s="31" t="n"/>
     </row>
     <row r="207" ht="20" customHeight="1">
-      <c r="A207" s="32" t="n"/>
+      <c r="A207" s="31" t="n"/>
       <c r="B207" s="31" t="n"/>
       <c r="C207" s="31" t="n"/>
       <c r="D207" s="31" t="n"/>
-      <c r="E207" s="33" t="n"/>
-      <c r="F207" s="33" t="n"/>
+      <c r="E207" s="32" t="n"/>
+      <c r="F207" s="32" t="n"/>
       <c r="G207" s="31" t="n"/>
       <c r="H207" s="31" t="n"/>
     </row>
     <row r="208" ht="20" customHeight="1">
-      <c r="A208" s="32" t="n"/>
+      <c r="A208" s="31" t="n"/>
       <c r="B208" s="31" t="n"/>
       <c r="C208" s="31" t="n"/>
       <c r="D208" s="31" t="n"/>
-      <c r="E208" s="33" t="n"/>
-      <c r="F208" s="33" t="n"/>
+      <c r="E208" s="32" t="n"/>
+      <c r="F208" s="32" t="n"/>
       <c r="G208" s="31" t="n"/>
       <c r="H208" s="31" t="n"/>
     </row>
     <row r="209" ht="20" customHeight="1">
-      <c r="A209" s="32" t="n"/>
+      <c r="A209" s="31" t="n"/>
       <c r="B209" s="31" t="n"/>
       <c r="C209" s="31" t="n"/>
       <c r="D209" s="31" t="n"/>
-      <c r="E209" s="33" t="n"/>
-      <c r="F209" s="33" t="n"/>
+      <c r="E209" s="32" t="n"/>
+      <c r="F209" s="32" t="n"/>
       <c r="G209" s="31" t="n"/>
       <c r="H209" s="31" t="n"/>
     </row>
     <row r="210" ht="20" customHeight="1">
-      <c r="A210" s="32" t="n"/>
+      <c r="A210" s="31" t="n"/>
       <c r="B210" s="31" t="n"/>
       <c r="C210" s="31" t="n"/>
       <c r="D210" s="31" t="n"/>
-      <c r="E210" s="33" t="n"/>
-      <c r="F210" s="33" t="n"/>
+      <c r="E210" s="32" t="n"/>
+      <c r="F210" s="32" t="n"/>
       <c r="G210" s="31" t="n"/>
       <c r="H210" s="31" t="n"/>
     </row>
     <row r="211" ht="20" customHeight="1">
-      <c r="A211" s="32" t="n"/>
+      <c r="A211" s="31" t="n"/>
       <c r="B211" s="31" t="n"/>
       <c r="C211" s="31" t="n"/>
       <c r="D211" s="31" t="n"/>
-      <c r="E211" s="33" t="n"/>
-      <c r="F211" s="33" t="n"/>
+      <c r="E211" s="32" t="n"/>
+      <c r="F211" s="32" t="n"/>
       <c r="G211" s="31" t="n"/>
       <c r="H211" s="31" t="n"/>
     </row>
     <row r="212" ht="20" customHeight="1">
-      <c r="A212" s="32" t="n"/>
+      <c r="A212" s="31" t="n"/>
       <c r="B212" s="31" t="n"/>
       <c r="C212" s="31" t="n"/>
       <c r="D212" s="31" t="n"/>
-      <c r="E212" s="33" t="n"/>
-      <c r="F212" s="33" t="n"/>
+      <c r="E212" s="32" t="n"/>
+      <c r="F212" s="32" t="n"/>
       <c r="G212" s="31" t="n"/>
       <c r="H212" s="31" t="n"/>
     </row>
     <row r="213" ht="20" customHeight="1">
-      <c r="A213" s="32" t="n"/>
+      <c r="A213" s="31" t="n"/>
       <c r="B213" s="31" t="n"/>
       <c r="C213" s="31" t="n"/>
       <c r="D213" s="31" t="n"/>
-      <c r="E213" s="33" t="n"/>
-      <c r="F213" s="33" t="n"/>
+      <c r="E213" s="32" t="n"/>
+      <c r="F213" s="32" t="n"/>
       <c r="G213" s="31" t="n"/>
       <c r="H213" s="31" t="n"/>
     </row>
     <row r="214" ht="20" customHeight="1">
-      <c r="A214" s="32" t="n"/>
+      <c r="A214" s="31" t="n"/>
       <c r="B214" s="31" t="n"/>
       <c r="C214" s="31" t="n"/>
       <c r="D214" s="31" t="n"/>
-      <c r="E214" s="33" t="n"/>
-      <c r="F214" s="33" t="n"/>
+      <c r="E214" s="32" t="n"/>
+      <c r="F214" s="32" t="n"/>
       <c r="G214" s="31" t="n"/>
       <c r="H214" s="31" t="n"/>
     </row>
     <row r="215" ht="20" customHeight="1">
-      <c r="A215" s="32" t="n"/>
+      <c r="A215" s="31" t="n"/>
       <c r="B215" s="31" t="n"/>
       <c r="C215" s="31" t="n"/>
       <c r="D215" s="31" t="n"/>
-      <c r="E215" s="33" t="n"/>
-      <c r="F215" s="33" t="n"/>
+      <c r="E215" s="32" t="n"/>
+      <c r="F215" s="32" t="n"/>
       <c r="G215" s="31" t="n"/>
       <c r="H215" s="31" t="n"/>
     </row>
     <row r="216" ht="20" customHeight="1">
-      <c r="A216" s="32" t="n"/>
+      <c r="A216" s="31" t="n"/>
       <c r="B216" s="31" t="n"/>
       <c r="C216" s="31" t="n"/>
       <c r="D216" s="31" t="n"/>
-      <c r="E216" s="33" t="n"/>
-      <c r="F216" s="33" t="n"/>
+      <c r="E216" s="32" t="n"/>
+      <c r="F216" s="32" t="n"/>
       <c r="G216" s="31" t="n"/>
       <c r="H216" s="31" t="n"/>
     </row>
     <row r="217" ht="20" customHeight="1">
-      <c r="A217" s="32" t="n"/>
+      <c r="A217" s="31" t="n"/>
       <c r="B217" s="31" t="n"/>
       <c r="C217" s="31" t="n"/>
       <c r="D217" s="31" t="n"/>
-      <c r="E217" s="33" t="n"/>
-      <c r="F217" s="33" t="n"/>
+      <c r="E217" s="32" t="n"/>
+      <c r="F217" s="32" t="n"/>
       <c r="G217" s="31" t="n"/>
       <c r="H217" s="31" t="n"/>
     </row>
     <row r="218" ht="20" customHeight="1">
-      <c r="A218" s="32" t="n"/>
+      <c r="A218" s="31" t="n"/>
       <c r="B218" s="31" t="n"/>
       <c r="C218" s="31" t="n"/>
       <c r="D218" s="31" t="n"/>
-      <c r="E218" s="33" t="n"/>
-      <c r="F218" s="33" t="n"/>
+      <c r="E218" s="32" t="n"/>
+      <c r="F218" s="32" t="n"/>
       <c r="G218" s="31" t="n"/>
       <c r="H218" s="31" t="n"/>
     </row>
     <row r="219" ht="20" customHeight="1">
-      <c r="A219" s="32" t="n"/>
+      <c r="A219" s="31" t="n"/>
       <c r="B219" s="31" t="n"/>
       <c r="C219" s="31" t="n"/>
       <c r="D219" s="31" t="n"/>
-      <c r="E219" s="33" t="n"/>
-      <c r="F219" s="33" t="n"/>
+      <c r="E219" s="32" t="n"/>
+      <c r="F219" s="32" t="n"/>
       <c r="G219" s="31" t="n"/>
       <c r="H219" s="31" t="n"/>
     </row>
     <row r="220" ht="20" customHeight="1">
-      <c r="A220" s="32" t="n"/>
+      <c r="A220" s="31" t="n"/>
       <c r="B220" s="31" t="n"/>
       <c r="C220" s="31" t="n"/>
       <c r="D220" s="31" t="n"/>
-      <c r="E220" s="33" t="n"/>
-      <c r="F220" s="33" t="n"/>
+      <c r="E220" s="32" t="n"/>
+      <c r="F220" s="32" t="n"/>
       <c r="G220" s="31" t="n"/>
       <c r="H220" s="31" t="n"/>
     </row>
     <row r="221" ht="20" customHeight="1">
-      <c r="A221" s="32" t="n"/>
+      <c r="A221" s="31" t="n"/>
       <c r="B221" s="31" t="n"/>
       <c r="C221" s="31" t="n"/>
       <c r="D221" s="31" t="n"/>
-      <c r="E221" s="33" t="n"/>
-      <c r="F221" s="33" t="n"/>
+      <c r="E221" s="32" t="n"/>
+      <c r="F221" s="32" t="n"/>
       <c r="G221" s="31" t="n"/>
       <c r="H221" s="31" t="n"/>
     </row>
     <row r="222" ht="20" customHeight="1">
-      <c r="A222" s="32" t="n"/>
+      <c r="A222" s="31" t="n"/>
       <c r="B222" s="31" t="n"/>
       <c r="C222" s="31" t="n"/>
       <c r="D222" s="31" t="n"/>
-      <c r="E222" s="33" t="n"/>
-      <c r="F222" s="33" t="n"/>
+      <c r="E222" s="32" t="n"/>
+      <c r="F222" s="32" t="n"/>
       <c r="G222" s="31" t="n"/>
       <c r="H222" s="31" t="n"/>
     </row>
     <row r="223" ht="20" customHeight="1">
-      <c r="A223" s="32" t="n"/>
+      <c r="A223" s="31" t="n"/>
       <c r="B223" s="31" t="n"/>
       <c r="C223" s="31" t="n"/>
       <c r="D223" s="31" t="n"/>
-      <c r="E223" s="33" t="n"/>
-      <c r="F223" s="33" t="n"/>
+      <c r="E223" s="32" t="n"/>
+      <c r="F223" s="32" t="n"/>
       <c r="G223" s="31" t="n"/>
       <c r="H223" s="31" t="n"/>
     </row>
     <row r="224" ht="20" customHeight="1">
-      <c r="A224" s="32" t="n"/>
+      <c r="A224" s="31" t="n"/>
       <c r="B224" s="31" t="n"/>
       <c r="C224" s="31" t="n"/>
       <c r="D224" s="31" t="n"/>
-      <c r="E224" s="33" t="n"/>
-      <c r="F224" s="33" t="n"/>
+      <c r="E224" s="32" t="n"/>
+      <c r="F224" s="32" t="n"/>
       <c r="G224" s="31" t="n"/>
       <c r="H224" s="31" t="n"/>
     </row>
     <row r="225" ht="20" customHeight="1">
-      <c r="A225" s="32" t="n"/>
+      <c r="A225" s="31" t="n"/>
       <c r="B225" s="31" t="n"/>
       <c r="C225" s="31" t="n"/>
       <c r="D225" s="31" t="n"/>
-      <c r="E225" s="33" t="n"/>
-      <c r="F225" s="33" t="n"/>
+      <c r="E225" s="32" t="n"/>
+      <c r="F225" s="32" t="n"/>
       <c r="G225" s="31" t="n"/>
       <c r="H225" s="31" t="n"/>
     </row>
     <row r="226" ht="20" customHeight="1">
-      <c r="A226" s="32" t="n"/>
+      <c r="A226" s="31" t="n"/>
       <c r="B226" s="31" t="n"/>
       <c r="C226" s="31" t="n"/>
       <c r="D226" s="31" t="n"/>
-      <c r="E226" s="33" t="n"/>
-      <c r="F226" s="33" t="n"/>
+      <c r="E226" s="32" t="n"/>
+      <c r="F226" s="32" t="n"/>
       <c r="G226" s="31" t="n"/>
       <c r="H226" s="31" t="n"/>
     </row>
     <row r="227" ht="20" customHeight="1">
-      <c r="A227" s="32" t="n"/>
+      <c r="A227" s="31" t="n"/>
       <c r="B227" s="31" t="n"/>
       <c r="C227" s="31" t="n"/>
       <c r="D227" s="31" t="n"/>
-      <c r="E227" s="33" t="n"/>
-      <c r="F227" s="33" t="n"/>
+      <c r="E227" s="32" t="n"/>
+      <c r="F227" s="32" t="n"/>
       <c r="G227" s="31" t="n"/>
       <c r="H227" s="31" t="n"/>
     </row>
     <row r="228" ht="20" customHeight="1">
-      <c r="A228" s="32" t="n"/>
+      <c r="A228" s="31" t="n"/>
       <c r="B228" s="31" t="n"/>
       <c r="C228" s="31" t="n"/>
       <c r="D228" s="31" t="n"/>
-      <c r="E228" s="33" t="n"/>
-      <c r="F228" s="33" t="n"/>
+      <c r="E228" s="32" t="n"/>
+      <c r="F228" s="32" t="n"/>
       <c r="G228" s="31" t="n"/>
       <c r="H228" s="31" t="n"/>
     </row>
     <row r="229" ht="20" customHeight="1">
-      <c r="A229" s="32" t="n"/>
+      <c r="A229" s="31" t="n"/>
       <c r="B229" s="31" t="n"/>
       <c r="C229" s="31" t="n"/>
       <c r="D229" s="31" t="n"/>
-      <c r="E229" s="33" t="n"/>
-      <c r="F229" s="33" t="n"/>
+      <c r="E229" s="32" t="n"/>
+      <c r="F229" s="32" t="n"/>
       <c r="G229" s="31" t="n"/>
       <c r="H229" s="31" t="n"/>
     </row>
     <row r="230" ht="20" customHeight="1">
-      <c r="A230" s="32" t="n"/>
+      <c r="A230" s="31" t="n"/>
       <c r="B230" s="31" t="n"/>
       <c r="C230" s="31" t="n"/>
       <c r="D230" s="31" t="n"/>
-      <c r="E230" s="33" t="n"/>
-      <c r="F230" s="33" t="n"/>
+      <c r="E230" s="32" t="n"/>
+      <c r="F230" s="32" t="n"/>
       <c r="G230" s="31" t="n"/>
       <c r="H230" s="31" t="n"/>
     </row>
     <row r="231" ht="20" customHeight="1">
-      <c r="A231" s="32" t="n"/>
+      <c r="A231" s="31" t="n"/>
       <c r="B231" s="31" t="n"/>
       <c r="C231" s="31" t="n"/>
       <c r="D231" s="31" t="n"/>
-      <c r="E231" s="33" t="n"/>
-      <c r="F231" s="33" t="n"/>
+      <c r="E231" s="32" t="n"/>
+      <c r="F231" s="32" t="n"/>
       <c r="G231" s="31" t="n"/>
       <c r="H231" s="31" t="n"/>
     </row>
     <row r="232" ht="20" customHeight="1">
-      <c r="A232" s="32" t="n"/>
+      <c r="A232" s="31" t="n"/>
       <c r="B232" s="31" t="n"/>
       <c r="C232" s="31" t="n"/>
       <c r="D232" s="31" t="n"/>
-      <c r="E232" s="33" t="n"/>
-      <c r="F232" s="33" t="n"/>
+      <c r="E232" s="32" t="n"/>
+      <c r="F232" s="32" t="n"/>
       <c r="G232" s="31" t="n"/>
       <c r="H232" s="31" t="n"/>
     </row>
     <row r="233" ht="20" customHeight="1">
-      <c r="A233" s="32" t="n"/>
+      <c r="A233" s="31" t="n"/>
       <c r="B233" s="31" t="n"/>
       <c r="C233" s="31" t="n"/>
       <c r="D233" s="31" t="n"/>
-      <c r="E233" s="33" t="n"/>
-      <c r="F233" s="33" t="n"/>
+      <c r="E233" s="32" t="n"/>
+      <c r="F233" s="32" t="n"/>
       <c r="G233" s="31" t="n"/>
       <c r="H233" s="31" t="n"/>
     </row>
     <row r="234" ht="20" customHeight="1">
-      <c r="A234" s="32" t="n"/>
+      <c r="A234" s="31" t="n"/>
       <c r="B234" s="31" t="n"/>
       <c r="C234" s="31" t="n"/>
       <c r="D234" s="31" t="n"/>
-      <c r="E234" s="33" t="n"/>
-      <c r="F234" s="33" t="n"/>
+      <c r="E234" s="32" t="n"/>
+      <c r="F234" s="32" t="n"/>
       <c r="G234" s="31" t="n"/>
       <c r="H234" s="31" t="n"/>
     </row>
     <row r="235" ht="20" customHeight="1">
-      <c r="A235" s="32" t="n"/>
+      <c r="A235" s="31" t="n"/>
       <c r="B235" s="31" t="n"/>
       <c r="C235" s="31" t="n"/>
       <c r="D235" s="31" t="n"/>
-      <c r="E235" s="33" t="n"/>
-      <c r="F235" s="33" t="n"/>
+      <c r="E235" s="32" t="n"/>
+      <c r="F235" s="32" t="n"/>
       <c r="G235" s="31" t="n"/>
       <c r="H235" s="31" t="n"/>
     </row>
     <row r="236" ht="20" customHeight="1">
-      <c r="A236" s="32" t="n"/>
+      <c r="A236" s="31" t="n"/>
       <c r="B236" s="31" t="n"/>
       <c r="C236" s="31" t="n"/>
       <c r="D236" s="31" t="n"/>
-      <c r="E236" s="33" t="n"/>
-      <c r="F236" s="33" t="n"/>
+      <c r="E236" s="32" t="n"/>
+      <c r="F236" s="32" t="n"/>
       <c r="G236" s="31" t="n"/>
       <c r="H236" s="31" t="n"/>
     </row>
     <row r="237" ht="20" customHeight="1">
-      <c r="A237" s="32" t="n"/>
+      <c r="A237" s="31" t="n"/>
       <c r="B237" s="31" t="n"/>
       <c r="C237" s="31" t="n"/>
       <c r="D237" s="31" t="n"/>
-      <c r="E237" s="33" t="n"/>
-      <c r="F237" s="33" t="n"/>
+      <c r="E237" s="32" t="n"/>
+      <c r="F237" s="32" t="n"/>
       <c r="G237" s="31" t="n"/>
       <c r="H237" s="31" t="n"/>
     </row>
     <row r="238" ht="20" customHeight="1">
-      <c r="A238" s="32" t="n"/>
+      <c r="A238" s="31" t="n"/>
       <c r="B238" s="31" t="n"/>
       <c r="C238" s="31" t="n"/>
       <c r="D238" s="31" t="n"/>
-      <c r="E238" s="33" t="n"/>
-      <c r="F238" s="33" t="n"/>
+      <c r="E238" s="32" t="n"/>
+      <c r="F238" s="32" t="n"/>
       <c r="G238" s="31" t="n"/>
       <c r="H238" s="31" t="n"/>
     </row>
     <row r="239" ht="20" customHeight="1">
-      <c r="A239" s="32" t="n"/>
+      <c r="A239" s="31" t="n"/>
       <c r="B239" s="31" t="n"/>
       <c r="C239" s="31" t="n"/>
       <c r="D239" s="31" t="n"/>
-      <c r="E239" s="33" t="n"/>
-      <c r="F239" s="33" t="n"/>
+      <c r="E239" s="32" t="n"/>
+      <c r="F239" s="32" t="n"/>
       <c r="G239" s="31" t="n"/>
       <c r="H239" s="31" t="n"/>
     </row>
     <row r="240" ht="20" customHeight="1">
-      <c r="A240" s="32" t="n"/>
+      <c r="A240" s="31" t="n"/>
       <c r="B240" s="31" t="n"/>
       <c r="C240" s="31" t="n"/>
       <c r="D240" s="31" t="n"/>
-      <c r="E240" s="33" t="n"/>
-      <c r="F240" s="33" t="n"/>
+      <c r="E240" s="32" t="n"/>
+      <c r="F240" s="32" t="n"/>
       <c r="G240" s="31" t="n"/>
       <c r="H240" s="31" t="n"/>
     </row>
     <row r="241" ht="20" customHeight="1">
-      <c r="A241" s="32" t="n"/>
+      <c r="A241" s="31" t="n"/>
       <c r="B241" s="31" t="n"/>
       <c r="C241" s="31" t="n"/>
       <c r="D241" s="31" t="n"/>
-      <c r="E241" s="33" t="n"/>
-      <c r="F241" s="33" t="n"/>
+      <c r="E241" s="32" t="n"/>
+      <c r="F241" s="32" t="n"/>
       <c r="G241" s="31" t="n"/>
       <c r="H241" s="31" t="n"/>
     </row>
     <row r="242" ht="20" customHeight="1">
-      <c r="A242" s="32" t="n"/>
+      <c r="A242" s="31" t="n"/>
       <c r="B242" s="31" t="n"/>
       <c r="C242" s="31" t="n"/>
       <c r="D242" s="31" t="n"/>
-      <c r="E242" s="33" t="n"/>
-      <c r="F242" s="33" t="n"/>
+      <c r="E242" s="32" t="n"/>
+      <c r="F242" s="32" t="n"/>
       <c r="G242" s="31" t="n"/>
       <c r="H242" s="31" t="n"/>
     </row>
     <row r="243" ht="20" customHeight="1">
-      <c r="A243" s="32" t="n"/>
+      <c r="A243" s="31" t="n"/>
       <c r="B243" s="31" t="n"/>
       <c r="C243" s="31" t="n"/>
       <c r="D243" s="31" t="n"/>
-      <c r="E243" s="33" t="n"/>
-      <c r="F243" s="33" t="n"/>
+      <c r="E243" s="32" t="n"/>
+      <c r="F243" s="32" t="n"/>
       <c r="G243" s="31" t="n"/>
       <c r="H243" s="31" t="n"/>
     </row>
     <row r="244" ht="20" customHeight="1">
-      <c r="A244" s="32" t="n"/>
+      <c r="A244" s="31" t="n"/>
       <c r="B244" s="31" t="n"/>
       <c r="C244" s="31" t="n"/>
       <c r="D244" s="31" t="n"/>
-      <c r="E244" s="33" t="n"/>
-      <c r="F244" s="33" t="n"/>
+      <c r="E244" s="32" t="n"/>
+      <c r="F244" s="32" t="n"/>
       <c r="G244" s="31" t="n"/>
       <c r="H244" s="31" t="n"/>
     </row>
     <row r="245" ht="20" customHeight="1">
-      <c r="A245" s="32" t="n"/>
+      <c r="A245" s="31" t="n"/>
       <c r="B245" s="31" t="n"/>
       <c r="C245" s="31" t="n"/>
       <c r="D245" s="31" t="n"/>
-      <c r="E245" s="33" t="n"/>
-      <c r="F245" s="33" t="n"/>
+      <c r="E245" s="32" t="n"/>
+      <c r="F245" s="32" t="n"/>
       <c r="G245" s="31" t="n"/>
       <c r="H245" s="31" t="n"/>
     </row>
     <row r="246" ht="20" customHeight="1">
-      <c r="A246" s="32" t="n"/>
+      <c r="A246" s="31" t="n"/>
       <c r="B246" s="31" t="n"/>
       <c r="C246" s="31" t="n"/>
       <c r="D246" s="31" t="n"/>
-      <c r="E246" s="33" t="n"/>
-      <c r="F246" s="33" t="n"/>
+      <c r="E246" s="32" t="n"/>
+      <c r="F246" s="32" t="n"/>
       <c r="G246" s="31" t="n"/>
       <c r="H246" s="31" t="n"/>
     </row>
     <row r="247" ht="20" customHeight="1">
-      <c r="A247" s="32" t="n"/>
+      <c r="A247" s="31" t="n"/>
       <c r="B247" s="31" t="n"/>
       <c r="C247" s="31" t="n"/>
       <c r="D247" s="31" t="n"/>
-      <c r="E247" s="33" t="n"/>
-      <c r="F247" s="33" t="n"/>
+      <c r="E247" s="32" t="n"/>
+      <c r="F247" s="32" t="n"/>
       <c r="G247" s="31" t="n"/>
       <c r="H247" s="31" t="n"/>
     </row>
     <row r="248" ht="20" customHeight="1">
-      <c r="A248" s="32" t="n"/>
+      <c r="A248" s="31" t="n"/>
       <c r="B248" s="31" t="n"/>
       <c r="C248" s="31" t="n"/>
       <c r="D248" s="31" t="n"/>
-      <c r="E248" s="33" t="n"/>
-      <c r="F248" s="33" t="n"/>
+      <c r="E248" s="32" t="n"/>
+      <c r="F248" s="32" t="n"/>
       <c r="G248" s="31" t="n"/>
       <c r="H248" s="31" t="n"/>
     </row>
     <row r="249" ht="20" customHeight="1">
-      <c r="A249" s="32" t="n"/>
+      <c r="A249" s="31" t="n"/>
       <c r="B249" s="31" t="n"/>
       <c r="C249" s="31" t="n"/>
       <c r="D249" s="31" t="n"/>
-      <c r="E249" s="33" t="n"/>
-      <c r="F249" s="33" t="n"/>
+      <c r="E249" s="32" t="n"/>
+      <c r="F249" s="32" t="n"/>
       <c r="G249" s="31" t="n"/>
       <c r="H249" s="31" t="n"/>
     </row>
     <row r="250" ht="20" customHeight="1">
-      <c r="A250" s="32" t="n"/>
+      <c r="A250" s="31" t="n"/>
       <c r="B250" s="31" t="n"/>
       <c r="C250" s="31" t="n"/>
       <c r="D250" s="31" t="n"/>
-      <c r="E250" s="33" t="n"/>
-      <c r="F250" s="33" t="n"/>
+      <c r="E250" s="32" t="n"/>
+      <c r="F250" s="32" t="n"/>
       <c r="G250" s="31" t="n"/>
       <c r="H250" s="31" t="n"/>
     </row>
     <row r="251" ht="20" customHeight="1">
-      <c r="A251" s="32" t="n"/>
+      <c r="A251" s="31" t="n"/>
       <c r="B251" s="31" t="n"/>
       <c r="C251" s="31" t="n"/>
       <c r="D251" s="31" t="n"/>
-      <c r="E251" s="33" t="n"/>
-      <c r="F251" s="33" t="n"/>
+      <c r="E251" s="32" t="n"/>
+      <c r="F251" s="32" t="n"/>
       <c r="G251" s="31" t="n"/>
       <c r="H251" s="31" t="n"/>
     </row>
     <row r="252" ht="20" customHeight="1">
-      <c r="A252" s="32" t="n"/>
+      <c r="A252" s="31" t="n"/>
       <c r="B252" s="31" t="n"/>
       <c r="C252" s="31" t="n"/>
       <c r="D252" s="31" t="n"/>
-      <c r="E252" s="33" t="n"/>
-      <c r="F252" s="33" t="n"/>
+      <c r="E252" s="32" t="n"/>
+      <c r="F252" s="32" t="n"/>
       <c r="G252" s="31" t="n"/>
       <c r="H252" s="31" t="n"/>
     </row>
     <row r="253" ht="20" customHeight="1">
-      <c r="A253" s="32" t="n"/>
+      <c r="A253" s="31" t="n"/>
       <c r="B253" s="31" t="n"/>
       <c r="C253" s="31" t="n"/>
       <c r="D253" s="31" t="n"/>
-      <c r="E253" s="33" t="n"/>
-      <c r="F253" s="33" t="n"/>
+      <c r="E253" s="32" t="n"/>
+      <c r="F253" s="32" t="n"/>
       <c r="G253" s="31" t="n"/>
       <c r="H253" s="31" t="n"/>
     </row>
     <row r="254" ht="20" customHeight="1">
-      <c r="A254" s="32" t="n"/>
+      <c r="A254" s="31" t="n"/>
       <c r="B254" s="31" t="n"/>
       <c r="C254" s="31" t="n"/>
       <c r="D254" s="31" t="n"/>
-      <c r="E254" s="33" t="n"/>
-      <c r="F254" s="33" t="n"/>
+      <c r="E254" s="32" t="n"/>
+      <c r="F254" s="32" t="n"/>
       <c r="G254" s="31" t="n"/>
       <c r="H254" s="31" t="n"/>
     </row>
     <row r="255" ht="20" customHeight="1">
-      <c r="A255" s="32" t="n"/>
+      <c r="A255" s="31" t="n"/>
       <c r="B255" s="31" t="n"/>
       <c r="C255" s="31" t="n"/>
       <c r="D255" s="31" t="n"/>
-      <c r="E255" s="33" t="n"/>
-      <c r="F255" s="33" t="n"/>
+      <c r="E255" s="32" t="n"/>
+      <c r="F255" s="32" t="n"/>
       <c r="G255" s="31" t="n"/>
       <c r="H255" s="31" t="n"/>
     </row>
     <row r="256" ht="20" customHeight="1">
-      <c r="A256" s="32" t="n"/>
+      <c r="A256" s="31" t="n"/>
       <c r="B256" s="31" t="n"/>
       <c r="C256" s="31" t="n"/>
       <c r="D256" s="31" t="n"/>
-      <c r="E256" s="33" t="n"/>
-      <c r="F256" s="33" t="n"/>
+      <c r="E256" s="32" t="n"/>
+      <c r="F256" s="32" t="n"/>
       <c r="G256" s="31" t="n"/>
       <c r="H256" s="31" t="n"/>
     </row>
     <row r="257" ht="20" customHeight="1">
-      <c r="A257" s="32" t="n"/>
+      <c r="A257" s="31" t="n"/>
       <c r="B257" s="31" t="n"/>
       <c r="C257" s="31" t="n"/>
       <c r="D257" s="31" t="n"/>
-      <c r="E257" s="33" t="n"/>
-      <c r="F257" s="33" t="n"/>
+      <c r="E257" s="32" t="n"/>
+      <c r="F257" s="32" t="n"/>
       <c r="G257" s="31" t="n"/>
       <c r="H257" s="31" t="n"/>
     </row>
     <row r="258" ht="20" customHeight="1">
-      <c r="A258" s="32" t="n"/>
+      <c r="A258" s="31" t="n"/>
       <c r="B258" s="31" t="n"/>
       <c r="C258" s="31" t="n"/>
       <c r="D258" s="31" t="n"/>
-      <c r="E258" s="33" t="n"/>
-      <c r="F258" s="33" t="n"/>
+      <c r="E258" s="32" t="n"/>
+      <c r="F258" s="32" t="n"/>
       <c r="G258" s="31" t="n"/>
       <c r="H258" s="31" t="n"/>
     </row>
     <row r="259" ht="20" customHeight="1">
-      <c r="A259" s="32" t="n"/>
+      <c r="A259" s="31" t="n"/>
       <c r="B259" s="31" t="n"/>
       <c r="C259" s="31" t="n"/>
       <c r="D259" s="31" t="n"/>
-      <c r="E259" s="33" t="n"/>
-      <c r="F259" s="33" t="n"/>
+      <c r="E259" s="32" t="n"/>
+      <c r="F259" s="32" t="n"/>
       <c r="G259" s="31" t="n"/>
       <c r="H259" s="31" t="n"/>
     </row>
     <row r="260" ht="20" customHeight="1">
-      <c r="A260" s="32" t="n"/>
+      <c r="A260" s="31" t="n"/>
       <c r="B260" s="31" t="n"/>
       <c r="C260" s="31" t="n"/>
       <c r="D260" s="31" t="n"/>
-      <c r="E260" s="33" t="n"/>
-      <c r="F260" s="33" t="n"/>
+      <c r="E260" s="32" t="n"/>
+      <c r="F260" s="32" t="n"/>
       <c r="G260" s="31" t="n"/>
       <c r="H260" s="31" t="n"/>
     </row>
     <row r="261" ht="20" customHeight="1">
-      <c r="A261" s="32" t="n"/>
+      <c r="A261" s="31" t="n"/>
       <c r="B261" s="31" t="n"/>
       <c r="C261" s="31" t="n"/>
       <c r="D261" s="31" t="n"/>
-      <c r="E261" s="33" t="n"/>
-      <c r="F261" s="33" t="n"/>
+      <c r="E261" s="32" t="n"/>
+      <c r="F261" s="32" t="n"/>
       <c r="G261" s="31" t="n"/>
       <c r="H261" s="31" t="n"/>
     </row>
     <row r="262" ht="20" customHeight="1">
-      <c r="A262" s="32" t="n"/>
+      <c r="A262" s="31" t="n"/>
       <c r="B262" s="31" t="n"/>
       <c r="C262" s="31" t="n"/>
       <c r="D262" s="31" t="n"/>
-      <c r="E262" s="33" t="n"/>
-      <c r="F262" s="33" t="n"/>
+      <c r="E262" s="32" t="n"/>
+      <c r="F262" s="32" t="n"/>
       <c r="G262" s="31" t="n"/>
       <c r="H262" s="31" t="n"/>
     </row>
     <row r="263" ht="20" customHeight="1">
-      <c r="A263" s="32" t="n"/>
+      <c r="A263" s="31" t="n"/>
       <c r="B263" s="31" t="n"/>
       <c r="C263" s="31" t="n"/>
       <c r="D263" s="31" t="n"/>
-      <c r="E263" s="33" t="n"/>
-      <c r="F263" s="33" t="n"/>
+      <c r="E263" s="32" t="n"/>
+      <c r="F263" s="32" t="n"/>
       <c r="G263" s="31" t="n"/>
       <c r="H263" s="31" t="n"/>
     </row>
     <row r="264" ht="20" customHeight="1">
-      <c r="A264" s="32" t="n"/>
+      <c r="A264" s="31" t="n"/>
       <c r="B264" s="31" t="n"/>
       <c r="C264" s="31" t="n"/>
       <c r="D264" s="31" t="n"/>
-      <c r="E264" s="33" t="n"/>
-      <c r="F264" s="33" t="n"/>
+      <c r="E264" s="32" t="n"/>
+      <c r="F264" s="32" t="n"/>
       <c r="G264" s="31" t="n"/>
       <c r="H264" s="31" t="n"/>
     </row>
     <row r="265" ht="20" customHeight="1">
-      <c r="A265" s="32" t="n"/>
+      <c r="A265" s="31" t="n"/>
       <c r="B265" s="31" t="n"/>
       <c r="C265" s="31" t="n"/>
       <c r="D265" s="31" t="n"/>
-      <c r="E265" s="33" t="n"/>
-      <c r="F265" s="33" t="n"/>
+      <c r="E265" s="32" t="n"/>
+      <c r="F265" s="32" t="n"/>
       <c r="G265" s="31" t="n"/>
       <c r="H265" s="31" t="n"/>
     </row>
     <row r="266" ht="20" customHeight="1">
-      <c r="A266" s="32" t="n"/>
+      <c r="A266" s="31" t="n"/>
       <c r="B266" s="31" t="n"/>
       <c r="C266" s="31" t="n"/>
       <c r="D266" s="31" t="n"/>
-      <c r="E266" s="33" t="n"/>
-      <c r="F266" s="33" t="n"/>
+      <c r="E266" s="32" t="n"/>
+      <c r="F266" s="32" t="n"/>
       <c r="G266" s="31" t="n"/>
       <c r="H266" s="31" t="n"/>
     </row>
     <row r="267" ht="20" customHeight="1">
-      <c r="A267" s="32" t="n"/>
+      <c r="A267" s="31" t="n"/>
       <c r="B267" s="31" t="n"/>
       <c r="C267" s="31" t="n"/>
       <c r="D267" s="31" t="n"/>
-      <c r="E267" s="33" t="n"/>
-      <c r="F267" s="33" t="n"/>
+      <c r="E267" s="32" t="n"/>
+      <c r="F267" s="32" t="n"/>
       <c r="G267" s="31" t="n"/>
       <c r="H267" s="31" t="n"/>
     </row>
     <row r="268" ht="20" customHeight="1">
-      <c r="A268" s="32" t="n"/>
+      <c r="A268" s="31" t="n"/>
       <c r="B268" s="31" t="n"/>
       <c r="C268" s="31" t="n"/>
       <c r="D268" s="31" t="n"/>
-      <c r="E268" s="33" t="n"/>
-      <c r="F268" s="33" t="n"/>
+      <c r="E268" s="32" t="n"/>
+      <c r="F268" s="32" t="n"/>
       <c r="G268" s="31" t="n"/>
       <c r="H268" s="31" t="n"/>
     </row>
     <row r="269" ht="20" customHeight="1">
-      <c r="A269" s="32" t="n"/>
+      <c r="A269" s="31" t="n"/>
       <c r="B269" s="31" t="n"/>
       <c r="C269" s="31" t="n"/>
       <c r="D269" s="31" t="n"/>
-      <c r="E269" s="33" t="n"/>
-      <c r="F269" s="33" t="n"/>
+      <c r="E269" s="32" t="n"/>
+      <c r="F269" s="32" t="n"/>
       <c r="G269" s="31" t="n"/>
       <c r="H269" s="31" t="n"/>
     </row>
     <row r="270" ht="20" customHeight="1">
-      <c r="A270" s="32" t="n"/>
+      <c r="A270" s="31" t="n"/>
       <c r="B270" s="31" t="n"/>
       <c r="C270" s="31" t="n"/>
       <c r="D270" s="31" t="n"/>
-      <c r="E270" s="33" t="n"/>
-      <c r="F270" s="33" t="n"/>
+      <c r="E270" s="32" t="n"/>
+      <c r="F270" s="32" t="n"/>
       <c r="G270" s="31" t="n"/>
       <c r="H270" s="31" t="n"/>
     </row>
     <row r="271" ht="20" customHeight="1">
-      <c r="A271" s="32" t="n"/>
+      <c r="A271" s="31" t="n"/>
       <c r="B271" s="31" t="n"/>
       <c r="C271" s="31" t="n"/>
       <c r="D271" s="31" t="n"/>
-      <c r="E271" s="33" t="n"/>
-      <c r="F271" s="33" t="n"/>
+      <c r="E271" s="32" t="n"/>
+      <c r="F271" s="32" t="n"/>
       <c r="G271" s="31" t="n"/>
       <c r="H271" s="31" t="n"/>
     </row>
     <row r="272" ht="20" customHeight="1">
-      <c r="A272" s="32" t="n"/>
+      <c r="A272" s="31" t="n"/>
       <c r="B272" s="31" t="n"/>
       <c r="C272" s="31" t="n"/>
       <c r="D272" s="31" t="n"/>
-      <c r="E272" s="33" t="n"/>
-      <c r="F272" s="33" t="n"/>
+      <c r="E272" s="32" t="n"/>
+      <c r="F272" s="32" t="n"/>
       <c r="G272" s="31" t="n"/>
       <c r="H272" s="31" t="n"/>
     </row>
     <row r="273" ht="20" customHeight="1">
-      <c r="A273" s="32" t="n"/>
+      <c r="A273" s="31" t="n"/>
       <c r="B273" s="31" t="n"/>
       <c r="C273" s="31" t="n"/>
       <c r="D273" s="31" t="n"/>
-      <c r="E273" s="33" t="n"/>
-      <c r="F273" s="33" t="n"/>
+      <c r="E273" s="32" t="n"/>
+      <c r="F273" s="32" t="n"/>
       <c r="G273" s="31" t="n"/>
       <c r="H273" s="31" t="n"/>
     </row>
     <row r="274" ht="20" customHeight="1">
-      <c r="A274" s="32" t="n"/>
+      <c r="A274" s="31" t="n"/>
       <c r="B274" s="31" t="n"/>
       <c r="C274" s="31" t="n"/>
       <c r="D274" s="31" t="n"/>
-      <c r="E274" s="33" t="n"/>
-      <c r="F274" s="33" t="n"/>
+      <c r="E274" s="32" t="n"/>
+      <c r="F274" s="32" t="n"/>
       <c r="G274" s="31" t="n"/>
       <c r="H274" s="31" t="n"/>
     </row>
     <row r="275" ht="20" customHeight="1">
-      <c r="A275" s="32" t="n"/>
+      <c r="A275" s="31" t="n"/>
       <c r="B275" s="31" t="n"/>
       <c r="C275" s="31" t="n"/>
       <c r="D275" s="31" t="n"/>
-      <c r="E275" s="33" t="n"/>
-      <c r="F275" s="33" t="n"/>
+      <c r="E275" s="32" t="n"/>
+      <c r="F275" s="32" t="n"/>
       <c r="G275" s="31" t="n"/>
       <c r="H275" s="31" t="n"/>
     </row>
     <row r="276" ht="20" customHeight="1">
-      <c r="A276" s="32" t="n"/>
+      <c r="A276" s="31" t="n"/>
       <c r="B276" s="31" t="n"/>
       <c r="C276" s="31" t="n"/>
       <c r="D276" s="31" t="n"/>
-      <c r="E276" s="33" t="n"/>
-      <c r="F276" s="33" t="n"/>
+      <c r="E276" s="32" t="n"/>
+      <c r="F276" s="32" t="n"/>
       <c r="G276" s="31" t="n"/>
       <c r="H276" s="31" t="n"/>
     </row>
     <row r="277" ht="20" customHeight="1">
-      <c r="A277" s="32" t="n"/>
+      <c r="A277" s="31" t="n"/>
       <c r="B277" s="31" t="n"/>
       <c r="C277" s="31" t="n"/>
       <c r="D277" s="31" t="n"/>
-      <c r="E277" s="33" t="n"/>
-      <c r="F277" s="33" t="n"/>
+      <c r="E277" s="32" t="n"/>
+      <c r="F277" s="32" t="n"/>
       <c r="G277" s="31" t="n"/>
       <c r="H277" s="31" t="n"/>
     </row>
     <row r="278" ht="20" customHeight="1">
-      <c r="A278" s="32" t="n"/>
+      <c r="A278" s="31" t="n"/>
       <c r="B278" s="31" t="n"/>
       <c r="C278" s="31" t="n"/>
       <c r="D278" s="31" t="n"/>
-      <c r="E278" s="33" t="n"/>
-      <c r="F278" s="33" t="n"/>
+      <c r="E278" s="32" t="n"/>
+      <c r="F278" s="32" t="n"/>
       <c r="G278" s="31" t="n"/>
       <c r="H278" s="31" t="n"/>
     </row>
     <row r="279" ht="20" customHeight="1">
-      <c r="A279" s="32" t="n"/>
+      <c r="A279" s="31" t="n"/>
       <c r="B279" s="31" t="n"/>
       <c r="C279" s="31" t="n"/>
       <c r="D279" s="31" t="n"/>
-      <c r="E279" s="33" t="n"/>
-      <c r="F279" s="33" t="n"/>
+      <c r="E279" s="32" t="n"/>
+      <c r="F279" s="32" t="n"/>
       <c r="G279" s="31" t="n"/>
       <c r="H279" s="31" t="n"/>
     </row>
     <row r="280" ht="20" customHeight="1">
-      <c r="A280" s="32" t="n"/>
+      <c r="A280" s="31" t="n"/>
       <c r="B280" s="31" t="n"/>
       <c r="C280" s="31" t="n"/>
       <c r="D280" s="31" t="n"/>
-      <c r="E280" s="33" t="n"/>
-      <c r="F280" s="33" t="n"/>
+      <c r="E280" s="32" t="n"/>
+      <c r="F280" s="32" t="n"/>
       <c r="G280" s="31" t="n"/>
       <c r="H280" s="31" t="n"/>
     </row>
     <row r="281" ht="20" customHeight="1">
-      <c r="A281" s="32" t="n"/>
+      <c r="A281" s="31" t="n"/>
       <c r="B281" s="31" t="n"/>
       <c r="C281" s="31" t="n"/>
       <c r="D281" s="31" t="n"/>
-      <c r="E281" s="33" t="n"/>
-      <c r="F281" s="33" t="n"/>
+      <c r="E281" s="32" t="n"/>
+      <c r="F281" s="32" t="n"/>
       <c r="G281" s="31" t="n"/>
       <c r="H281" s="31" t="n"/>
     </row>
     <row r="282" ht="20" customHeight="1">
-      <c r="A282" s="32" t="n"/>
+      <c r="A282" s="31" t="n"/>
       <c r="B282" s="31" t="n"/>
       <c r="C282" s="31" t="n"/>
       <c r="D282" s="31" t="n"/>
-      <c r="E282" s="33" t="n"/>
-      <c r="F282" s="33" t="n"/>
+      <c r="E282" s="32" t="n"/>
+      <c r="F282" s="32" t="n"/>
       <c r="G282" s="31" t="n"/>
       <c r="H282" s="31" t="n"/>
     </row>
     <row r="283" ht="20" customHeight="1">
-      <c r="A283" s="32" t="n"/>
+      <c r="A283" s="31" t="n"/>
       <c r="B283" s="31" t="n"/>
       <c r="C283" s="31" t="n"/>
       <c r="D283" s="31" t="n"/>
-      <c r="E283" s="33" t="n"/>
-      <c r="F283" s="33" t="n"/>
+      <c r="E283" s="32" t="n"/>
+      <c r="F283" s="32" t="n"/>
       <c r="G283" s="31" t="n"/>
       <c r="H283" s="31" t="n"/>
     </row>
     <row r="284" ht="20" customHeight="1">
-      <c r="A284" s="32" t="n"/>
+      <c r="A284" s="31" t="n"/>
       <c r="B284" s="31" t="n"/>
       <c r="C284" s="31" t="n"/>
       <c r="D284" s="31" t="n"/>
-      <c r="E284" s="33" t="n"/>
-      <c r="F284" s="33" t="n"/>
+      <c r="E284" s="32" t="n"/>
+      <c r="F284" s="32" t="n"/>
       <c r="G284" s="31" t="n"/>
       <c r="H284" s="31" t="n"/>
     </row>
     <row r="285" ht="20" customHeight="1">
-      <c r="A285" s="32" t="n"/>
+      <c r="A285" s="31" t="n"/>
       <c r="B285" s="31" t="n"/>
       <c r="C285" s="31" t="n"/>
       <c r="D285" s="31" t="n"/>
-      <c r="E285" s="33" t="n"/>
-      <c r="F285" s="33" t="n"/>
+      <c r="E285" s="32" t="n"/>
+      <c r="F285" s="32" t="n"/>
       <c r="G285" s="31" t="n"/>
       <c r="H285" s="31" t="n"/>
     </row>
     <row r="286" ht="20" customHeight="1">
-      <c r="A286" s="32" t="n"/>
+      <c r="A286" s="31" t="n"/>
       <c r="B286" s="31" t="n"/>
       <c r="C286" s="31" t="n"/>
       <c r="D286" s="31" t="n"/>
-      <c r="E286" s="33" t="n"/>
-      <c r="F286" s="33" t="n"/>
+      <c r="E286" s="32" t="n"/>
+      <c r="F286" s="32" t="n"/>
       <c r="G286" s="31" t="n"/>
       <c r="H286" s="31" t="n"/>
     </row>
     <row r="287" ht="20" customHeight="1">
-      <c r="A287" s="32" t="n"/>
+      <c r="A287" s="31" t="n"/>
       <c r="B287" s="31" t="n"/>
       <c r="C287" s="31" t="n"/>
       <c r="D287" s="31" t="n"/>
-      <c r="E287" s="33" t="n"/>
-      <c r="F287" s="33" t="n"/>
+      <c r="E287" s="32" t="n"/>
+      <c r="F287" s="32" t="n"/>
       <c r="G287" s="31" t="n"/>
       <c r="H287" s="31" t="n"/>
     </row>
     <row r="288" ht="20" customHeight="1">
-      <c r="A288" s="32" t="n"/>
+      <c r="A288" s="31" t="n"/>
       <c r="B288" s="31" t="n"/>
       <c r="C288" s="31" t="n"/>
       <c r="D288" s="31" t="n"/>
-      <c r="E288" s="33" t="n"/>
-      <c r="F288" s="33" t="n"/>
+      <c r="E288" s="32" t="n"/>
+      <c r="F288" s="32" t="n"/>
       <c r="G288" s="31" t="n"/>
       <c r="H288" s="31" t="n"/>
     </row>
     <row r="289" ht="20" customHeight="1">
-      <c r="A289" s="32" t="n"/>
+      <c r="A289" s="31" t="n"/>
       <c r="B289" s="31" t="n"/>
       <c r="C289" s="31" t="n"/>
       <c r="D289" s="31" t="n"/>
-      <c r="E289" s="33" t="n"/>
-      <c r="F289" s="33" t="n"/>
+      <c r="E289" s="32" t="n"/>
+      <c r="F289" s="32" t="n"/>
       <c r="G289" s="31" t="n"/>
       <c r="H289" s="31" t="n"/>
     </row>
     <row r="290" ht="20" customHeight="1">
-      <c r="A290" s="32" t="n"/>
+      <c r="A290" s="31" t="n"/>
       <c r="B290" s="31" t="n"/>
       <c r="C290" s="31" t="n"/>
       <c r="D290" s="31" t="n"/>
-      <c r="E290" s="33" t="n"/>
-      <c r="F290" s="33" t="n"/>
+      <c r="E290" s="32" t="n"/>
+      <c r="F290" s="32" t="n"/>
       <c r="G290" s="31" t="n"/>
       <c r="H290" s="31" t="n"/>
     </row>
     <row r="291" ht="20" customHeight="1">
-      <c r="A291" s="32" t="n"/>
+      <c r="A291" s="31" t="n"/>
       <c r="B291" s="31" t="n"/>
       <c r="C291" s="31" t="n"/>
       <c r="D291" s="31" t="n"/>
-      <c r="E291" s="33" t="n"/>
-      <c r="F291" s="33" t="n"/>
+      <c r="E291" s="32" t="n"/>
+      <c r="F291" s="32" t="n"/>
       <c r="G291" s="31" t="n"/>
       <c r="H291" s="31" t="n"/>
     </row>
     <row r="292" ht="20" customHeight="1">
-      <c r="A292" s="32" t="n"/>
+      <c r="A292" s="31" t="n"/>
       <c r="B292" s="31" t="n"/>
       <c r="C292" s="31" t="n"/>
       <c r="D292" s="31" t="n"/>
-      <c r="E292" s="33" t="n"/>
-      <c r="F292" s="33" t="n"/>
+      <c r="E292" s="32" t="n"/>
+      <c r="F292" s="32" t="n"/>
       <c r="G292" s="31" t="n"/>
       <c r="H292" s="31" t="n"/>
     </row>
     <row r="293" ht="20" customHeight="1">
-      <c r="A293" s="32" t="n"/>
+      <c r="A293" s="31" t="n"/>
       <c r="B293" s="31" t="n"/>
       <c r="C293" s="31" t="n"/>
       <c r="D293" s="31" t="n"/>
-      <c r="E293" s="33" t="n"/>
-      <c r="F293" s="33" t="n"/>
+      <c r="E293" s="32" t="n"/>
+      <c r="F293" s="32" t="n"/>
       <c r="G293" s="31" t="n"/>
       <c r="H293" s="31" t="n"/>
     </row>
     <row r="294" ht="20" customHeight="1">
-      <c r="A294" s="32" t="n"/>
+      <c r="A294" s="31" t="n"/>
       <c r="B294" s="31" t="n"/>
       <c r="C294" s="31" t="n"/>
       <c r="D294" s="31" t="n"/>
-      <c r="E294" s="33" t="n"/>
-      <c r="F294" s="33" t="n"/>
+      <c r="E294" s="32" t="n"/>
+      <c r="F294" s="32" t="n"/>
       <c r="G294" s="31" t="n"/>
       <c r="H294" s="31" t="n"/>
     </row>
     <row r="295" ht="20" customHeight="1">
-      <c r="A295" s="32" t="n"/>
+      <c r="A295" s="31" t="n"/>
       <c r="B295" s="31" t="n"/>
       <c r="C295" s="31" t="n"/>
       <c r="D295" s="31" t="n"/>
-      <c r="E295" s="33" t="n"/>
-      <c r="F295" s="33" t="n"/>
+      <c r="E295" s="32" t="n"/>
+      <c r="F295" s="32" t="n"/>
       <c r="G295" s="31" t="n"/>
       <c r="H295" s="31" t="n"/>
     </row>
     <row r="296" ht="20" customHeight="1">
-      <c r="A296" s="32" t="n"/>
+      <c r="A296" s="31" t="n"/>
       <c r="B296" s="31" t="n"/>
       <c r="C296" s="31" t="n"/>
       <c r="D296" s="31" t="n"/>
-      <c r="E296" s="33" t="n"/>
-      <c r="F296" s="33" t="n"/>
+      <c r="E296" s="32" t="n"/>
+      <c r="F296" s="32" t="n"/>
       <c r="G296" s="31" t="n"/>
       <c r="H296" s="31" t="n"/>
     </row>
     <row r="297" ht="20" customHeight="1">
-      <c r="A297" s="32" t="n"/>
+      <c r="A297" s="31" t="n"/>
       <c r="B297" s="31" t="n"/>
       <c r="C297" s="31" t="n"/>
       <c r="D297" s="31" t="n"/>
-      <c r="E297" s="33" t="n"/>
-      <c r="F297" s="33" t="n"/>
+      <c r="E297" s="32" t="n"/>
+      <c r="F297" s="32" t="n"/>
       <c r="G297" s="31" t="n"/>
       <c r="H297" s="31" t="n"/>
     </row>
     <row r="298" ht="20" customHeight="1">
-      <c r="A298" s="32" t="n"/>
+      <c r="A298" s="31" t="n"/>
       <c r="B298" s="31" t="n"/>
       <c r="C298" s="31" t="n"/>
       <c r="D298" s="31" t="n"/>
-      <c r="E298" s="33" t="n"/>
-      <c r="F298" s="33" t="n"/>
+      <c r="E298" s="32" t="n"/>
+      <c r="F298" s="32" t="n"/>
       <c r="G298" s="31" t="n"/>
       <c r="H298" s="31" t="n"/>
     </row>
     <row r="299" ht="20" customHeight="1">
-      <c r="A299" s="32" t="n"/>
+      <c r="A299" s="31" t="n"/>
       <c r="B299" s="31" t="n"/>
       <c r="C299" s="31" t="n"/>
       <c r="D299" s="31" t="n"/>
-      <c r="E299" s="33" t="n"/>
-      <c r="F299" s="33" t="n"/>
+      <c r="E299" s="32" t="n"/>
+      <c r="F299" s="32" t="n"/>
       <c r="G299" s="31" t="n"/>
       <c r="H299" s="31" t="n"/>
     </row>
     <row r="300" ht="20" customHeight="1">
-      <c r="A300" s="32" t="n"/>
+      <c r="A300" s="31" t="n"/>
       <c r="B300" s="31" t="n"/>
       <c r="C300" s="31" t="n"/>
       <c r="D300" s="31" t="n"/>
-      <c r="E300" s="33" t="n"/>
-      <c r="F300" s="33" t="n"/>
+      <c r="E300" s="32" t="n"/>
+      <c r="F300" s="32" t="n"/>
       <c r="G300" s="31" t="n"/>
       <c r="H300" s="31" t="n"/>
     </row>
     <row r="301" ht="20" customHeight="1">
-      <c r="A301" s="32" t="n"/>
+      <c r="A301" s="31" t="n"/>
       <c r="B301" s="31" t="n"/>
       <c r="C301" s="31" t="n"/>
       <c r="D301" s="31" t="n"/>
-      <c r="E301" s="33" t="n"/>
-      <c r="F301" s="33" t="n"/>
+      <c r="E301" s="32" t="n"/>
+      <c r="F301" s="32" t="n"/>
       <c r="G301" s="31" t="n"/>
       <c r="H301" s="31" t="n"/>
     </row>
     <row r="302" ht="20" customHeight="1">
-      <c r="A302" s="32" t="n"/>
+      <c r="A302" s="31" t="n"/>
       <c r="B302" s="31" t="n"/>
       <c r="C302" s="31" t="n"/>
       <c r="D302" s="31" t="n"/>
-      <c r="E302" s="33" t="n"/>
-      <c r="F302" s="33" t="n"/>
+      <c r="E302" s="32" t="n"/>
+      <c r="F302" s="32" t="n"/>
       <c r="G302" s="31" t="n"/>
       <c r="H302" s="31" t="n"/>
     </row>
     <row r="303" ht="20" customHeight="1">
-      <c r="A303" s="32" t="n"/>
+      <c r="A303" s="31" t="n"/>
       <c r="B303" s="31" t="n"/>
       <c r="C303" s="31" t="n"/>
       <c r="D303" s="31" t="n"/>
-      <c r="E303" s="33" t="n"/>
-      <c r="F303" s="33" t="n"/>
+      <c r="E303" s="32" t="n"/>
+      <c r="F303" s="32" t="n"/>
       <c r="G303" s="31" t="n"/>
       <c r="H303" s="31" t="n"/>
     </row>
     <row r="304" ht="20" customHeight="1">
-      <c r="A304" s="32" t="n"/>
+      <c r="A304" s="31" t="n"/>
       <c r="B304" s="31" t="n"/>
       <c r="C304" s="31" t="n"/>
       <c r="D304" s="31" t="n"/>
-      <c r="E304" s="33" t="n"/>
-      <c r="F304" s="33" t="n"/>
+      <c r="E304" s="32" t="n"/>
+      <c r="F304" s="32" t="n"/>
       <c r="G304" s="31" t="n"/>
       <c r="H304" s="31" t="n"/>
     </row>
     <row r="305" ht="20" customHeight="1">
-      <c r="A305" s="32" t="n"/>
+      <c r="A305" s="31" t="n"/>
       <c r="B305" s="31" t="n"/>
       <c r="C305" s="31" t="n"/>
       <c r="D305" s="31" t="n"/>
-      <c r="E305" s="33" t="n"/>
-      <c r="F305" s="33" t="n"/>
+      <c r="E305" s="32" t="n"/>
+      <c r="F305" s="32" t="n"/>
       <c r="G305" s="31" t="n"/>
       <c r="H305" s="31" t="n"/>
     </row>
     <row r="306" ht="20" customHeight="1">
-      <c r="A306" s="32" t="n"/>
+      <c r="A306" s="31" t="n"/>
       <c r="B306" s="31" t="n"/>
       <c r="C306" s="31" t="n"/>
       <c r="D306" s="31" t="n"/>
-      <c r="E306" s="33" t="n"/>
-      <c r="F306" s="33" t="n"/>
+      <c r="E306" s="32" t="n"/>
+      <c r="F306" s="32" t="n"/>
       <c r="G306" s="31" t="n"/>
       <c r="H306" s="31" t="n"/>
     </row>
     <row r="307" ht="20" customHeight="1">
-      <c r="A307" s="32" t="n"/>
+      <c r="A307" s="31" t="n"/>
       <c r="B307" s="31" t="n"/>
       <c r="C307" s="31" t="n"/>
       <c r="D307" s="31" t="n"/>
-      <c r="E307" s="33" t="n"/>
-      <c r="F307" s="33" t="n"/>
+      <c r="E307" s="32" t="n"/>
+      <c r="F307" s="32" t="n"/>
       <c r="G307" s="31" t="n"/>
       <c r="H307" s="31" t="n"/>
     </row>
     <row r="308" ht="20" customHeight="1">
-      <c r="A308" s="32" t="n"/>
+      <c r="A308" s="31" t="n"/>
       <c r="B308" s="31" t="n"/>
       <c r="C308" s="31" t="n"/>
       <c r="D308" s="31" t="n"/>
-      <c r="E308" s="33" t="n"/>
-      <c r="F308" s="33" t="n"/>
+      <c r="E308" s="32" t="n"/>
+      <c r="F308" s="32" t="n"/>
       <c r="G308" s="31" t="n"/>
       <c r="H308" s="31" t="n"/>
     </row>
     <row r="309" ht="20" customHeight="1">
-      <c r="A309" s="32" t="n"/>
+      <c r="A309" s="31" t="n"/>
       <c r="B309" s="31" t="n"/>
       <c r="C309" s="31" t="n"/>
       <c r="D309" s="31" t="n"/>
-      <c r="E309" s="33" t="n"/>
-      <c r="F309" s="33" t="n"/>
+      <c r="E309" s="32" t="n"/>
+      <c r="F309" s="32" t="n"/>
       <c r="G309" s="31" t="n"/>
       <c r="H309" s="31" t="n"/>
     </row>
     <row r="310" ht="20" customHeight="1">
-      <c r="A310" s="32" t="n"/>
+      <c r="A310" s="31" t="n"/>
       <c r="B310" s="31" t="n"/>
       <c r="C310" s="31" t="n"/>
       <c r="D310" s="31" t="n"/>
-      <c r="E310" s="33" t="n"/>
-      <c r="F310" s="33" t="n"/>
+      <c r="E310" s="32" t="n"/>
+      <c r="F310" s="32" t="n"/>
       <c r="G310" s="31" t="n"/>
       <c r="H310" s="31" t="n"/>
     </row>
     <row r="311" ht="20" customHeight="1">
-      <c r="A311" s="32" t="n"/>
+      <c r="A311" s="31" t="n"/>
       <c r="B311" s="31" t="n"/>
       <c r="C311" s="31" t="n"/>
       <c r="D311" s="31" t="n"/>
-      <c r="E311" s="33" t="n"/>
-      <c r="F311" s="33" t="n"/>
+      <c r="E311" s="32" t="n"/>
+      <c r="F311" s="32" t="n"/>
       <c r="G311" s="31" t="n"/>
       <c r="H311" s="31" t="n"/>
     </row>
     <row r="312" ht="20" customHeight="1">
-      <c r="A312" s="32" t="n"/>
+      <c r="A312" s="31" t="n"/>
       <c r="B312" s="31" t="n"/>
       <c r="C312" s="31" t="n"/>
       <c r="D312" s="31" t="n"/>
-      <c r="E312" s="33" t="n"/>
-      <c r="F312" s="33" t="n"/>
+      <c r="E312" s="32" t="n"/>
+      <c r="F312" s="32" t="n"/>
       <c r="G312" s="31" t="n"/>
       <c r="H312" s="31" t="n"/>
     </row>
     <row r="313" ht="20" customHeight="1">
-      <c r="A313" s="32" t="n"/>
+      <c r="A313" s="31" t="n"/>
       <c r="B313" s="31" t="n"/>
       <c r="C313" s="31" t="n"/>
       <c r="D313" s="31" t="n"/>
-      <c r="E313" s="33" t="n"/>
-      <c r="F313" s="33" t="n"/>
+      <c r="E313" s="32" t="n"/>
+      <c r="F313" s="32" t="n"/>
       <c r="G313" s="31" t="n"/>
       <c r="H313" s="31" t="n"/>
     </row>
     <row r="314" ht="20" customHeight="1">
-      <c r="A314" s="32" t="n"/>
+      <c r="A314" s="31" t="n"/>
       <c r="B314" s="31" t="n"/>
       <c r="C314" s="31" t="n"/>
       <c r="D314" s="31" t="n"/>
-      <c r="E314" s="33" t="n"/>
-      <c r="F314" s="33" t="n"/>
+      <c r="E314" s="32" t="n"/>
+      <c r="F314" s="32" t="n"/>
       <c r="G314" s="31" t="n"/>
       <c r="H314" s="31" t="n"/>
     </row>
     <row r="315" ht="20" customHeight="1">
-      <c r="A315" s="32" t="n"/>
+      <c r="A315" s="31" t="n"/>
       <c r="B315" s="31" t="n"/>
       <c r="C315" s="31" t="n"/>
       <c r="D315" s="31" t="n"/>
-      <c r="E315" s="33" t="n"/>
-      <c r="F315" s="33" t="n"/>
+      <c r="E315" s="32" t="n"/>
+      <c r="F315" s="32" t="n"/>
       <c r="G315" s="31" t="n"/>
       <c r="H315" s="31" t="n"/>
     </row>
     <row r="316" ht="20" customHeight="1">
-      <c r="A316" s="32" t="n"/>
+      <c r="A316" s="31" t="n"/>
       <c r="B316" s="31" t="n"/>
       <c r="C316" s="31" t="n"/>
       <c r="D316" s="31" t="n"/>
-      <c r="E316" s="33" t="n"/>
-      <c r="F316" s="33" t="n"/>
+      <c r="E316" s="32" t="n"/>
+      <c r="F316" s="32" t="n"/>
       <c r="G316" s="31" t="n"/>
       <c r="H316" s="31" t="n"/>
     </row>
     <row r="317" ht="20" customHeight="1">
-      <c r="A317" s="32" t="n"/>
+      <c r="A317" s="31" t="n"/>
       <c r="B317" s="31" t="n"/>
       <c r="C317" s="31" t="n"/>
       <c r="D317" s="31" t="n"/>
-      <c r="E317" s="33" t="n"/>
-      <c r="F317" s="33" t="n"/>
+      <c r="E317" s="32" t="n"/>
+      <c r="F317" s="32" t="n"/>
       <c r="G317" s="31" t="n"/>
       <c r="H317" s="31" t="n"/>
     </row>
     <row r="318" ht="20" customHeight="1">
-      <c r="A318" s="32" t="n"/>
+      <c r="A318" s="31" t="n"/>
       <c r="B318" s="31" t="n"/>
       <c r="C318" s="31" t="n"/>
       <c r="D318" s="31" t="n"/>
-      <c r="E318" s="33" t="n"/>
-      <c r="F318" s="33" t="n"/>
+      <c r="E318" s="32" t="n"/>
+      <c r="F318" s="32" t="n"/>
       <c r="G318" s="31" t="n"/>
       <c r="H318" s="31" t="n"/>
     </row>
     <row r="319" ht="20" customHeight="1">
-      <c r="A319" s="32" t="n"/>
+      <c r="A319" s="31" t="n"/>
       <c r="B319" s="31" t="n"/>
       <c r="C319" s="31" t="n"/>
       <c r="D319" s="31" t="n"/>
-      <c r="E319" s="33" t="n"/>
-      <c r="F319" s="33" t="n"/>
+      <c r="E319" s="32" t="n"/>
+      <c r="F319" s="32" t="n"/>
       <c r="G319" s="31" t="n"/>
       <c r="H319" s="31" t="n"/>
     </row>
     <row r="320" ht="20" customHeight="1">
-      <c r="A320" s="32" t="n"/>
+      <c r="A320" s="31" t="n"/>
       <c r="B320" s="31" t="n"/>
       <c r="C320" s="31" t="n"/>
       <c r="D320" s="31" t="n"/>
-      <c r="E320" s="33" t="n"/>
-      <c r="F320" s="33" t="n"/>
+      <c r="E320" s="32" t="n"/>
+      <c r="F320" s="32" t="n"/>
       <c r="G320" s="31" t="n"/>
       <c r="H320" s="31" t="n"/>
     </row>
     <row r="321" ht="20" customHeight="1">
-      <c r="A321" s="32" t="n"/>
+      <c r="A321" s="31" t="n"/>
       <c r="B321" s="31" t="n"/>
       <c r="C321" s="31" t="n"/>
       <c r="D321" s="31" t="n"/>
-      <c r="E321" s="33" t="n"/>
-      <c r="F321" s="33" t="n"/>
+      <c r="E321" s="32" t="n"/>
+      <c r="F321" s="32" t="n"/>
       <c r="G321" s="31" t="n"/>
       <c r="H321" s="31" t="n"/>
     </row>
     <row r="322" ht="20" customHeight="1">
-      <c r="A322" s="32" t="n"/>
+      <c r="A322" s="31" t="n"/>
       <c r="B322" s="31" t="n"/>
       <c r="C322" s="31" t="n"/>
       <c r="D322" s="31" t="n"/>
-      <c r="E322" s="33" t="n"/>
-      <c r="F322" s="33" t="n"/>
+      <c r="E322" s="32" t="n"/>
+      <c r="F322" s="32" t="n"/>
       <c r="G322" s="31" t="n"/>
       <c r="H322" s="31" t="n"/>
     </row>
     <row r="323" ht="20" customHeight="1">
-      <c r="A323" s="32" t="n"/>
+      <c r="A323" s="31" t="n"/>
       <c r="B323" s="31" t="n"/>
       <c r="C323" s="31" t="n"/>
       <c r="D323" s="31" t="n"/>
-      <c r="E323" s="33" t="n"/>
-      <c r="F323" s="33" t="n"/>
+      <c r="E323" s="32" t="n"/>
+      <c r="F323" s="32" t="n"/>
       <c r="G323" s="31" t="n"/>
       <c r="H323" s="31" t="n"/>
     </row>
     <row r="324" ht="20" customHeight="1">
-      <c r="A324" s="32" t="n"/>
+      <c r="A324" s="31" t="n"/>
       <c r="B324" s="31" t="n"/>
       <c r="C324" s="31" t="n"/>
       <c r="D324" s="31" t="n"/>
-      <c r="E324" s="33" t="n"/>
-      <c r="F324" s="33" t="n"/>
+      <c r="E324" s="32" t="n"/>
+      <c r="F324" s="32" t="n"/>
       <c r="G324" s="31" t="n"/>
       <c r="H324" s="31" t="n"/>
     </row>
     <row r="325" ht="20" customHeight="1">
-      <c r="A325" s="32" t="n"/>
+      <c r="A325" s="31" t="n"/>
       <c r="B325" s="31" t="n"/>
       <c r="C325" s="31" t="n"/>
       <c r="D325" s="31" t="n"/>
-      <c r="E325" s="33" t="n"/>
-      <c r="F325" s="33" t="n"/>
+      <c r="E325" s="32" t="n"/>
+      <c r="F325" s="32" t="n"/>
       <c r="G325" s="31" t="n"/>
       <c r="H325" s="31" t="n"/>
     </row>
     <row r="326" ht="20" customHeight="1">
-      <c r="A326" s="32" t="n"/>
+      <c r="A326" s="31" t="n"/>
       <c r="B326" s="31" t="n"/>
       <c r="C326" s="31" t="n"/>
       <c r="D326" s="31" t="n"/>
-      <c r="E326" s="33" t="n"/>
-      <c r="F326" s="33" t="n"/>
+      <c r="E326" s="32" t="n"/>
+      <c r="F326" s="32" t="n"/>
       <c r="G326" s="31" t="n"/>
       <c r="H326" s="31" t="n"/>
     </row>
     <row r="327" ht="20" customHeight="1">
-      <c r="A327" s="32" t="n"/>
+      <c r="A327" s="31" t="n"/>
       <c r="B327" s="31" t="n"/>
       <c r="C327" s="31" t="n"/>
       <c r="D327" s="31" t="n"/>
-      <c r="E327" s="33" t="n"/>
-      <c r="F327" s="33" t="n"/>
+      <c r="E327" s="32" t="n"/>
+      <c r="F327" s="32" t="n"/>
       <c r="G327" s="31" t="n"/>
       <c r="H327" s="31" t="n"/>
     </row>
     <row r="328" ht="20" customHeight="1">
-      <c r="A328" s="32" t="n"/>
+      <c r="A328" s="31" t="n"/>
       <c r="B328" s="31" t="n"/>
       <c r="C328" s="31" t="n"/>
       <c r="D328" s="31" t="n"/>
-      <c r="E328" s="33" t="n"/>
-      <c r="F328" s="33" t="n"/>
+      <c r="E328" s="32" t="n"/>
+      <c r="F328" s="32" t="n"/>
       <c r="G328" s="31" t="n"/>
       <c r="H328" s="31" t="n"/>
     </row>
     <row r="329" ht="20" customHeight="1">
-      <c r="A329" s="32" t="n"/>
+      <c r="A329" s="31" t="n"/>
       <c r="B329" s="31" t="n"/>
       <c r="C329" s="31" t="n"/>
       <c r="D329" s="31" t="n"/>
-      <c r="E329" s="33" t="n"/>
-      <c r="F329" s="33" t="n"/>
+      <c r="E329" s="32" t="n"/>
+      <c r="F329" s="32" t="n"/>
       <c r="G329" s="31" t="n"/>
       <c r="H329" s="31" t="n"/>
     </row>
     <row r="330" ht="20" customHeight="1">
-      <c r="A330" s="32" t="n"/>
+      <c r="A330" s="31" t="n"/>
       <c r="B330" s="31" t="n"/>
       <c r="C330" s="31" t="n"/>
       <c r="D330" s="31" t="n"/>
-      <c r="E330" s="33" t="n"/>
-      <c r="F330" s="33" t="n"/>
+      <c r="E330" s="32" t="n"/>
+      <c r="F330" s="32" t="n"/>
       <c r="G330" s="31" t="n"/>
       <c r="H330" s="31" t="n"/>
     </row>
     <row r="331" ht="20" customHeight="1">
-      <c r="A331" s="32" t="n"/>
+      <c r="A331" s="31" t="n"/>
       <c r="B331" s="31" t="n"/>
       <c r="C331" s="31" t="n"/>
       <c r="D331" s="31" t="n"/>
-      <c r="E331" s="33" t="n"/>
-      <c r="F331" s="33" t="n"/>
+      <c r="E331" s="32" t="n"/>
+      <c r="F331" s="32" t="n"/>
       <c r="G331" s="31" t="n"/>
       <c r="H331" s="31" t="n"/>
     </row>
     <row r="332" ht="20" customHeight="1">
-      <c r="A332" s="32" t="n"/>
+      <c r="A332" s="31" t="n"/>
       <c r="B332" s="31" t="n"/>
       <c r="C332" s="31" t="n"/>
       <c r="D332" s="31" t="n"/>
-      <c r="E332" s="33" t="n"/>
-      <c r="F332" s="33" t="n"/>
+      <c r="E332" s="32" t="n"/>
+      <c r="F332" s="32" t="n"/>
       <c r="G332" s="31" t="n"/>
       <c r="H332" s="31" t="n"/>
     </row>
     <row r="333" ht="20" customHeight="1">
-      <c r="A333" s="32" t="n"/>
+      <c r="A333" s="31" t="n"/>
       <c r="B333" s="31" t="n"/>
       <c r="C333" s="31" t="n"/>
       <c r="D333" s="31" t="n"/>
-      <c r="E333" s="33" t="n"/>
-      <c r="F333" s="33" t="n"/>
+      <c r="E333" s="32" t="n"/>
+      <c r="F333" s="32" t="n"/>
       <c r="G333" s="31" t="n"/>
       <c r="H333" s="31" t="n"/>
     </row>
     <row r="334" ht="20" customHeight="1">
-      <c r="A334" s="32" t="n"/>
+      <c r="A334" s="31" t="n"/>
       <c r="B334" s="31" t="n"/>
       <c r="C334" s="31" t="n"/>
       <c r="D334" s="31" t="n"/>
-      <c r="E334" s="33" t="n"/>
-      <c r="F334" s="33" t="n"/>
+      <c r="E334" s="32" t="n"/>
+      <c r="F334" s="32" t="n"/>
       <c r="G334" s="31" t="n"/>
       <c r="H334" s="31" t="n"/>
     </row>
     <row r="335" ht="20" customHeight="1">
-      <c r="A335" s="32" t="n"/>
+      <c r="A335" s="31" t="n"/>
       <c r="B335" s="31" t="n"/>
       <c r="C335" s="31" t="n"/>
       <c r="D335" s="31" t="n"/>
-      <c r="E335" s="33" t="n"/>
-      <c r="F335" s="33" t="n"/>
+      <c r="E335" s="32" t="n"/>
+      <c r="F335" s="32" t="n"/>
       <c r="G335" s="31" t="n"/>
       <c r="H335" s="31" t="n"/>
     </row>
     <row r="336" ht="20" customHeight="1">
-      <c r="A336" s="32" t="n"/>
+      <c r="A336" s="31" t="n"/>
       <c r="B336" s="31" t="n"/>
       <c r="C336" s="31" t="n"/>
       <c r="D336" s="31" t="n"/>
-      <c r="E336" s="33" t="n"/>
-      <c r="F336" s="33" t="n"/>
+      <c r="E336" s="32" t="n"/>
+      <c r="F336" s="32" t="n"/>
       <c r="G336" s="31" t="n"/>
       <c r="H336" s="31" t="n"/>
     </row>
     <row r="337" ht="20" customHeight="1">
-      <c r="A337" s="32" t="n"/>
+      <c r="A337" s="31" t="n"/>
       <c r="B337" s="31" t="n"/>
       <c r="C337" s="31" t="n"/>
       <c r="D337" s="31" t="n"/>
-      <c r="E337" s="33" t="n"/>
-      <c r="F337" s="33" t="n"/>
+      <c r="E337" s="32" t="n"/>
+      <c r="F337" s="32" t="n"/>
       <c r="G337" s="31" t="n"/>
       <c r="H337" s="31" t="n"/>
     </row>
     <row r="338" ht="20" customHeight="1">
-      <c r="A338" s="32" t="n"/>
+      <c r="A338" s="31" t="n"/>
       <c r="B338" s="31" t="n"/>
       <c r="C338" s="31" t="n"/>
       <c r="D338" s="31" t="n"/>
-      <c r="E338" s="33" t="n"/>
-      <c r="F338" s="33" t="n"/>
+      <c r="E338" s="32" t="n"/>
+      <c r="F338" s="32" t="n"/>
       <c r="G338" s="31" t="n"/>
       <c r="H338" s="31" t="n"/>
     </row>
     <row r="339" ht="20" customHeight="1">
-      <c r="A339" s="32" t="n"/>
+      <c r="A339" s="31" t="n"/>
       <c r="B339" s="31" t="n"/>
       <c r="C339" s="31" t="n"/>
       <c r="D339" s="31" t="n"/>
-      <c r="E339" s="33" t="n"/>
-      <c r="F339" s="33" t="n"/>
+      <c r="E339" s="32" t="n"/>
+      <c r="F339" s="32" t="n"/>
       <c r="G339" s="31" t="n"/>
       <c r="H339" s="31" t="n"/>
     </row>
     <row r="340" ht="20" customHeight="1">
-      <c r="A340" s="32" t="n"/>
+      <c r="A340" s="31" t="n"/>
       <c r="B340" s="31" t="n"/>
       <c r="C340" s="31" t="n"/>
       <c r="D340" s="31" t="n"/>
-      <c r="E340" s="33" t="n"/>
-      <c r="F340" s="33" t="n"/>
+      <c r="E340" s="32" t="n"/>
+      <c r="F340" s="32" t="n"/>
       <c r="G340" s="31" t="n"/>
       <c r="H340" s="31" t="n"/>
     </row>
     <row r="341" ht="20" customHeight="1">
-      <c r="A341" s="32" t="n"/>
+      <c r="A341" s="31" t="n"/>
       <c r="B341" s="31" t="n"/>
       <c r="C341" s="31" t="n"/>
       <c r="D341" s="31" t="n"/>
-      <c r="E341" s="33" t="n"/>
-      <c r="F341" s="33" t="n"/>
+      <c r="E341" s="32" t="n"/>
+      <c r="F341" s="32" t="n"/>
       <c r="G341" s="31" t="n"/>
       <c r="H341" s="31" t="n"/>
     </row>
     <row r="342" ht="20" customHeight="1">
-      <c r="A342" s="32" t="n"/>
+      <c r="A342" s="31" t="n"/>
       <c r="B342" s="31" t="n"/>
       <c r="C342" s="31" t="n"/>
       <c r="D342" s="31" t="n"/>
-      <c r="E342" s="33" t="n"/>
-      <c r="F342" s="33" t="n"/>
+      <c r="E342" s="32" t="n"/>
+      <c r="F342" s="32" t="n"/>
       <c r="G342" s="31" t="n"/>
       <c r="H342" s="31" t="n"/>
     </row>
     <row r="343" ht="20" customHeight="1">
-      <c r="A343" s="32" t="n"/>
+      <c r="A343" s="31" t="n"/>
       <c r="B343" s="31" t="n"/>
       <c r="C343" s="31" t="n"/>
       <c r="D343" s="31" t="n"/>
-      <c r="E343" s="33" t="n"/>
-      <c r="F343" s="33" t="n"/>
+      <c r="E343" s="32" t="n"/>
+      <c r="F343" s="32" t="n"/>
       <c r="G343" s="31" t="n"/>
       <c r="H343" s="31" t="n"/>
     </row>
     <row r="344" ht="20" customHeight="1">
-      <c r="A344" s="32" t="n"/>
+      <c r="A344" s="31" t="n"/>
       <c r="B344" s="31" t="n"/>
       <c r="C344" s="31" t="n"/>
       <c r="D344" s="31" t="n"/>
-      <c r="E344" s="33" t="n"/>
-      <c r="F344" s="33" t="n"/>
+      <c r="E344" s="32" t="n"/>
+      <c r="F344" s="32" t="n"/>
       <c r="G344" s="31" t="n"/>
       <c r="H344" s="31" t="n"/>
     </row>
     <row r="345" ht="20" customHeight="1">
-      <c r="A345" s="32" t="n"/>
+      <c r="A345" s="31" t="n"/>
       <c r="B345" s="31" t="n"/>
       <c r="C345" s="31" t="n"/>
       <c r="D345" s="31" t="n"/>
-      <c r="E345" s="33" t="n"/>
-      <c r="F345" s="33" t="n"/>
+      <c r="E345" s="32" t="n"/>
+      <c r="F345" s="32" t="n"/>
       <c r="G345" s="31" t="n"/>
       <c r="H345" s="31" t="n"/>
     </row>
     <row r="346" ht="20" customHeight="1">
-      <c r="A346" s="32" t="n"/>
+      <c r="A346" s="31" t="n"/>
       <c r="B346" s="31" t="n"/>
       <c r="C346" s="31" t="n"/>
       <c r="D346" s="31" t="n"/>
-      <c r="E346" s="33" t="n"/>
-      <c r="F346" s="33" t="n"/>
+      <c r="E346" s="32" t="n"/>
+      <c r="F346" s="32" t="n"/>
       <c r="G346" s="31" t="n"/>
       <c r="H346" s="31" t="n"/>
     </row>
     <row r="347" ht="20" customHeight="1">
-      <c r="A347" s="32" t="n"/>
+      <c r="A347" s="31" t="n"/>
       <c r="B347" s="31" t="n"/>
       <c r="C347" s="31" t="n"/>
       <c r="D347" s="31" t="n"/>
-      <c r="E347" s="33" t="n"/>
-      <c r="F347" s="33" t="n"/>
+      <c r="E347" s="32" t="n"/>
+      <c r="F347" s="32" t="n"/>
       <c r="G347" s="31" t="n"/>
       <c r="H347" s="31" t="n"/>
     </row>
     <row r="348" ht="20" customHeight="1">
-      <c r="A348" s="32" t="n"/>
+      <c r="A348" s="31" t="n"/>
       <c r="B348" s="31" t="n"/>
       <c r="C348" s="31" t="n"/>
       <c r="D348" s="31" t="n"/>
-      <c r="E348" s="33" t="n"/>
-      <c r="F348" s="33" t="n"/>
+      <c r="E348" s="32" t="n"/>
+      <c r="F348" s="32" t="n"/>
       <c r="G348" s="31" t="n"/>
       <c r="H348" s="31" t="n"/>
     </row>
     <row r="349" ht="20" customHeight="1">
-      <c r="A349" s="32" t="n"/>
+      <c r="A349" s="31" t="n"/>
       <c r="B349" s="31" t="n"/>
       <c r="C349" s="31" t="n"/>
       <c r="D349" s="31" t="n"/>
-      <c r="E349" s="33" t="n"/>
-      <c r="F349" s="33" t="n"/>
+      <c r="E349" s="32" t="n"/>
+      <c r="F349" s="32" t="n"/>
       <c r="G349" s="31" t="n"/>
       <c r="H349" s="31" t="n"/>
     </row>
     <row r="350" ht="20" customHeight="1">
-      <c r="A350" s="32" t="n"/>
+      <c r="A350" s="31" t="n"/>
       <c r="B350" s="31" t="n"/>
       <c r="C350" s="31" t="n"/>
       <c r="D350" s="31" t="n"/>
-      <c r="E350" s="33" t="n"/>
-      <c r="F350" s="33" t="n"/>
+      <c r="E350" s="32" t="n"/>
+      <c r="F350" s="32" t="n"/>
       <c r="G350" s="31" t="n"/>
       <c r="H350" s="31" t="n"/>
     </row>
     <row r="351" ht="20" customHeight="1">
-      <c r="A351" s="32" t="n"/>
+      <c r="A351" s="31" t="n"/>
       <c r="B351" s="31" t="n"/>
       <c r="C351" s="31" t="n"/>
       <c r="D351" s="31" t="n"/>
-      <c r="E351" s="33" t="n"/>
-      <c r="F351" s="33" t="n"/>
+      <c r="E351" s="32" t="n"/>
+      <c r="F351" s="32" t="n"/>
       <c r="G351" s="31" t="n"/>
       <c r="H351" s="31" t="n"/>
     </row>
     <row r="352" ht="20" customHeight="1">
-      <c r="A352" s="32" t="n"/>
+      <c r="A352" s="31" t="n"/>
       <c r="B352" s="31" t="n"/>
       <c r="C352" s="31" t="n"/>
       <c r="D352" s="31" t="n"/>
-      <c r="E352" s="33" t="n"/>
-      <c r="F352" s="33" t="n"/>
+      <c r="E352" s="32" t="n"/>
+      <c r="F352" s="32" t="n"/>
       <c r="G352" s="31" t="n"/>
       <c r="H352" s="31" t="n"/>
     </row>
     <row r="353" ht="20" customHeight="1">
-      <c r="A353" s="32" t="n"/>
+      <c r="A353" s="31" t="n"/>
       <c r="B353" s="31" t="n"/>
       <c r="C353" s="31" t="n"/>
       <c r="D353" s="31" t="n"/>
-      <c r="E353" s="33" t="n"/>
-      <c r="F353" s="33" t="n"/>
+      <c r="E353" s="32" t="n"/>
+      <c r="F353" s="32" t="n"/>
       <c r="G353" s="31" t="n"/>
       <c r="H353" s="31" t="n"/>
     </row>
     <row r="354" ht="20" customHeight="1">
-      <c r="A354" s="32" t="n"/>
+      <c r="A354" s="31" t="n"/>
       <c r="B354" s="31" t="n"/>
       <c r="C354" s="31" t="n"/>
       <c r="D354" s="31" t="n"/>
-      <c r="E354" s="33" t="n"/>
-      <c r="F354" s="33" t="n"/>
+      <c r="E354" s="32" t="n"/>
+      <c r="F354" s="32" t="n"/>
       <c r="G354" s="31" t="n"/>
       <c r="H354" s="31" t="n"/>
     </row>
     <row r="355" ht="20" customHeight="1">
-      <c r="A355" s="32" t="n"/>
+      <c r="A355" s="31" t="n"/>
       <c r="B355" s="31" t="n"/>
       <c r="C355" s="31" t="n"/>
       <c r="D355" s="31" t="n"/>
-      <c r="E355" s="33" t="n"/>
-      <c r="F355" s="33" t="n"/>
+      <c r="E355" s="32" t="n"/>
+      <c r="F355" s="32" t="n"/>
       <c r="G355" s="31" t="n"/>
       <c r="H355" s="31" t="n"/>
     </row>
     <row r="356" ht="20" customHeight="1">
-      <c r="A356" s="32" t="n"/>
+      <c r="A356" s="31" t="n"/>
       <c r="B356" s="31" t="n"/>
       <c r="C356" s="31" t="n"/>
       <c r="D356" s="31" t="n"/>
-      <c r="E356" s="33" t="n"/>
-      <c r="F356" s="33" t="n"/>
+      <c r="E356" s="32" t="n"/>
+      <c r="F356" s="32" t="n"/>
       <c r="G356" s="31" t="n"/>
       <c r="H356" s="31" t="n"/>
     </row>
     <row r="357" ht="20" customHeight="1">
-      <c r="A357" s="32" t="n"/>
+      <c r="A357" s="31" t="n"/>
       <c r="B357" s="31" t="n"/>
       <c r="C357" s="31" t="n"/>
       <c r="D357" s="31" t="n"/>
-      <c r="E357" s="33" t="n"/>
-      <c r="F357" s="33" t="n"/>
+      <c r="E357" s="32" t="n"/>
+      <c r="F357" s="32" t="n"/>
       <c r="G357" s="31" t="n"/>
       <c r="H357" s="31" t="n"/>
     </row>
     <row r="358" ht="20" customHeight="1">
-      <c r="A358" s="32" t="n"/>
+      <c r="A358" s="31" t="n"/>
       <c r="B358" s="31" t="n"/>
       <c r="C358" s="31" t="n"/>
       <c r="D358" s="31" t="n"/>
-      <c r="E358" s="33" t="n"/>
-      <c r="F358" s="33" t="n"/>
+      <c r="E358" s="32" t="n"/>
+      <c r="F358" s="32" t="n"/>
       <c r="G358" s="31" t="n"/>
       <c r="H358" s="31" t="n"/>
     </row>
     <row r="359" ht="20" customHeight="1">
-      <c r="A359" s="32" t="n"/>
+      <c r="A359" s="31" t="n"/>
       <c r="B359" s="31" t="n"/>
       <c r="C359" s="31" t="n"/>
       <c r="D359" s="31" t="n"/>
-      <c r="E359" s="33" t="n"/>
-      <c r="F359" s="33" t="n"/>
+      <c r="E359" s="32" t="n"/>
+      <c r="F359" s="32" t="n"/>
       <c r="G359" s="31" t="n"/>
       <c r="H359" s="31" t="n"/>
     </row>
     <row r="360" ht="20" customHeight="1">
-      <c r="A360" s="32" t="n"/>
+      <c r="A360" s="31" t="n"/>
       <c r="B360" s="31" t="n"/>
       <c r="C360" s="31" t="n"/>
       <c r="D360" s="31" t="n"/>
-      <c r="E360" s="33" t="n"/>
-      <c r="F360" s="33" t="n"/>
+      <c r="E360" s="32" t="n"/>
+      <c r="F360" s="32" t="n"/>
       <c r="G360" s="31" t="n"/>
       <c r="H360" s="31" t="n"/>
     </row>
     <row r="361" ht="20" customHeight="1">
-      <c r="A361" s="32" t="n"/>
+      <c r="A361" s="31" t="n"/>
       <c r="B361" s="31" t="n"/>
       <c r="C361" s="31" t="n"/>
       <c r="D361" s="31" t="n"/>
-      <c r="E361" s="33" t="n"/>
-      <c r="F361" s="33" t="n"/>
+      <c r="E361" s="32" t="n"/>
+      <c r="F361" s="32" t="n"/>
       <c r="G361" s="31" t="n"/>
       <c r="H361" s="31" t="n"/>
     </row>
     <row r="362" ht="20" customHeight="1">
-      <c r="A362" s="32" t="n"/>
+      <c r="A362" s="31" t="n"/>
       <c r="B362" s="31" t="n"/>
       <c r="C362" s="31" t="n"/>
       <c r="D362" s="31" t="n"/>
-      <c r="E362" s="33" t="n"/>
-      <c r="F362" s="33" t="n"/>
+      <c r="E362" s="32" t="n"/>
+      <c r="F362" s="32" t="n"/>
       <c r="G362" s="31" t="n"/>
       <c r="H362" s="31" t="n"/>
     </row>
     <row r="363" ht="20" customHeight="1">
-      <c r="A363" s="32" t="n"/>
+      <c r="A363" s="31" t="n"/>
       <c r="B363" s="31" t="n"/>
       <c r="C363" s="31" t="n"/>
       <c r="D363" s="31" t="n"/>
-      <c r="E363" s="33" t="n"/>
-      <c r="F363" s="33" t="n"/>
+      <c r="E363" s="32" t="n"/>
+      <c r="F363" s="32" t="n"/>
       <c r="G363" s="31" t="n"/>
       <c r="H363" s="31" t="n"/>
     </row>
     <row r="364" ht="20" customHeight="1">
-      <c r="A364" s="32" t="n"/>
+      <c r="A364" s="31" t="n"/>
       <c r="B364" s="31" t="n"/>
       <c r="C364" s="31" t="n"/>
       <c r="D364" s="31" t="n"/>
-      <c r="E364" s="33" t="n"/>
-      <c r="F364" s="33" t="n"/>
+      <c r="E364" s="32" t="n"/>
+      <c r="F364" s="32" t="n"/>
       <c r="G364" s="31" t="n"/>
       <c r="H364" s="31" t="n"/>
     </row>
     <row r="365" ht="20" customHeight="1">
-      <c r="A365" s="32" t="n"/>
+      <c r="A365" s="31" t="n"/>
       <c r="B365" s="31" t="n"/>
       <c r="C365" s="31" t="n"/>
       <c r="D365" s="31" t="n"/>
-      <c r="E365" s="33" t="n"/>
-      <c r="F365" s="33" t="n"/>
+      <c r="E365" s="32" t="n"/>
+      <c r="F365" s="32" t="n"/>
       <c r="G365" s="31" t="n"/>
       <c r="H365" s="31" t="n"/>
     </row>
     <row r="366" ht="20" customHeight="1">
-      <c r="A366" s="32" t="n"/>
+      <c r="A366" s="31" t="n"/>
       <c r="B366" s="31" t="n"/>
       <c r="C366" s="31" t="n"/>
       <c r="D366" s="31" t="n"/>
-      <c r="E366" s="33" t="n"/>
-      <c r="F366" s="33" t="n"/>
+      <c r="E366" s="32" t="n"/>
+      <c r="F366" s="32" t="n"/>
       <c r="G366" s="31" t="n"/>
       <c r="H366" s="31" t="n"/>
     </row>
     <row r="367" ht="20" customHeight="1">
-      <c r="A367" s="32" t="n"/>
+      <c r="A367" s="31" t="n"/>
       <c r="B367" s="31" t="n"/>
       <c r="C367" s="31" t="n"/>
       <c r="D367" s="31" t="n"/>
-      <c r="E367" s="33" t="n"/>
-      <c r="F367" s="33" t="n"/>
+      <c r="E367" s="32" t="n"/>
+      <c r="F367" s="32" t="n"/>
       <c r="G367" s="31" t="n"/>
       <c r="H367" s="31" t="n"/>
     </row>
     <row r="368" ht="20" customHeight="1">
-      <c r="A368" s="32" t="n"/>
+      <c r="A368" s="31" t="n"/>
       <c r="B368" s="31" t="n"/>
       <c r="C368" s="31" t="n"/>
       <c r="D368" s="31" t="n"/>
-      <c r="E368" s="33" t="n"/>
-      <c r="F368" s="33" t="n"/>
+      <c r="E368" s="32" t="n"/>
+      <c r="F368" s="32" t="n"/>
       <c r="G368" s="31" t="n"/>
       <c r="H368" s="31" t="n"/>
     </row>
     <row r="369" ht="20" customHeight="1">
-      <c r="A369" s="32" t="n"/>
+      <c r="A369" s="31" t="n"/>
       <c r="B369" s="31" t="n"/>
       <c r="C369" s="31" t="n"/>
       <c r="D369" s="31" t="n"/>
-      <c r="E369" s="33" t="n"/>
-      <c r="F369" s="33" t="n"/>
+      <c r="E369" s="32" t="n"/>
+      <c r="F369" s="32" t="n"/>
       <c r="G369" s="31" t="n"/>
       <c r="H369" s="31" t="n"/>
     </row>
     <row r="370" ht="20" customHeight="1">
-      <c r="A370" s="32" t="n"/>
+      <c r="A370" s="31" t="n"/>
       <c r="B370" s="31" t="n"/>
       <c r="C370" s="31" t="n"/>
       <c r="D370" s="31" t="n"/>
-      <c r="E370" s="33" t="n"/>
-      <c r="F370" s="33" t="n"/>
+      <c r="E370" s="32" t="n"/>
+      <c r="F370" s="32" t="n"/>
       <c r="G370" s="31" t="n"/>
       <c r="H370" s="31" t="n"/>
     </row>
     <row r="371" ht="20" customHeight="1">
-      <c r="A371" s="32" t="n"/>
+      <c r="A371" s="31" t="n"/>
       <c r="B371" s="31" t="n"/>
       <c r="C371" s="31" t="n"/>
       <c r="D371" s="31" t="n"/>
-      <c r="E371" s="33" t="n"/>
-      <c r="F371" s="33" t="n"/>
+      <c r="E371" s="32" t="n"/>
+      <c r="F371" s="32" t="n"/>
       <c r="G371" s="31" t="n"/>
       <c r="H371" s="31" t="n"/>
     </row>
     <row r="372" ht="20" customHeight="1">
-      <c r="A372" s="32" t="n"/>
+      <c r="A372" s="31" t="n"/>
       <c r="B372" s="31" t="n"/>
       <c r="C372" s="31" t="n"/>
       <c r="D372" s="31" t="n"/>
-      <c r="E372" s="33" t="n"/>
-      <c r="F372" s="33" t="n"/>
+      <c r="E372" s="32" t="n"/>
+      <c r="F372" s="32" t="n"/>
       <c r="G372" s="31" t="n"/>
       <c r="H372" s="31" t="n"/>
     </row>
     <row r="373" ht="20" customHeight="1">
-      <c r="A373" s="32" t="n"/>
+      <c r="A373" s="31" t="n"/>
       <c r="B373" s="31" t="n"/>
       <c r="C373" s="31" t="n"/>
       <c r="D373" s="31" t="n"/>
-      <c r="E373" s="33" t="n"/>
-      <c r="F373" s="33" t="n"/>
+      <c r="E373" s="32" t="n"/>
+      <c r="F373" s="32" t="n"/>
       <c r="G373" s="31" t="n"/>
       <c r="H373" s="31" t="n"/>
     </row>
     <row r="374" ht="20" customHeight="1">
-      <c r="A374" s="32" t="n"/>
+      <c r="A374" s="31" t="n"/>
       <c r="B374" s="31" t="n"/>
       <c r="C374" s="31" t="n"/>
       <c r="D374" s="31" t="n"/>
-      <c r="E374" s="33" t="n"/>
-      <c r="F374" s="33" t="n"/>
+      <c r="E374" s="32" t="n"/>
+      <c r="F374" s="32" t="n"/>
       <c r="G374" s="31" t="n"/>
       <c r="H374" s="31" t="n"/>
     </row>
     <row r="375" ht="20" customHeight="1">
-      <c r="A375" s="32" t="n"/>
+      <c r="A375" s="31" t="n"/>
       <c r="B375" s="31" t="n"/>
       <c r="C375" s="31" t="n"/>
       <c r="D375" s="31" t="n"/>
-      <c r="E375" s="33" t="n"/>
-      <c r="F375" s="33" t="n"/>
+      <c r="E375" s="32" t="n"/>
+      <c r="F375" s="32" t="n"/>
       <c r="G375" s="31" t="n"/>
       <c r="H375" s="31" t="n"/>
     </row>
     <row r="376" ht="20" customHeight="1">
-      <c r="A376" s="32" t="n"/>
+      <c r="A376" s="31" t="n"/>
       <c r="B376" s="31" t="n"/>
       <c r="C376" s="31" t="n"/>
       <c r="D376" s="31" t="n"/>
-      <c r="E376" s="33" t="n"/>
-      <c r="F376" s="33" t="n"/>
+      <c r="E376" s="32" t="n"/>
+      <c r="F376" s="32" t="n"/>
       <c r="G376" s="31" t="n"/>
       <c r="H376" s="31" t="n"/>
     </row>
     <row r="377" ht="20" customHeight="1">
-      <c r="A377" s="32" t="n"/>
+      <c r="A377" s="31" t="n"/>
       <c r="B377" s="31" t="n"/>
       <c r="C377" s="31" t="n"/>
       <c r="D377" s="31" t="n"/>
-      <c r="E377" s="33" t="n"/>
-      <c r="F377" s="33" t="n"/>
+      <c r="E377" s="32" t="n"/>
+      <c r="F377" s="32" t="n"/>
       <c r="G377" s="31" t="n"/>
       <c r="H377" s="31" t="n"/>
     </row>
     <row r="378" ht="20" customHeight="1">
-      <c r="A378" s="32" t="n"/>
+      <c r="A378" s="31" t="n"/>
       <c r="B378" s="31" t="n"/>
       <c r="C378" s="31" t="n"/>
       <c r="D378" s="31" t="n"/>
-      <c r="E378" s="33" t="n"/>
-      <c r="F378" s="33" t="n"/>
+      <c r="E378" s="32" t="n"/>
+      <c r="F378" s="32" t="n"/>
       <c r="G378" s="31" t="n"/>
       <c r="H378" s="31" t="n"/>
     </row>
     <row r="379" ht="20" customHeight="1">
-      <c r="A379" s="32" t="n"/>
+      <c r="A379" s="31" t="n"/>
       <c r="B379" s="31" t="n"/>
       <c r="C379" s="31" t="n"/>
       <c r="D379" s="31" t="n"/>
-      <c r="E379" s="33" t="n"/>
-      <c r="F379" s="33" t="n"/>
+      <c r="E379" s="32" t="n"/>
+      <c r="F379" s="32" t="n"/>
       <c r="G379" s="31" t="n"/>
       <c r="H379" s="31" t="n"/>
     </row>
     <row r="380" ht="20" customHeight="1">
-      <c r="A380" s="32" t="n"/>
+      <c r="A380" s="31" t="n"/>
       <c r="B380" s="31" t="n"/>
       <c r="C380" s="31" t="n"/>
       <c r="D380" s="31" t="n"/>
-      <c r="E380" s="33" t="n"/>
-      <c r="F380" s="33" t="n"/>
+      <c r="E380" s="32" t="n"/>
+      <c r="F380" s="32" t="n"/>
       <c r="G380" s="31" t="n"/>
       <c r="H380" s="31" t="n"/>
     </row>
     <row r="381" ht="20" customHeight="1">
-      <c r="A381" s="32" t="n"/>
+      <c r="A381" s="31" t="n"/>
       <c r="B381" s="31" t="n"/>
       <c r="C381" s="31" t="n"/>
       <c r="D381" s="31" t="n"/>
-      <c r="E381" s="33" t="n"/>
-      <c r="F381" s="33" t="n"/>
+      <c r="E381" s="32" t="n"/>
+      <c r="F381" s="32" t="n"/>
       <c r="G381" s="31" t="n"/>
       <c r="H381" s="31" t="n"/>
     </row>
     <row r="382" ht="20" customHeight="1">
-      <c r="A382" s="32" t="n"/>
+      <c r="A382" s="31" t="n"/>
       <c r="B382" s="31" t="n"/>
       <c r="C382" s="31" t="n"/>
       <c r="D382" s="31" t="n"/>
-      <c r="E382" s="33" t="n"/>
-      <c r="F382" s="33" t="n"/>
+      <c r="E382" s="32" t="n"/>
+      <c r="F382" s="32" t="n"/>
       <c r="G382" s="31" t="n"/>
       <c r="H382" s="31" t="n"/>
     </row>
     <row r="383" ht="20" customHeight="1">
-      <c r="A383" s="32" t="n"/>
+      <c r="A383" s="31" t="n"/>
       <c r="B383" s="31" t="n"/>
       <c r="C383" s="31" t="n"/>
       <c r="D383" s="31" t="n"/>
-      <c r="E383" s="33" t="n"/>
-      <c r="F383" s="33" t="n"/>
+      <c r="E383" s="32" t="n"/>
+      <c r="F383" s="32" t="n"/>
       <c r="G383" s="31" t="n"/>
       <c r="H383" s="31" t="n"/>
     </row>
     <row r="384" ht="20" customHeight="1">
-      <c r="A384" s="32" t="n"/>
+      <c r="A384" s="31" t="n"/>
       <c r="B384" s="31" t="n"/>
       <c r="C384" s="31" t="n"/>
       <c r="D384" s="31" t="n"/>
-      <c r="E384" s="33" t="n"/>
-      <c r="F384" s="33" t="n"/>
+      <c r="E384" s="32" t="n"/>
+      <c r="F384" s="32" t="n"/>
       <c r="G384" s="31" t="n"/>
       <c r="H384" s="31" t="n"/>
     </row>
     <row r="385" ht="20" customHeight="1">
-      <c r="A385" s="32" t="n"/>
+      <c r="A385" s="31" t="n"/>
       <c r="B385" s="31" t="n"/>
       <c r="C385" s="31" t="n"/>
       <c r="D385" s="31" t="n"/>
-      <c r="E385" s="33" t="n"/>
-      <c r="F385" s="33" t="n"/>
+      <c r="E385" s="32" t="n"/>
+      <c r="F385" s="32" t="n"/>
       <c r="G385" s="31" t="n"/>
       <c r="H385" s="31" t="n"/>
     </row>
     <row r="386" ht="20" customHeight="1">
-      <c r="A386" s="32" t="n"/>
+      <c r="A386" s="31" t="n"/>
       <c r="B386" s="31" t="n"/>
       <c r="C386" s="31" t="n"/>
       <c r="D386" s="31" t="n"/>
-      <c r="E386" s="33" t="n"/>
-      <c r="F386" s="33" t="n"/>
+      <c r="E386" s="32" t="n"/>
+      <c r="F386" s="32" t="n"/>
       <c r="G386" s="31" t="n"/>
       <c r="H386" s="31" t="n"/>
     </row>
     <row r="387" ht="20" customHeight="1">
-      <c r="A387" s="32" t="n"/>
+      <c r="A387" s="31" t="n"/>
       <c r="B387" s="31" t="n"/>
       <c r="C387" s="31" t="n"/>
       <c r="D387" s="31" t="n"/>
-      <c r="E387" s="33" t="n"/>
-      <c r="F387" s="33" t="n"/>
+      <c r="E387" s="32" t="n"/>
+      <c r="F387" s="32" t="n"/>
       <c r="G387" s="31" t="n"/>
       <c r="H387" s="31" t="n"/>
     </row>
     <row r="388" ht="20" customHeight="1">
-      <c r="A388" s="32" t="n"/>
+      <c r="A388" s="31" t="n"/>
       <c r="B388" s="31" t="n"/>
       <c r="C388" s="31" t="n"/>
       <c r="D388" s="31" t="n"/>
-      <c r="E388" s="33" t="n"/>
-      <c r="F388" s="33" t="n"/>
+      <c r="E388" s="32" t="n"/>
+      <c r="F388" s="32" t="n"/>
       <c r="G388" s="31" t="n"/>
       <c r="H388" s="31" t="n"/>
     </row>
     <row r="389" ht="20" customHeight="1">
-      <c r="A389" s="32" t="n"/>
+      <c r="A389" s="31" t="n"/>
       <c r="B389" s="31" t="n"/>
       <c r="C389" s="31" t="n"/>
       <c r="D389" s="31" t="n"/>
-      <c r="E389" s="33" t="n"/>
-      <c r="F389" s="33" t="n"/>
+      <c r="E389" s="32" t="n"/>
+      <c r="F389" s="32" t="n"/>
       <c r="G389" s="31" t="n"/>
       <c r="H389" s="31" t="n"/>
     </row>
     <row r="390" ht="20" customHeight="1">
-      <c r="A390" s="32" t="n"/>
+      <c r="A390" s="31" t="n"/>
       <c r="B390" s="31" t="n"/>
       <c r="C390" s="31" t="n"/>
       <c r="D390" s="31" t="n"/>
-      <c r="E390" s="33" t="n"/>
-      <c r="F390" s="33" t="n"/>
+      <c r="E390" s="32" t="n"/>
+      <c r="F390" s="32" t="n"/>
       <c r="G390" s="31" t="n"/>
       <c r="H390" s="31" t="n"/>
     </row>
     <row r="391" ht="20" customHeight="1">
-      <c r="A391" s="32" t="n"/>
+      <c r="A391" s="31" t="n"/>
       <c r="B391" s="31" t="n"/>
       <c r="C391" s="31" t="n"/>
       <c r="D391" s="31" t="n"/>
-      <c r="E391" s="33" t="n"/>
-      <c r="F391" s="33" t="n"/>
+      <c r="E391" s="32" t="n"/>
+      <c r="F391" s="32" t="n"/>
       <c r="G391" s="31" t="n"/>
       <c r="H391" s="31" t="n"/>
     </row>
     <row r="392" ht="20" customHeight="1">
-      <c r="A392" s="32" t="n"/>
+      <c r="A392" s="31" t="n"/>
       <c r="B392" s="31" t="n"/>
       <c r="C392" s="31" t="n"/>
       <c r="D392" s="31" t="n"/>
-      <c r="E392" s="33" t="n"/>
-      <c r="F392" s="33" t="n"/>
+      <c r="E392" s="32" t="n"/>
+      <c r="F392" s="32" t="n"/>
       <c r="G392" s="31" t="n"/>
       <c r="H392" s="31" t="n"/>
     </row>
     <row r="393" ht="20" customHeight="1">
-      <c r="A393" s="32" t="n"/>
+      <c r="A393" s="31" t="n"/>
       <c r="B393" s="31" t="n"/>
       <c r="C393" s="31" t="n"/>
       <c r="D393" s="31" t="n"/>
-      <c r="E393" s="33" t="n"/>
-      <c r="F393" s="33" t="n"/>
+      <c r="E393" s="32" t="n"/>
+      <c r="F393" s="32" t="n"/>
       <c r="G393" s="31" t="n"/>
       <c r="H393" s="31" t="n"/>
     </row>
     <row r="394" ht="20" customHeight="1">
-      <c r="A394" s="32" t="n"/>
+      <c r="A394" s="31" t="n"/>
       <c r="B394" s="31" t="n"/>
       <c r="C394" s="31" t="n"/>
       <c r="D394" s="31" t="n"/>
-      <c r="E394" s="33" t="n"/>
-      <c r="F394" s="33" t="n"/>
+      <c r="E394" s="32" t="n"/>
+      <c r="F394" s="32" t="n"/>
       <c r="G394" s="31" t="n"/>
       <c r="H394" s="31" t="n"/>
     </row>
     <row r="395" ht="20" customHeight="1">
-      <c r="A395" s="32" t="n"/>
+      <c r="A395" s="31" t="n"/>
       <c r="B395" s="31" t="n"/>
       <c r="C395" s="31" t="n"/>
       <c r="D395" s="31" t="n"/>
-      <c r="E395" s="33" t="n"/>
-      <c r="F395" s="33" t="n"/>
+      <c r="E395" s="32" t="n"/>
+      <c r="F395" s="32" t="n"/>
       <c r="G395" s="31" t="n"/>
       <c r="H395" s="31" t="n"/>
     </row>
     <row r="396" ht="20" customHeight="1">
-      <c r="A396" s="32" t="n"/>
+      <c r="A396" s="31" t="n"/>
       <c r="B396" s="31" t="n"/>
       <c r="C396" s="31" t="n"/>
       <c r="D396" s="31" t="n"/>
-      <c r="E396" s="33" t="n"/>
-      <c r="F396" s="33" t="n"/>
+      <c r="E396" s="32" t="n"/>
+      <c r="F396" s="32" t="n"/>
       <c r="G396" s="31" t="n"/>
       <c r="H396" s="31" t="n"/>
     </row>
     <row r="397" ht="20" customHeight="1">
-      <c r="A397" s="32" t="n"/>
+      <c r="A397" s="31" t="n"/>
       <c r="B397" s="31" t="n"/>
       <c r="C397" s="31" t="n"/>
       <c r="D397" s="31" t="n"/>
-      <c r="E397" s="33" t="n"/>
-      <c r="F397" s="33" t="n"/>
+      <c r="E397" s="32" t="n"/>
+      <c r="F397" s="32" t="n"/>
       <c r="G397" s="31" t="n"/>
       <c r="H397" s="31" t="n"/>
     </row>
     <row r="398" ht="20" customHeight="1">
-      <c r="A398" s="32" t="n"/>
+      <c r="A398" s="31" t="n"/>
       <c r="B398" s="31" t="n"/>
       <c r="C398" s="31" t="n"/>
       <c r="D398" s="31" t="n"/>
-      <c r="E398" s="33" t="n"/>
-      <c r="F398" s="33" t="n"/>
+      <c r="E398" s="32" t="n"/>
+      <c r="F398" s="32" t="n"/>
       <c r="G398" s="31" t="n"/>
       <c r="H398" s="31" t="n"/>
     </row>
     <row r="399" ht="20" customHeight="1">
-      <c r="A399" s="32" t="n"/>
+      <c r="A399" s="31" t="n"/>
       <c r="B399" s="31" t="n"/>
       <c r="C399" s="31" t="n"/>
       <c r="D399" s="31" t="n"/>
-      <c r="E399" s="33" t="n"/>
-      <c r="F399" s="33" t="n"/>
+      <c r="E399" s="32" t="n"/>
+      <c r="F399" s="32" t="n"/>
       <c r="G399" s="31" t="n"/>
       <c r="H399" s="31" t="n"/>
     </row>
     <row r="400" ht="20" customHeight="1">
-      <c r="A400" s="32" t="n"/>
+      <c r="A400" s="31" t="n"/>
       <c r="B400" s="31" t="n"/>
       <c r="C400" s="31" t="n"/>
       <c r="D400" s="31" t="n"/>
-      <c r="E400" s="33" t="n"/>
-      <c r="F400" s="33" t="n"/>
+      <c r="E400" s="32" t="n"/>
+      <c r="F400" s="32" t="n"/>
       <c r="G400" s="31" t="n"/>
       <c r="H400" s="31" t="n"/>
     </row>
+    <row r="401" ht="20" customHeight="1">
+      <c r="A401" s="31" t="n"/>
+      <c r="B401" s="31" t="n"/>
+      <c r="C401" s="31" t="n"/>
+      <c r="D401" s="31" t="n"/>
+      <c r="E401" s="32" t="n"/>
+      <c r="F401" s="32" t="n"/>
+      <c r="G401" s="31" t="n"/>
+      <c r="H401" s="31" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H400"/>
-  <conditionalFormatting sqref="D2:D400">
+  <autoFilter ref="A1:H401"/>
+  <conditionalFormatting sqref="D2:D401">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>EXACT($D2,"Norsk")</formula>
     </cfRule>
@@ -9071,28 +9029,34 @@
       <formula>EXACT($D2,"Valgfag")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:H400">
+  <conditionalFormatting sqref="A2:H401">
     <cfRule type="expression" priority="13" dxfId="12">
       <formula>AND($B2&lt;&gt;"",ISODD(MATCH($B2,Klasser,0)))</formula>
     </cfRule>
     <cfRule type="expression" priority="14" dxfId="13">
       <formula>AND($B2&lt;&gt;"",$B2&lt;&gt;$B1)</formula>
     </cfRule>
+    <cfRule type="expression" priority="15" dxfId="14">
+      <formula>AND($A2&lt;&gt;"",$A2&lt;&gt;$A1)</formula>
+    </cfRule>
   </conditionalFormatting>
-  <dataValidations count="5">
-    <dataValidation sqref="B2:B400" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Velg fra lista" prompt="Klassen dette gjelder. Velg «Alle» for alle klasser." type="list">
+  <dataValidations count="6">
+    <dataValidation sqref="A2:A401" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Velg fra lista" prompt="Velg uke. Lista viser ukenummer og datoer." type="list">
+      <formula1>Uker</formula1>
+    </dataValidation>
+    <dataValidation sqref="B2:B401" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Velg fra lista" prompt="Klassen dette gjelder. Velg «Alle» for alle klasser." type="list">
       <formula1>Klasser</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C400" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Velg fra lista" prompt="Dagen innholdet hører til." type="list">
+    <dataValidation sqref="C2:C401" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Velg fra lista" prompt="Dagen innholdet hører til." type="list">
       <formula1>Dager</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D400" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Velg fra lista" prompt="Faget. Må stemme med timeplanen for å havne i riktig time." type="list">
+    <dataValidation sqref="D2:D401" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Velg fra lista" prompt="Faget. Må stemme med timeplanen for å havne i riktig time." type="list">
       <formula1>Fagliste</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G400" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Velg fra lista" prompt="Når må det være gjort? La stå tomt om det ikke har frist." type="list">
+    <dataValidation sqref="G2:G401" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Velg fra lista" prompt="Når må det være gjort? La stå tomt om det ikke har frist." type="list">
       <formula1>Dager</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H400" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Velg fra lista" prompt="Merk prøver, innleveringer og turer." type="list">
+    <dataValidation sqref="H2:H401" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Velg fra lista" prompt="Merk prøver, innleveringer og turer." type="list">
       <formula1>Typer</formula1>
     </dataValidation>
   </dataValidations>
@@ -9106,13 +9070,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D120"/>
+  <dimension ref="A1:D121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="72" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -9138,8 +9102,10 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="32" t="n">
-        <v>35</v>
+      <c r="A2" s="31" t="inlineStr">
+        <is>
+          <t>35 · 24.–28. aug 2026</t>
+        </is>
       </c>
       <c r="B2" s="31" t="inlineStr">
         <is>
@@ -9151,15 +9117,17 @@
           <t>Velkommen til et nytt skoleår</t>
         </is>
       </c>
-      <c r="D2" s="33" t="inlineStr">
+      <c r="D2" s="32" t="inlineStr">
         <is>
           <t>Første skoledag er mandag kl. 08.30. Ta med skrivesaker og matpakke.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="32" t="n">
-        <v>36</v>
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t>36 · 31. aug – 4. sep 2026</t>
+        </is>
       </c>
       <c r="B3" s="31" t="inlineStr">
         <is>
@@ -9171,15 +9139,17 @@
           <t>Foreldremøte torsdag</t>
         </is>
       </c>
-      <c r="D3" s="33" t="inlineStr">
+      <c r="D3" s="32" t="inlineStr">
         <is>
           <t>Foreldremøte for hele trinnet torsdag kl. 18.00 i aulaen. Meld fra i Vigilo om dere kommer.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="32" t="n">
-        <v>36</v>
+      <c r="A4" s="31" t="inlineStr">
+        <is>
+          <t>36 · 31. aug – 4. sep 2026</t>
+        </is>
       </c>
       <c r="B4" s="31" t="inlineStr">
         <is>
@@ -9191,15 +9161,17 @@
           <t>Ny mattelærer fra mandag</t>
         </is>
       </c>
-      <c r="D4" s="33" t="inlineStr">
+      <c r="D4" s="32" t="inlineStr">
         <is>
           <t>Anders tar over mattetimene ut skoleåret. Han treffes på e-post og i Vigilo.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="32" t="n">
-        <v>36</v>
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>36 · 31. aug – 4. sep 2026</t>
+        </is>
       </c>
       <c r="B5" s="31" t="inlineStr">
         <is>
@@ -9211,15 +9183,17 @@
           <t>Museumstur torsdag</t>
         </is>
       </c>
-      <c r="D5" s="33" t="inlineStr">
+      <c r="D5" s="32" t="inlineStr">
         <is>
           <t>Vi går fra skolen kl. 12.00 og er tilbake til siste time. Ta med matpakke og drikke.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="32" t="n">
-        <v>37</v>
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>37 · 7.–11. sep 2026</t>
+        </is>
       </c>
       <c r="B6" s="31" t="inlineStr">
         <is>
@@ -9231,15 +9205,17 @@
           <t>Planleggingsdag fredag</t>
         </is>
       </c>
-      <c r="D6" s="33" t="inlineStr">
+      <c r="D6" s="32" t="inlineStr">
         <is>
           <t>Skolen slutter kl. 12.00 på fredag. SFO holder åpent som vanlig.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="32" t="n">
-        <v>37</v>
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>37 · 7.–11. sep 2026</t>
+        </is>
       </c>
       <c r="B7" s="31" t="inlineStr">
         <is>
@@ -9251,702 +9227,714 @@
           <t>Tentamen mandag</t>
         </is>
       </c>
-      <c r="D7" s="33" t="inlineStr">
+      <c r="D7" s="32" t="inlineStr">
         <is>
           <t>Norsktentamen mandag. Møt opp kl. 08.15 utenfor rom 305.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="32" t="n"/>
+      <c r="A8" s="31" t="n"/>
       <c r="B8" s="31" t="n"/>
       <c r="C8" s="31" t="n"/>
-      <c r="D8" s="33" t="n"/>
+      <c r="D8" s="32" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="32" t="n"/>
+      <c r="A9" s="31" t="n"/>
       <c r="B9" s="31" t="n"/>
       <c r="C9" s="31" t="n"/>
-      <c r="D9" s="33" t="n"/>
+      <c r="D9" s="32" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="32" t="n"/>
+      <c r="A10" s="31" t="n"/>
       <c r="B10" s="31" t="n"/>
       <c r="C10" s="31" t="n"/>
-      <c r="D10" s="33" t="n"/>
+      <c r="D10" s="32" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="32" t="n"/>
+      <c r="A11" s="31" t="n"/>
       <c r="B11" s="31" t="n"/>
       <c r="C11" s="31" t="n"/>
-      <c r="D11" s="33" t="n"/>
+      <c r="D11" s="32" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="32" t="n"/>
+      <c r="A12" s="31" t="n"/>
       <c r="B12" s="31" t="n"/>
       <c r="C12" s="31" t="n"/>
-      <c r="D12" s="33" t="n"/>
+      <c r="D12" s="32" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="32" t="n"/>
+      <c r="A13" s="31" t="n"/>
       <c r="B13" s="31" t="n"/>
       <c r="C13" s="31" t="n"/>
-      <c r="D13" s="33" t="n"/>
+      <c r="D13" s="32" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="32" t="n"/>
+      <c r="A14" s="31" t="n"/>
       <c r="B14" s="31" t="n"/>
       <c r="C14" s="31" t="n"/>
-      <c r="D14" s="33" t="n"/>
+      <c r="D14" s="32" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="32" t="n"/>
+      <c r="A15" s="31" t="n"/>
       <c r="B15" s="31" t="n"/>
       <c r="C15" s="31" t="n"/>
-      <c r="D15" s="33" t="n"/>
+      <c r="D15" s="32" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="32" t="n"/>
+      <c r="A16" s="31" t="n"/>
       <c r="B16" s="31" t="n"/>
       <c r="C16" s="31" t="n"/>
-      <c r="D16" s="33" t="n"/>
+      <c r="D16" s="32" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="32" t="n"/>
+      <c r="A17" s="31" t="n"/>
       <c r="B17" s="31" t="n"/>
       <c r="C17" s="31" t="n"/>
-      <c r="D17" s="33" t="n"/>
+      <c r="D17" s="32" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="32" t="n"/>
+      <c r="A18" s="31" t="n"/>
       <c r="B18" s="31" t="n"/>
       <c r="C18" s="31" t="n"/>
-      <c r="D18" s="33" t="n"/>
+      <c r="D18" s="32" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="32" t="n"/>
+      <c r="A19" s="31" t="n"/>
       <c r="B19" s="31" t="n"/>
       <c r="C19" s="31" t="n"/>
-      <c r="D19" s="33" t="n"/>
+      <c r="D19" s="32" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="32" t="n"/>
+      <c r="A20" s="31" t="n"/>
       <c r="B20" s="31" t="n"/>
       <c r="C20" s="31" t="n"/>
-      <c r="D20" s="33" t="n"/>
+      <c r="D20" s="32" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="32" t="n"/>
+      <c r="A21" s="31" t="n"/>
       <c r="B21" s="31" t="n"/>
       <c r="C21" s="31" t="n"/>
-      <c r="D21" s="33" t="n"/>
+      <c r="D21" s="32" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="32" t="n"/>
+      <c r="A22" s="31" t="n"/>
       <c r="B22" s="31" t="n"/>
       <c r="C22" s="31" t="n"/>
-      <c r="D22" s="33" t="n"/>
+      <c r="D22" s="32" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="32" t="n"/>
+      <c r="A23" s="31" t="n"/>
       <c r="B23" s="31" t="n"/>
       <c r="C23" s="31" t="n"/>
-      <c r="D23" s="33" t="n"/>
+      <c r="D23" s="32" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="32" t="n"/>
+      <c r="A24" s="31" t="n"/>
       <c r="B24" s="31" t="n"/>
       <c r="C24" s="31" t="n"/>
-      <c r="D24" s="33" t="n"/>
+      <c r="D24" s="32" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="32" t="n"/>
+      <c r="A25" s="31" t="n"/>
       <c r="B25" s="31" t="n"/>
       <c r="C25" s="31" t="n"/>
-      <c r="D25" s="33" t="n"/>
+      <c r="D25" s="32" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="32" t="n"/>
+      <c r="A26" s="31" t="n"/>
       <c r="B26" s="31" t="n"/>
       <c r="C26" s="31" t="n"/>
-      <c r="D26" s="33" t="n"/>
+      <c r="D26" s="32" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="32" t="n"/>
+      <c r="A27" s="31" t="n"/>
       <c r="B27" s="31" t="n"/>
       <c r="C27" s="31" t="n"/>
-      <c r="D27" s="33" t="n"/>
+      <c r="D27" s="32" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="32" t="n"/>
+      <c r="A28" s="31" t="n"/>
       <c r="B28" s="31" t="n"/>
       <c r="C28" s="31" t="n"/>
-      <c r="D28" s="33" t="n"/>
+      <c r="D28" s="32" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="32" t="n"/>
+      <c r="A29" s="31" t="n"/>
       <c r="B29" s="31" t="n"/>
       <c r="C29" s="31" t="n"/>
-      <c r="D29" s="33" t="n"/>
+      <c r="D29" s="32" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="32" t="n"/>
+      <c r="A30" s="31" t="n"/>
       <c r="B30" s="31" t="n"/>
       <c r="C30" s="31" t="n"/>
-      <c r="D30" s="33" t="n"/>
+      <c r="D30" s="32" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="32" t="n"/>
+      <c r="A31" s="31" t="n"/>
       <c r="B31" s="31" t="n"/>
       <c r="C31" s="31" t="n"/>
-      <c r="D31" s="33" t="n"/>
+      <c r="D31" s="32" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="32" t="n"/>
+      <c r="A32" s="31" t="n"/>
       <c r="B32" s="31" t="n"/>
       <c r="C32" s="31" t="n"/>
-      <c r="D32" s="33" t="n"/>
+      <c r="D32" s="32" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="32" t="n"/>
+      <c r="A33" s="31" t="n"/>
       <c r="B33" s="31" t="n"/>
       <c r="C33" s="31" t="n"/>
-      <c r="D33" s="33" t="n"/>
+      <c r="D33" s="32" t="n"/>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="32" t="n"/>
+      <c r="A34" s="31" t="n"/>
       <c r="B34" s="31" t="n"/>
       <c r="C34" s="31" t="n"/>
-      <c r="D34" s="33" t="n"/>
+      <c r="D34" s="32" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="32" t="n"/>
+      <c r="A35" s="31" t="n"/>
       <c r="B35" s="31" t="n"/>
       <c r="C35" s="31" t="n"/>
-      <c r="D35" s="33" t="n"/>
+      <c r="D35" s="32" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="32" t="n"/>
+      <c r="A36" s="31" t="n"/>
       <c r="B36" s="31" t="n"/>
       <c r="C36" s="31" t="n"/>
-      <c r="D36" s="33" t="n"/>
+      <c r="D36" s="32" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="32" t="n"/>
+      <c r="A37" s="31" t="n"/>
       <c r="B37" s="31" t="n"/>
       <c r="C37" s="31" t="n"/>
-      <c r="D37" s="33" t="n"/>
+      <c r="D37" s="32" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="32" t="n"/>
+      <c r="A38" s="31" t="n"/>
       <c r="B38" s="31" t="n"/>
       <c r="C38" s="31" t="n"/>
-      <c r="D38" s="33" t="n"/>
+      <c r="D38" s="32" t="n"/>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="32" t="n"/>
+      <c r="A39" s="31" t="n"/>
       <c r="B39" s="31" t="n"/>
       <c r="C39" s="31" t="n"/>
-      <c r="D39" s="33" t="n"/>
+      <c r="D39" s="32" t="n"/>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="32" t="n"/>
+      <c r="A40" s="31" t="n"/>
       <c r="B40" s="31" t="n"/>
       <c r="C40" s="31" t="n"/>
-      <c r="D40" s="33" t="n"/>
+      <c r="D40" s="32" t="n"/>
     </row>
     <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="32" t="n"/>
+      <c r="A41" s="31" t="n"/>
       <c r="B41" s="31" t="n"/>
       <c r="C41" s="31" t="n"/>
-      <c r="D41" s="33" t="n"/>
+      <c r="D41" s="32" t="n"/>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="32" t="n"/>
+      <c r="A42" s="31" t="n"/>
       <c r="B42" s="31" t="n"/>
       <c r="C42" s="31" t="n"/>
-      <c r="D42" s="33" t="n"/>
+      <c r="D42" s="32" t="n"/>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="32" t="n"/>
+      <c r="A43" s="31" t="n"/>
       <c r="B43" s="31" t="n"/>
       <c r="C43" s="31" t="n"/>
-      <c r="D43" s="33" t="n"/>
+      <c r="D43" s="32" t="n"/>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="32" t="n"/>
+      <c r="A44" s="31" t="n"/>
       <c r="B44" s="31" t="n"/>
       <c r="C44" s="31" t="n"/>
-      <c r="D44" s="33" t="n"/>
+      <c r="D44" s="32" t="n"/>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="32" t="n"/>
+      <c r="A45" s="31" t="n"/>
       <c r="B45" s="31" t="n"/>
       <c r="C45" s="31" t="n"/>
-      <c r="D45" s="33" t="n"/>
+      <c r="D45" s="32" t="n"/>
     </row>
     <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="32" t="n"/>
+      <c r="A46" s="31" t="n"/>
       <c r="B46" s="31" t="n"/>
       <c r="C46" s="31" t="n"/>
-      <c r="D46" s="33" t="n"/>
+      <c r="D46" s="32" t="n"/>
     </row>
     <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="32" t="n"/>
+      <c r="A47" s="31" t="n"/>
       <c r="B47" s="31" t="n"/>
       <c r="C47" s="31" t="n"/>
-      <c r="D47" s="33" t="n"/>
+      <c r="D47" s="32" t="n"/>
     </row>
     <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="32" t="n"/>
+      <c r="A48" s="31" t="n"/>
       <c r="B48" s="31" t="n"/>
       <c r="C48" s="31" t="n"/>
-      <c r="D48" s="33" t="n"/>
+      <c r="D48" s="32" t="n"/>
     </row>
     <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="32" t="n"/>
+      <c r="A49" s="31" t="n"/>
       <c r="B49" s="31" t="n"/>
       <c r="C49" s="31" t="n"/>
-      <c r="D49" s="33" t="n"/>
+      <c r="D49" s="32" t="n"/>
     </row>
     <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="32" t="n"/>
+      <c r="A50" s="31" t="n"/>
       <c r="B50" s="31" t="n"/>
       <c r="C50" s="31" t="n"/>
-      <c r="D50" s="33" t="n"/>
+      <c r="D50" s="32" t="n"/>
     </row>
     <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="32" t="n"/>
+      <c r="A51" s="31" t="n"/>
       <c r="B51" s="31" t="n"/>
       <c r="C51" s="31" t="n"/>
-      <c r="D51" s="33" t="n"/>
+      <c r="D51" s="32" t="n"/>
     </row>
     <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="32" t="n"/>
+      <c r="A52" s="31" t="n"/>
       <c r="B52" s="31" t="n"/>
       <c r="C52" s="31" t="n"/>
-      <c r="D52" s="33" t="n"/>
+      <c r="D52" s="32" t="n"/>
     </row>
     <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="32" t="n"/>
+      <c r="A53" s="31" t="n"/>
       <c r="B53" s="31" t="n"/>
       <c r="C53" s="31" t="n"/>
-      <c r="D53" s="33" t="n"/>
+      <c r="D53" s="32" t="n"/>
     </row>
     <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="32" t="n"/>
+      <c r="A54" s="31" t="n"/>
       <c r="B54" s="31" t="n"/>
       <c r="C54" s="31" t="n"/>
-      <c r="D54" s="33" t="n"/>
+      <c r="D54" s="32" t="n"/>
     </row>
     <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="32" t="n"/>
+      <c r="A55" s="31" t="n"/>
       <c r="B55" s="31" t="n"/>
       <c r="C55" s="31" t="n"/>
-      <c r="D55" s="33" t="n"/>
+      <c r="D55" s="32" t="n"/>
     </row>
     <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="32" t="n"/>
+      <c r="A56" s="31" t="n"/>
       <c r="B56" s="31" t="n"/>
       <c r="C56" s="31" t="n"/>
-      <c r="D56" s="33" t="n"/>
+      <c r="D56" s="32" t="n"/>
     </row>
     <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="32" t="n"/>
+      <c r="A57" s="31" t="n"/>
       <c r="B57" s="31" t="n"/>
       <c r="C57" s="31" t="n"/>
-      <c r="D57" s="33" t="n"/>
+      <c r="D57" s="32" t="n"/>
     </row>
     <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="32" t="n"/>
+      <c r="A58" s="31" t="n"/>
       <c r="B58" s="31" t="n"/>
       <c r="C58" s="31" t="n"/>
-      <c r="D58" s="33" t="n"/>
+      <c r="D58" s="32" t="n"/>
     </row>
     <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="32" t="n"/>
+      <c r="A59" s="31" t="n"/>
       <c r="B59" s="31" t="n"/>
       <c r="C59" s="31" t="n"/>
-      <c r="D59" s="33" t="n"/>
+      <c r="D59" s="32" t="n"/>
     </row>
     <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="32" t="n"/>
+      <c r="A60" s="31" t="n"/>
       <c r="B60" s="31" t="n"/>
       <c r="C60" s="31" t="n"/>
-      <c r="D60" s="33" t="n"/>
+      <c r="D60" s="32" t="n"/>
     </row>
     <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="32" t="n"/>
+      <c r="A61" s="31" t="n"/>
       <c r="B61" s="31" t="n"/>
       <c r="C61" s="31" t="n"/>
-      <c r="D61" s="33" t="n"/>
+      <c r="D61" s="32" t="n"/>
     </row>
     <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="32" t="n"/>
+      <c r="A62" s="31" t="n"/>
       <c r="B62" s="31" t="n"/>
       <c r="C62" s="31" t="n"/>
-      <c r="D62" s="33" t="n"/>
+      <c r="D62" s="32" t="n"/>
     </row>
     <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="32" t="n"/>
+      <c r="A63" s="31" t="n"/>
       <c r="B63" s="31" t="n"/>
       <c r="C63" s="31" t="n"/>
-      <c r="D63" s="33" t="n"/>
+      <c r="D63" s="32" t="n"/>
     </row>
     <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="32" t="n"/>
+      <c r="A64" s="31" t="n"/>
       <c r="B64" s="31" t="n"/>
       <c r="C64" s="31" t="n"/>
-      <c r="D64" s="33" t="n"/>
+      <c r="D64" s="32" t="n"/>
     </row>
     <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="32" t="n"/>
+      <c r="A65" s="31" t="n"/>
       <c r="B65" s="31" t="n"/>
       <c r="C65" s="31" t="n"/>
-      <c r="D65" s="33" t="n"/>
+      <c r="D65" s="32" t="n"/>
     </row>
     <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="32" t="n"/>
+      <c r="A66" s="31" t="n"/>
       <c r="B66" s="31" t="n"/>
       <c r="C66" s="31" t="n"/>
-      <c r="D66" s="33" t="n"/>
+      <c r="D66" s="32" t="n"/>
     </row>
     <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="32" t="n"/>
+      <c r="A67" s="31" t="n"/>
       <c r="B67" s="31" t="n"/>
       <c r="C67" s="31" t="n"/>
-      <c r="D67" s="33" t="n"/>
+      <c r="D67" s="32" t="n"/>
     </row>
     <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="32" t="n"/>
+      <c r="A68" s="31" t="n"/>
       <c r="B68" s="31" t="n"/>
       <c r="C68" s="31" t="n"/>
-      <c r="D68" s="33" t="n"/>
+      <c r="D68" s="32" t="n"/>
     </row>
     <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="32" t="n"/>
+      <c r="A69" s="31" t="n"/>
       <c r="B69" s="31" t="n"/>
       <c r="C69" s="31" t="n"/>
-      <c r="D69" s="33" t="n"/>
+      <c r="D69" s="32" t="n"/>
     </row>
     <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="32" t="n"/>
+      <c r="A70" s="31" t="n"/>
       <c r="B70" s="31" t="n"/>
       <c r="C70" s="31" t="n"/>
-      <c r="D70" s="33" t="n"/>
+      <c r="D70" s="32" t="n"/>
     </row>
     <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="32" t="n"/>
+      <c r="A71" s="31" t="n"/>
       <c r="B71" s="31" t="n"/>
       <c r="C71" s="31" t="n"/>
-      <c r="D71" s="33" t="n"/>
+      <c r="D71" s="32" t="n"/>
     </row>
     <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="32" t="n"/>
+      <c r="A72" s="31" t="n"/>
       <c r="B72" s="31" t="n"/>
       <c r="C72" s="31" t="n"/>
-      <c r="D72" s="33" t="n"/>
+      <c r="D72" s="32" t="n"/>
     </row>
     <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="32" t="n"/>
+      <c r="A73" s="31" t="n"/>
       <c r="B73" s="31" t="n"/>
       <c r="C73" s="31" t="n"/>
-      <c r="D73" s="33" t="n"/>
+      <c r="D73" s="32" t="n"/>
     </row>
     <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="32" t="n"/>
+      <c r="A74" s="31" t="n"/>
       <c r="B74" s="31" t="n"/>
       <c r="C74" s="31" t="n"/>
-      <c r="D74" s="33" t="n"/>
+      <c r="D74" s="32" t="n"/>
     </row>
     <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="32" t="n"/>
+      <c r="A75" s="31" t="n"/>
       <c r="B75" s="31" t="n"/>
       <c r="C75" s="31" t="n"/>
-      <c r="D75" s="33" t="n"/>
+      <c r="D75" s="32" t="n"/>
     </row>
     <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="32" t="n"/>
+      <c r="A76" s="31" t="n"/>
       <c r="B76" s="31" t="n"/>
       <c r="C76" s="31" t="n"/>
-      <c r="D76" s="33" t="n"/>
+      <c r="D76" s="32" t="n"/>
     </row>
     <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="32" t="n"/>
+      <c r="A77" s="31" t="n"/>
       <c r="B77" s="31" t="n"/>
       <c r="C77" s="31" t="n"/>
-      <c r="D77" s="33" t="n"/>
+      <c r="D77" s="32" t="n"/>
     </row>
     <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="32" t="n"/>
+      <c r="A78" s="31" t="n"/>
       <c r="B78" s="31" t="n"/>
       <c r="C78" s="31" t="n"/>
-      <c r="D78" s="33" t="n"/>
+      <c r="D78" s="32" t="n"/>
     </row>
     <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="32" t="n"/>
+      <c r="A79" s="31" t="n"/>
       <c r="B79" s="31" t="n"/>
       <c r="C79" s="31" t="n"/>
-      <c r="D79" s="33" t="n"/>
+      <c r="D79" s="32" t="n"/>
     </row>
     <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="32" t="n"/>
+      <c r="A80" s="31" t="n"/>
       <c r="B80" s="31" t="n"/>
       <c r="C80" s="31" t="n"/>
-      <c r="D80" s="33" t="n"/>
+      <c r="D80" s="32" t="n"/>
     </row>
     <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="32" t="n"/>
+      <c r="A81" s="31" t="n"/>
       <c r="B81" s="31" t="n"/>
       <c r="C81" s="31" t="n"/>
-      <c r="D81" s="33" t="n"/>
+      <c r="D81" s="32" t="n"/>
     </row>
     <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="32" t="n"/>
+      <c r="A82" s="31" t="n"/>
       <c r="B82" s="31" t="n"/>
       <c r="C82" s="31" t="n"/>
-      <c r="D82" s="33" t="n"/>
+      <c r="D82" s="32" t="n"/>
     </row>
     <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="32" t="n"/>
+      <c r="A83" s="31" t="n"/>
       <c r="B83" s="31" t="n"/>
       <c r="C83" s="31" t="n"/>
-      <c r="D83" s="33" t="n"/>
+      <c r="D83" s="32" t="n"/>
     </row>
     <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="32" t="n"/>
+      <c r="A84" s="31" t="n"/>
       <c r="B84" s="31" t="n"/>
       <c r="C84" s="31" t="n"/>
-      <c r="D84" s="33" t="n"/>
+      <c r="D84" s="32" t="n"/>
     </row>
     <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="32" t="n"/>
+      <c r="A85" s="31" t="n"/>
       <c r="B85" s="31" t="n"/>
       <c r="C85" s="31" t="n"/>
-      <c r="D85" s="33" t="n"/>
+      <c r="D85" s="32" t="n"/>
     </row>
     <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="32" t="n"/>
+      <c r="A86" s="31" t="n"/>
       <c r="B86" s="31" t="n"/>
       <c r="C86" s="31" t="n"/>
-      <c r="D86" s="33" t="n"/>
+      <c r="D86" s="32" t="n"/>
     </row>
     <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="32" t="n"/>
+      <c r="A87" s="31" t="n"/>
       <c r="B87" s="31" t="n"/>
       <c r="C87" s="31" t="n"/>
-      <c r="D87" s="33" t="n"/>
+      <c r="D87" s="32" t="n"/>
     </row>
     <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="32" t="n"/>
+      <c r="A88" s="31" t="n"/>
       <c r="B88" s="31" t="n"/>
       <c r="C88" s="31" t="n"/>
-      <c r="D88" s="33" t="n"/>
+      <c r="D88" s="32" t="n"/>
     </row>
     <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="32" t="n"/>
+      <c r="A89" s="31" t="n"/>
       <c r="B89" s="31" t="n"/>
       <c r="C89" s="31" t="n"/>
-      <c r="D89" s="33" t="n"/>
+      <c r="D89" s="32" t="n"/>
     </row>
     <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="32" t="n"/>
+      <c r="A90" s="31" t="n"/>
       <c r="B90" s="31" t="n"/>
       <c r="C90" s="31" t="n"/>
-      <c r="D90" s="33" t="n"/>
+      <c r="D90" s="32" t="n"/>
     </row>
     <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="32" t="n"/>
+      <c r="A91" s="31" t="n"/>
       <c r="B91" s="31" t="n"/>
       <c r="C91" s="31" t="n"/>
-      <c r="D91" s="33" t="n"/>
+      <c r="D91" s="32" t="n"/>
     </row>
     <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="32" t="n"/>
+      <c r="A92" s="31" t="n"/>
       <c r="B92" s="31" t="n"/>
       <c r="C92" s="31" t="n"/>
-      <c r="D92" s="33" t="n"/>
+      <c r="D92" s="32" t="n"/>
     </row>
     <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="32" t="n"/>
+      <c r="A93" s="31" t="n"/>
       <c r="B93" s="31" t="n"/>
       <c r="C93" s="31" t="n"/>
-      <c r="D93" s="33" t="n"/>
+      <c r="D93" s="32" t="n"/>
     </row>
     <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="32" t="n"/>
+      <c r="A94" s="31" t="n"/>
       <c r="B94" s="31" t="n"/>
       <c r="C94" s="31" t="n"/>
-      <c r="D94" s="33" t="n"/>
+      <c r="D94" s="32" t="n"/>
     </row>
     <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="32" t="n"/>
+      <c r="A95" s="31" t="n"/>
       <c r="B95" s="31" t="n"/>
       <c r="C95" s="31" t="n"/>
-      <c r="D95" s="33" t="n"/>
+      <c r="D95" s="32" t="n"/>
     </row>
     <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="32" t="n"/>
+      <c r="A96" s="31" t="n"/>
       <c r="B96" s="31" t="n"/>
       <c r="C96" s="31" t="n"/>
-      <c r="D96" s="33" t="n"/>
+      <c r="D96" s="32" t="n"/>
     </row>
     <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="32" t="n"/>
+      <c r="A97" s="31" t="n"/>
       <c r="B97" s="31" t="n"/>
       <c r="C97" s="31" t="n"/>
-      <c r="D97" s="33" t="n"/>
+      <c r="D97" s="32" t="n"/>
     </row>
     <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="32" t="n"/>
+      <c r="A98" s="31" t="n"/>
       <c r="B98" s="31" t="n"/>
       <c r="C98" s="31" t="n"/>
-      <c r="D98" s="33" t="n"/>
+      <c r="D98" s="32" t="n"/>
     </row>
     <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="32" t="n"/>
+      <c r="A99" s="31" t="n"/>
       <c r="B99" s="31" t="n"/>
       <c r="C99" s="31" t="n"/>
-      <c r="D99" s="33" t="n"/>
+      <c r="D99" s="32" t="n"/>
     </row>
     <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="32" t="n"/>
+      <c r="A100" s="31" t="n"/>
       <c r="B100" s="31" t="n"/>
       <c r="C100" s="31" t="n"/>
-      <c r="D100" s="33" t="n"/>
+      <c r="D100" s="32" t="n"/>
     </row>
     <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="32" t="n"/>
+      <c r="A101" s="31" t="n"/>
       <c r="B101" s="31" t="n"/>
       <c r="C101" s="31" t="n"/>
-      <c r="D101" s="33" t="n"/>
+      <c r="D101" s="32" t="n"/>
     </row>
     <row r="102" ht="20" customHeight="1">
-      <c r="A102" s="32" t="n"/>
+      <c r="A102" s="31" t="n"/>
       <c r="B102" s="31" t="n"/>
       <c r="C102" s="31" t="n"/>
-      <c r="D102" s="33" t="n"/>
+      <c r="D102" s="32" t="n"/>
     </row>
     <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="32" t="n"/>
+      <c r="A103" s="31" t="n"/>
       <c r="B103" s="31" t="n"/>
       <c r="C103" s="31" t="n"/>
-      <c r="D103" s="33" t="n"/>
+      <c r="D103" s="32" t="n"/>
     </row>
     <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="32" t="n"/>
+      <c r="A104" s="31" t="n"/>
       <c r="B104" s="31" t="n"/>
       <c r="C104" s="31" t="n"/>
-      <c r="D104" s="33" t="n"/>
+      <c r="D104" s="32" t="n"/>
     </row>
     <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="32" t="n"/>
+      <c r="A105" s="31" t="n"/>
       <c r="B105" s="31" t="n"/>
       <c r="C105" s="31" t="n"/>
-      <c r="D105" s="33" t="n"/>
+      <c r="D105" s="32" t="n"/>
     </row>
     <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="32" t="n"/>
+      <c r="A106" s="31" t="n"/>
       <c r="B106" s="31" t="n"/>
       <c r="C106" s="31" t="n"/>
-      <c r="D106" s="33" t="n"/>
+      <c r="D106" s="32" t="n"/>
     </row>
     <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="32" t="n"/>
+      <c r="A107" s="31" t="n"/>
       <c r="B107" s="31" t="n"/>
       <c r="C107" s="31" t="n"/>
-      <c r="D107" s="33" t="n"/>
+      <c r="D107" s="32" t="n"/>
     </row>
     <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="32" t="n"/>
+      <c r="A108" s="31" t="n"/>
       <c r="B108" s="31" t="n"/>
       <c r="C108" s="31" t="n"/>
-      <c r="D108" s="33" t="n"/>
+      <c r="D108" s="32" t="n"/>
     </row>
     <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="32" t="n"/>
+      <c r="A109" s="31" t="n"/>
       <c r="B109" s="31" t="n"/>
       <c r="C109" s="31" t="n"/>
-      <c r="D109" s="33" t="n"/>
+      <c r="D109" s="32" t="n"/>
     </row>
     <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="32" t="n"/>
+      <c r="A110" s="31" t="n"/>
       <c r="B110" s="31" t="n"/>
       <c r="C110" s="31" t="n"/>
-      <c r="D110" s="33" t="n"/>
+      <c r="D110" s="32" t="n"/>
     </row>
     <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="32" t="n"/>
+      <c r="A111" s="31" t="n"/>
       <c r="B111" s="31" t="n"/>
       <c r="C111" s="31" t="n"/>
-      <c r="D111" s="33" t="n"/>
+      <c r="D111" s="32" t="n"/>
     </row>
     <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="32" t="n"/>
+      <c r="A112" s="31" t="n"/>
       <c r="B112" s="31" t="n"/>
       <c r="C112" s="31" t="n"/>
-      <c r="D112" s="33" t="n"/>
+      <c r="D112" s="32" t="n"/>
     </row>
     <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="32" t="n"/>
+      <c r="A113" s="31" t="n"/>
       <c r="B113" s="31" t="n"/>
       <c r="C113" s="31" t="n"/>
-      <c r="D113" s="33" t="n"/>
+      <c r="D113" s="32" t="n"/>
     </row>
     <row r="114" ht="20" customHeight="1">
-      <c r="A114" s="32" t="n"/>
+      <c r="A114" s="31" t="n"/>
       <c r="B114" s="31" t="n"/>
       <c r="C114" s="31" t="n"/>
-      <c r="D114" s="33" t="n"/>
+      <c r="D114" s="32" t="n"/>
     </row>
     <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="32" t="n"/>
+      <c r="A115" s="31" t="n"/>
       <c r="B115" s="31" t="n"/>
       <c r="C115" s="31" t="n"/>
-      <c r="D115" s="33" t="n"/>
+      <c r="D115" s="32" t="n"/>
     </row>
     <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="32" t="n"/>
+      <c r="A116" s="31" t="n"/>
       <c r="B116" s="31" t="n"/>
       <c r="C116" s="31" t="n"/>
-      <c r="D116" s="33" t="n"/>
+      <c r="D116" s="32" t="n"/>
     </row>
     <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="32" t="n"/>
+      <c r="A117" s="31" t="n"/>
       <c r="B117" s="31" t="n"/>
       <c r="C117" s="31" t="n"/>
-      <c r="D117" s="33" t="n"/>
+      <c r="D117" s="32" t="n"/>
     </row>
     <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="32" t="n"/>
+      <c r="A118" s="31" t="n"/>
       <c r="B118" s="31" t="n"/>
       <c r="C118" s="31" t="n"/>
-      <c r="D118" s="33" t="n"/>
+      <c r="D118" s="32" t="n"/>
     </row>
     <row r="119" ht="20" customHeight="1">
-      <c r="A119" s="32" t="n"/>
+      <c r="A119" s="31" t="n"/>
       <c r="B119" s="31" t="n"/>
       <c r="C119" s="31" t="n"/>
-      <c r="D119" s="33" t="n"/>
+      <c r="D119" s="32" t="n"/>
     </row>
     <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="32" t="n"/>
+      <c r="A120" s="31" t="n"/>
       <c r="B120" s="31" t="n"/>
       <c r="C120" s="31" t="n"/>
-      <c r="D120" s="33" t="n"/>
+      <c r="D120" s="32" t="n"/>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="31" t="n"/>
+      <c r="B121" s="31" t="n"/>
+      <c r="C121" s="31" t="n"/>
+      <c r="D121" s="32" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D120"/>
-  <conditionalFormatting sqref="A2:D120">
+  <autoFilter ref="A1:D121"/>
+  <conditionalFormatting sqref="A2:D121">
     <cfRule type="expression" priority="1" dxfId="12">
       <formula>AND($B2&lt;&gt;"",ISODD(MATCH($B2,Klasser,0)))</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="13">
       <formula>AND($B2&lt;&gt;"",$B2&lt;&gt;$B1)</formula>
     </cfRule>
+    <cfRule type="expression" priority="3" dxfId="14">
+      <formula>AND($A2&lt;&gt;"",$A2&lt;&gt;$A1)</formula>
+    </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation sqref="B2:B120" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Velg fra lista" prompt="Klassen beskjeden gjelder. «Alle» går til alle." type="list">
+  <dataValidations count="2">
+    <dataValidation sqref="A2:A121" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Velg fra lista" prompt="Velg uke." type="list">
+      <formula1>Uker</formula1>
+    </dataValidation>
+    <dataValidation sqref="B2:B121" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Velg fra lista" prompt="Klassen beskjeden gjelder. «Alle» går til alle." type="list">
       <formula1>Klasser</formula1>
     </dataValidation>
   </dataValidations>
